--- a/dictionary/ユーザー辞書_統合版_公開用.xlsx
+++ b/dictionary/ユーザー辞書_統合版_公開用.xlsx
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6961" uniqueCount="1411">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6961" uniqueCount="1414">
   <si>
     <r>
       <rPr>
@@ -6767,26 +6767,7 @@
         <rFont val="WenQuanYi Zen Hei"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">処理：変更なし／文章修正／よみ統一／統合（重複・類似のため</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color rgb="FF595959"/>
-        <rFont val="游ゴシック"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">1</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color rgb="FF595959"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">件にまとめた）／削除。「一覧の</t>
+      <t xml:space="preserve">処理：変更なし／文章修正／よみ統一／統合（完全に同じ・同じ文で別のよみ・表記ゆれ・途中で切れた同じ文・似た内容）／削除。「一覧の</t>
     </r>
     <r>
       <rPr>
@@ -7075,7 +7056,7 @@
     <t xml:space="preserve">サイドレールや介助用手すりが確実に固定されているか、ガタつきが生じていないか定期的に点検してください。</t>
   </si>
   <si>
-    <t xml:space="preserve">統合（類似）</t>
+    <t xml:space="preserve">統合（似た内容）</t>
   </si>
   <si>
     <t xml:space="preserve">サイドレールや介助バーが確実に差し込まれ、固定されているか、使用前にガタつきがないか確認してください。</t>
@@ -7172,6 +7153,9 @@
   </si>
   <si>
     <t xml:space="preserve">シャワーベンチを利用する事で、入浴時の立ち座りや座位保持の安定に繋がるため、選定しました。</t>
+  </si>
+  <si>
+    <t xml:space="preserve">統合（同じ文・別のよみ）</t>
   </si>
   <si>
     <t xml:space="preserve">入浴時の立ち座りや座位保持の安定のため、選定しました。動作の安全のため、ひじ掛け跳ね上げ付きのシャワーチェアを選定。</t>
@@ -7379,7 +7363,7 @@
     <t xml:space="preserve">ご自身の生活に対する意欲やご要望は、引き続き現状のまま保たれています。</t>
   </si>
   <si>
-    <t xml:space="preserve">統合（重複）</t>
+    <t xml:space="preserve">統合（完全に同じ）</t>
   </si>
   <si>
     <t xml:space="preserve">現在ご利用中のサービスやご自宅の環境について、変わりなく継続されています。</t>
@@ -7401,6 +7385,9 @@
   </si>
   <si>
     <t xml:space="preserve">ケアプランセンターリプラス</t>
+  </si>
+  <si>
+    <t xml:space="preserve">統合（表記ゆれ）</t>
   </si>
   <si>
     <t xml:space="preserve">標準型の杖では支持基底面が狭く不安定なため、多点支持の杖により安定した歩行をサポートするため、選定しました。</t>
@@ -7712,6 +7699,9 @@
   </si>
   <si>
     <t xml:space="preserve">状況変化に伴う福祉用具追加の担当者会議に参加しました。追加する用具の適合状況を確認し、利用時の注意点をご説明するとともに</t>
+  </si>
+  <si>
+    <t xml:space="preserve">統合（途中で切れた同じ文）</t>
   </si>
   <si>
     <t xml:space="preserve">元の文が途中で切れていたため補完</t>
@@ -29624,7 +29614,7 @@
         <v>1157</v>
       </c>
       <c r="E105" s="60" t="s">
-        <v>1125</v>
+        <v>1158</v>
       </c>
       <c r="F105" s="60" t="s">
         <v>105</v>
@@ -29648,7 +29638,7 @@
         <v>967</v>
       </c>
       <c r="D106" s="61" t="s">
-        <v>1158</v>
+        <v>1159</v>
       </c>
       <c r="E106" s="60" t="s">
         <v>1083</v>
@@ -29675,7 +29665,7 @@
         <v>998</v>
       </c>
       <c r="D107" s="61" t="s">
-        <v>1159</v>
+        <v>1160</v>
       </c>
       <c r="E107" s="60" t="s">
         <v>1083</v>
@@ -29702,7 +29692,7 @@
         <v>997</v>
       </c>
       <c r="D108" s="61" t="s">
-        <v>1160</v>
+        <v>1161</v>
       </c>
       <c r="E108" s="60" t="s">
         <v>1125</v>
@@ -29729,7 +29719,7 @@
         <v>981</v>
       </c>
       <c r="D109" s="61" t="s">
-        <v>1161</v>
+        <v>1162</v>
       </c>
       <c r="E109" s="60" t="s">
         <v>1083</v>
@@ -29756,7 +29746,7 @@
         <v>989</v>
       </c>
       <c r="D110" s="61" t="s">
-        <v>1162</v>
+        <v>1163</v>
       </c>
       <c r="E110" s="60" t="s">
         <v>1083</v>
@@ -29783,7 +29773,7 @@
         <v>991</v>
       </c>
       <c r="D111" s="62" t="s">
-        <v>1163</v>
+        <v>1164</v>
       </c>
       <c r="E111" s="60" t="s">
         <v>1125</v>
@@ -29810,7 +29800,7 @@
         <v>217</v>
       </c>
       <c r="D112" s="61" t="s">
-        <v>1164</v>
+        <v>1165</v>
       </c>
       <c r="E112" s="60" t="s">
         <v>1068</v>
@@ -29828,7 +29818,7 @@
     </row>
     <row r="113" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A113" s="58" t="s">
-        <v>1165</v>
+        <v>1166</v>
       </c>
       <c r="B113" s="59" t="n">
         <v>1</v>
@@ -29837,7 +29827,7 @@
         <v>339</v>
       </c>
       <c r="D113" s="61" t="s">
-        <v>1166</v>
+        <v>1167</v>
       </c>
       <c r="E113" s="60" t="s">
         <v>17</v>
@@ -29846,7 +29836,7 @@
         <v>339</v>
       </c>
       <c r="G113" s="61" t="s">
-        <v>1166</v>
+        <v>1167</v>
       </c>
       <c r="H113" s="59" t="n">
         <v>180</v>
@@ -29855,7 +29845,7 @@
     </row>
     <row r="114" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A114" s="58" t="s">
-        <v>1165</v>
+        <v>1166</v>
       </c>
       <c r="B114" s="59" t="n">
         <v>2</v>
@@ -29864,7 +29854,7 @@
         <v>339</v>
       </c>
       <c r="D114" s="61" t="s">
-        <v>1167</v>
+        <v>1168</v>
       </c>
       <c r="E114" s="60" t="s">
         <v>17</v>
@@ -29873,7 +29863,7 @@
         <v>339</v>
       </c>
       <c r="G114" s="61" t="s">
-        <v>1167</v>
+        <v>1168</v>
       </c>
       <c r="H114" s="59" t="n">
         <v>181</v>
@@ -29882,7 +29872,7 @@
     </row>
     <row r="115" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A115" s="58" t="s">
-        <v>1165</v>
+        <v>1166</v>
       </c>
       <c r="B115" s="59" t="n">
         <v>3</v>
@@ -29891,7 +29881,7 @@
         <v>339</v>
       </c>
       <c r="D115" s="61" t="s">
-        <v>1168</v>
+        <v>1169</v>
       </c>
       <c r="E115" s="60" t="s">
         <v>1068</v>
@@ -29900,7 +29890,7 @@
         <v>339</v>
       </c>
       <c r="G115" s="61" t="s">
-        <v>1169</v>
+        <v>1170</v>
       </c>
       <c r="H115" s="59" t="n">
         <v>182</v>
@@ -29909,7 +29899,7 @@
     </row>
     <row r="116" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A116" s="58" t="s">
-        <v>1165</v>
+        <v>1166</v>
       </c>
       <c r="B116" s="59" t="n">
         <v>4</v>
@@ -29918,7 +29908,7 @@
         <v>339</v>
       </c>
       <c r="D116" s="61" t="s">
-        <v>1170</v>
+        <v>1171</v>
       </c>
       <c r="E116" s="60" t="s">
         <v>17</v>
@@ -29927,7 +29917,7 @@
         <v>339</v>
       </c>
       <c r="G116" s="61" t="s">
-        <v>1170</v>
+        <v>1171</v>
       </c>
       <c r="H116" s="59" t="n">
         <v>183</v>
@@ -29936,7 +29926,7 @@
     </row>
     <row r="117" customFormat="false" ht="16.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A117" s="58" t="s">
-        <v>1165</v>
+        <v>1166</v>
       </c>
       <c r="B117" s="59" t="n">
         <v>5</v>
@@ -29945,7 +29935,7 @@
         <v>339</v>
       </c>
       <c r="D117" s="61" t="s">
-        <v>1171</v>
+        <v>1172</v>
       </c>
       <c r="E117" s="60" t="s">
         <v>17</v>
@@ -29954,7 +29944,7 @@
         <v>339</v>
       </c>
       <c r="G117" s="61" t="s">
-        <v>1171</v>
+        <v>1172</v>
       </c>
       <c r="H117" s="59" t="n">
         <v>184</v>
@@ -29963,7 +29953,7 @@
     </row>
     <row r="118" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A118" s="58" t="s">
-        <v>1165</v>
+        <v>1166</v>
       </c>
       <c r="B118" s="59" t="n">
         <v>6</v>
@@ -29990,7 +29980,7 @@
     </row>
     <row r="119" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A119" s="58" t="s">
-        <v>1165</v>
+        <v>1166</v>
       </c>
       <c r="B119" s="59" t="n">
         <v>7</v>
@@ -29999,7 +29989,7 @@
         <v>349</v>
       </c>
       <c r="D119" s="61" t="s">
-        <v>1172</v>
+        <v>1173</v>
       </c>
       <c r="E119" s="60" t="s">
         <v>1068</v>
@@ -30017,7 +30007,7 @@
     </row>
     <row r="120" customFormat="false" ht="16.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A120" s="58" t="s">
-        <v>1165</v>
+        <v>1166</v>
       </c>
       <c r="B120" s="59" t="n">
         <v>8</v>
@@ -30044,7 +30034,7 @@
     </row>
     <row r="121" customFormat="false" ht="16.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A121" s="58" t="s">
-        <v>1165</v>
+        <v>1166</v>
       </c>
       <c r="B121" s="59" t="n">
         <v>9</v>
@@ -30071,7 +30061,7 @@
     </row>
     <row r="122" customFormat="false" ht="16.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A122" s="58" t="s">
-        <v>1165</v>
+        <v>1166</v>
       </c>
       <c r="B122" s="59" t="n">
         <v>10</v>
@@ -30083,7 +30073,7 @@
         <v>361</v>
       </c>
       <c r="E122" s="60" t="s">
-        <v>1173</v>
+        <v>1174</v>
       </c>
       <c r="F122" s="60" t="s">
         <v>360</v>
@@ -30098,7 +30088,7 @@
     </row>
     <row r="123" customFormat="false" ht="16.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A123" s="58" t="s">
-        <v>1165</v>
+        <v>1166</v>
       </c>
       <c r="B123" s="59" t="n">
         <v>11</v>
@@ -30125,7 +30115,7 @@
     </row>
     <row r="124" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A124" s="58" t="s">
-        <v>1165</v>
+        <v>1166</v>
       </c>
       <c r="B124" s="59" t="n">
         <v>12</v>
@@ -30134,7 +30124,7 @@
         <v>369</v>
       </c>
       <c r="D124" s="61" t="s">
-        <v>1174</v>
+        <v>1175</v>
       </c>
       <c r="E124" s="60" t="s">
         <v>1068</v>
@@ -30152,7 +30142,7 @@
     </row>
     <row r="125" customFormat="false" ht="43.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A125" s="58" t="s">
-        <v>1165</v>
+        <v>1166</v>
       </c>
       <c r="B125" s="59" t="n">
         <v>13</v>
@@ -30164,7 +30154,7 @@
         <v>361</v>
       </c>
       <c r="E125" s="60" t="s">
-        <v>1125</v>
+        <v>1158</v>
       </c>
       <c r="F125" s="60" t="s">
         <v>360</v>
@@ -30176,12 +30166,12 @@
         <v>191</v>
       </c>
       <c r="I125" s="61" t="s">
-        <v>1175</v>
+        <v>1176</v>
       </c>
     </row>
     <row r="126" customFormat="false" ht="43.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A126" s="58" t="s">
-        <v>1165</v>
+        <v>1166</v>
       </c>
       <c r="B126" s="59" t="n">
         <v>14</v>
@@ -30193,7 +30183,7 @@
         <v>363</v>
       </c>
       <c r="E126" s="60" t="s">
-        <v>1125</v>
+        <v>1158</v>
       </c>
       <c r="F126" s="60" t="s">
         <v>360</v>
@@ -30205,12 +30195,12 @@
         <v>192</v>
       </c>
       <c r="I126" s="61" t="s">
-        <v>1175</v>
+        <v>1176</v>
       </c>
     </row>
     <row r="127" customFormat="false" ht="43.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A127" s="58" t="s">
-        <v>1165</v>
+        <v>1166</v>
       </c>
       <c r="B127" s="59" t="n">
         <v>15</v>
@@ -30219,7 +30209,7 @@
         <v>1001</v>
       </c>
       <c r="D127" s="61" t="s">
-        <v>1176</v>
+        <v>1177</v>
       </c>
       <c r="E127" s="60" t="s">
         <v>1125</v>
@@ -30237,7 +30227,7 @@
     </row>
     <row r="128" customFormat="false" ht="16.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A128" s="58" t="s">
-        <v>1177</v>
+        <v>1178</v>
       </c>
       <c r="B128" s="59" t="n">
         <v>1</v>
@@ -30264,7 +30254,7 @@
     </row>
     <row r="129" customFormat="false" ht="16.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A129" s="58" t="s">
-        <v>1177</v>
+        <v>1178</v>
       </c>
       <c r="B129" s="59" t="n">
         <v>2</v>
@@ -30291,7 +30281,7 @@
     </row>
     <row r="130" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A130" s="58" t="s">
-        <v>1177</v>
+        <v>1178</v>
       </c>
       <c r="B130" s="59" t="n">
         <v>3</v>
@@ -30300,10 +30290,10 @@
         <v>1027</v>
       </c>
       <c r="D130" s="61" t="s">
-        <v>1178</v>
+        <v>1179</v>
       </c>
       <c r="E130" s="60" t="s">
-        <v>1083</v>
+        <v>1158</v>
       </c>
       <c r="F130" s="60" t="s">
         <v>313</v>
@@ -30318,7 +30308,7 @@
     </row>
     <row r="131" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A131" s="58" t="s">
-        <v>1177</v>
+        <v>1178</v>
       </c>
       <c r="B131" s="59" t="n">
         <v>5</v>
@@ -30327,10 +30317,10 @@
         <v>313</v>
       </c>
       <c r="D131" s="61" t="s">
-        <v>1178</v>
+        <v>1179</v>
       </c>
       <c r="E131" s="60" t="s">
-        <v>1125</v>
+        <v>1068</v>
       </c>
       <c r="F131" s="60" t="s">
         <v>313</v>
@@ -30345,7 +30335,7 @@
     </row>
     <row r="132" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A132" s="58" t="s">
-        <v>1177</v>
+        <v>1178</v>
       </c>
       <c r="B132" s="59" t="n">
         <v>6</v>
@@ -30354,7 +30344,7 @@
         <v>1029</v>
       </c>
       <c r="D132" s="61" t="s">
-        <v>1179</v>
+        <v>1180</v>
       </c>
       <c r="E132" s="60" t="s">
         <v>1083</v>
@@ -30372,7 +30362,7 @@
     </row>
     <row r="133" customFormat="false" ht="16.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A133" s="58" t="s">
-        <v>1177</v>
+        <v>1178</v>
       </c>
       <c r="B133" s="59" t="n">
         <v>7</v>
@@ -30399,7 +30389,7 @@
     </row>
     <row r="134" customFormat="false" ht="16.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A134" s="58" t="s">
-        <v>1177</v>
+        <v>1178</v>
       </c>
       <c r="B134" s="59" t="n">
         <v>8</v>
@@ -30408,10 +30398,10 @@
         <v>784</v>
       </c>
       <c r="D134" s="61" t="s">
-        <v>1180</v>
+        <v>1181</v>
       </c>
       <c r="E134" s="60" t="s">
-        <v>1125</v>
+        <v>1182</v>
       </c>
       <c r="F134" s="60" t="s">
         <v>784</v>
@@ -30426,7 +30416,7 @@
     </row>
     <row r="135" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A135" s="58" t="s">
-        <v>1177</v>
+        <v>1178</v>
       </c>
       <c r="B135" s="59" t="n">
         <v>9</v>
@@ -30435,7 +30425,7 @@
         <v>963</v>
       </c>
       <c r="D135" s="61" t="s">
-        <v>1181</v>
+        <v>1183</v>
       </c>
       <c r="E135" s="60" t="s">
         <v>1083</v>
@@ -30453,7 +30443,7 @@
     </row>
     <row r="136" customFormat="false" ht="16.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A136" s="58" t="s">
-        <v>1177</v>
+        <v>1178</v>
       </c>
       <c r="B136" s="59" t="n">
         <v>10</v>
@@ -30480,7 +30470,7 @@
     </row>
     <row r="137" customFormat="false" ht="16.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A137" s="58" t="s">
-        <v>1177</v>
+        <v>1178</v>
       </c>
       <c r="B137" s="59" t="n">
         <v>11</v>
@@ -30489,7 +30479,7 @@
         <v>893</v>
       </c>
       <c r="D137" s="62" t="s">
-        <v>1182</v>
+        <v>1184</v>
       </c>
       <c r="E137" s="60" t="s">
         <v>17</v>
@@ -30498,7 +30488,7 @@
         <v>893</v>
       </c>
       <c r="G137" s="62" t="s">
-        <v>1182</v>
+        <v>1184</v>
       </c>
       <c r="H137" s="59" t="n">
         <v>441</v>
@@ -30507,7 +30497,7 @@
     </row>
     <row r="138" customFormat="false" ht="16.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A138" s="58" t="s">
-        <v>1177</v>
+        <v>1178</v>
       </c>
       <c r="B138" s="59" t="n">
         <v>12</v>
@@ -30516,10 +30506,10 @@
         <v>535</v>
       </c>
       <c r="D138" s="61" t="s">
-        <v>1183</v>
+        <v>1185</v>
       </c>
       <c r="E138" s="60" t="s">
-        <v>1184</v>
+        <v>1186</v>
       </c>
       <c r="F138" s="60" t="s">
         <v>535</v>
@@ -30534,7 +30524,7 @@
     </row>
     <row r="139" customFormat="false" ht="16.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A139" s="58" t="s">
-        <v>1177</v>
+        <v>1178</v>
       </c>
       <c r="B139" s="59" t="n">
         <v>16</v>
@@ -30561,7 +30551,7 @@
     </row>
     <row r="140" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A140" s="58" t="s">
-        <v>1177</v>
+        <v>1178</v>
       </c>
       <c r="B140" s="59" t="n">
         <v>18</v>
@@ -30570,7 +30560,7 @@
         <v>975</v>
       </c>
       <c r="D140" s="61" t="s">
-        <v>1185</v>
+        <v>1187</v>
       </c>
       <c r="E140" s="60" t="s">
         <v>1083</v>
@@ -30588,7 +30578,7 @@
     </row>
     <row r="141" customFormat="false" ht="16.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A141" s="58" t="s">
-        <v>1177</v>
+        <v>1178</v>
       </c>
       <c r="B141" s="59" t="n">
         <v>19</v>
@@ -30597,7 +30587,7 @@
         <v>605</v>
       </c>
       <c r="D141" s="61" t="s">
-        <v>1186</v>
+        <v>1188</v>
       </c>
       <c r="E141" s="60" t="s">
         <v>17</v>
@@ -30606,7 +30596,7 @@
         <v>605</v>
       </c>
       <c r="G141" s="61" t="s">
-        <v>1186</v>
+        <v>1188</v>
       </c>
       <c r="H141" s="59" t="n">
         <v>310</v>
@@ -30615,7 +30605,7 @@
     </row>
     <row r="142" customFormat="false" ht="16.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A142" s="58" t="s">
-        <v>1177</v>
+        <v>1178</v>
       </c>
       <c r="B142" s="59" t="n">
         <v>20</v>
@@ -30624,7 +30614,7 @@
         <v>1042</v>
       </c>
       <c r="D142" s="61" t="s">
-        <v>1187</v>
+        <v>1189</v>
       </c>
       <c r="E142" s="60" t="s">
         <v>1083</v>
@@ -30642,7 +30632,7 @@
     </row>
     <row r="143" customFormat="false" ht="43.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A143" s="58" t="s">
-        <v>1177</v>
+        <v>1178</v>
       </c>
       <c r="B143" s="59" t="n">
         <v>21</v>
@@ -30651,7 +30641,7 @@
         <v>970</v>
       </c>
       <c r="D143" s="61" t="s">
-        <v>1188</v>
+        <v>1190</v>
       </c>
       <c r="E143" s="60" t="s">
         <v>1083</v>
@@ -30669,7 +30659,7 @@
     </row>
     <row r="144" customFormat="false" ht="16.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A144" s="58" t="s">
-        <v>1177</v>
+        <v>1178</v>
       </c>
       <c r="B144" s="59" t="n">
         <v>22</v>
@@ -30696,7 +30686,7 @@
     </row>
     <row r="145" customFormat="false" ht="16.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A145" s="58" t="s">
-        <v>1177</v>
+        <v>1178</v>
       </c>
       <c r="B145" s="59" t="n">
         <v>23</v>
@@ -30723,7 +30713,7 @@
     </row>
     <row r="146" customFormat="false" ht="16.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A146" s="58" t="s">
-        <v>1177</v>
+        <v>1178</v>
       </c>
       <c r="B146" s="59" t="n">
         <v>24</v>
@@ -30750,7 +30740,7 @@
     </row>
     <row r="147" customFormat="false" ht="16.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A147" s="58" t="s">
-        <v>1177</v>
+        <v>1178</v>
       </c>
       <c r="B147" s="59" t="n">
         <v>25</v>
@@ -30759,7 +30749,7 @@
         <v>599</v>
       </c>
       <c r="D147" s="61" t="s">
-        <v>1189</v>
+        <v>1191</v>
       </c>
       <c r="E147" s="60" t="s">
         <v>17</v>
@@ -30768,7 +30758,7 @@
         <v>599</v>
       </c>
       <c r="G147" s="61" t="s">
-        <v>1189</v>
+        <v>1191</v>
       </c>
       <c r="H147" s="59" t="n">
         <v>307</v>
@@ -30777,7 +30767,7 @@
     </row>
     <row r="148" customFormat="false" ht="16.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A148" s="58" t="s">
-        <v>1177</v>
+        <v>1178</v>
       </c>
       <c r="B148" s="59" t="n">
         <v>26</v>
@@ -30804,7 +30794,7 @@
     </row>
     <row r="149" customFormat="false" ht="16.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A149" s="58" t="s">
-        <v>1177</v>
+        <v>1178</v>
       </c>
       <c r="B149" s="59" t="n">
         <v>27</v>
@@ -30831,7 +30821,7 @@
     </row>
     <row r="150" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A150" s="58" t="s">
-        <v>1177</v>
+        <v>1178</v>
       </c>
       <c r="B150" s="59" t="n">
         <v>31</v>
@@ -30840,10 +30830,10 @@
         <v>915</v>
       </c>
       <c r="D150" s="61" t="s">
-        <v>1190</v>
+        <v>1192</v>
       </c>
       <c r="E150" s="60" t="s">
-        <v>1184</v>
+        <v>1186</v>
       </c>
       <c r="F150" s="60" t="s">
         <v>915</v>
@@ -30858,7 +30848,7 @@
     </row>
     <row r="151" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A151" s="58" t="s">
-        <v>1177</v>
+        <v>1178</v>
       </c>
       <c r="B151" s="59" t="n">
         <v>32</v>
@@ -30867,10 +30857,10 @@
         <v>1030</v>
       </c>
       <c r="D151" s="61" t="s">
-        <v>1179</v>
+        <v>1180</v>
       </c>
       <c r="E151" s="60" t="s">
-        <v>1125</v>
+        <v>1158</v>
       </c>
       <c r="F151" s="60" t="s">
         <v>313</v>
@@ -30885,7 +30875,7 @@
     </row>
     <row r="152" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A152" s="58" t="s">
-        <v>1177</v>
+        <v>1178</v>
       </c>
       <c r="B152" s="59" t="n">
         <v>33</v>
@@ -30894,10 +30884,10 @@
         <v>1031</v>
       </c>
       <c r="D152" s="61" t="s">
-        <v>1179</v>
+        <v>1180</v>
       </c>
       <c r="E152" s="60" t="s">
-        <v>1125</v>
+        <v>1158</v>
       </c>
       <c r="F152" s="60" t="s">
         <v>313</v>
@@ -30912,7 +30902,7 @@
     </row>
     <row r="153" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A153" s="58" t="s">
-        <v>1177</v>
+        <v>1178</v>
       </c>
       <c r="B153" s="59" t="n">
         <v>34</v>
@@ -30921,7 +30911,7 @@
         <v>1052</v>
       </c>
       <c r="D153" s="61" t="s">
-        <v>1191</v>
+        <v>1193</v>
       </c>
       <c r="E153" s="60" t="s">
         <v>1083</v>
@@ -30939,7 +30929,7 @@
     </row>
     <row r="154" customFormat="false" ht="16.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A154" s="58" t="s">
-        <v>1177</v>
+        <v>1178</v>
       </c>
       <c r="B154" s="59" t="n">
         <v>35</v>
@@ -30966,7 +30956,7 @@
     </row>
     <row r="155" customFormat="false" ht="16.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A155" s="58" t="s">
-        <v>1177</v>
+        <v>1178</v>
       </c>
       <c r="B155" s="59" t="n">
         <v>38</v>
@@ -30993,7 +30983,7 @@
     </row>
     <row r="156" customFormat="false" ht="16.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A156" s="58" t="s">
-        <v>1177</v>
+        <v>1178</v>
       </c>
       <c r="B156" s="59" t="n">
         <v>41</v>
@@ -31002,10 +30992,10 @@
         <v>488</v>
       </c>
       <c r="D156" s="61" t="s">
-        <v>1192</v>
+        <v>1194</v>
       </c>
       <c r="E156" s="60" t="s">
-        <v>1184</v>
+        <v>1186</v>
       </c>
       <c r="F156" s="60" t="s">
         <v>488</v>
@@ -31020,7 +31010,7 @@
     </row>
     <row r="157" customFormat="false" ht="43.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A157" s="58" t="s">
-        <v>1177</v>
+        <v>1178</v>
       </c>
       <c r="B157" s="59" t="n">
         <v>42</v>
@@ -31029,7 +31019,7 @@
         <v>993</v>
       </c>
       <c r="D157" s="61" t="s">
-        <v>1193</v>
+        <v>1195</v>
       </c>
       <c r="E157" s="60" t="s">
         <v>1125</v>
@@ -31047,7 +31037,7 @@
     </row>
     <row r="158" customFormat="false" ht="16.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A158" s="58" t="s">
-        <v>1177</v>
+        <v>1178</v>
       </c>
       <c r="B158" s="59" t="n">
         <v>43</v>
@@ -31074,7 +31064,7 @@
     </row>
     <row r="159" customFormat="false" ht="16.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A159" s="58" t="s">
-        <v>1177</v>
+        <v>1178</v>
       </c>
       <c r="B159" s="59" t="n">
         <v>44</v>
@@ -31101,7 +31091,7 @@
     </row>
     <row r="160" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A160" s="58" t="s">
-        <v>1177</v>
+        <v>1178</v>
       </c>
       <c r="B160" s="59" t="n">
         <v>45</v>
@@ -31110,7 +31100,7 @@
         <v>987</v>
       </c>
       <c r="D160" s="61" t="s">
-        <v>1194</v>
+        <v>1196</v>
       </c>
       <c r="E160" s="60" t="s">
         <v>1083</v>
@@ -31128,7 +31118,7 @@
     </row>
     <row r="161" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A161" s="58" t="s">
-        <v>1177</v>
+        <v>1178</v>
       </c>
       <c r="B161" s="59" t="n">
         <v>46</v>
@@ -31140,7 +31130,7 @@
         <v>77</v>
       </c>
       <c r="E161" s="60" t="s">
-        <v>1195</v>
+        <v>1197</v>
       </c>
       <c r="F161" s="60" t="s">
         <v>73</v>
@@ -31155,7 +31145,7 @@
     </row>
     <row r="162" customFormat="false" ht="16.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A162" s="58" t="s">
-        <v>1177</v>
+        <v>1178</v>
       </c>
       <c r="B162" s="59" t="n">
         <v>47</v>
@@ -31182,7 +31172,7 @@
     </row>
     <row r="163" customFormat="false" ht="16.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A163" s="58" t="s">
-        <v>1177</v>
+        <v>1178</v>
       </c>
       <c r="B163" s="59" t="n">
         <v>48</v>
@@ -31209,7 +31199,7 @@
     </row>
     <row r="164" customFormat="false" ht="16.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A164" s="58" t="s">
-        <v>1177</v>
+        <v>1178</v>
       </c>
       <c r="B164" s="59" t="n">
         <v>49</v>
@@ -31236,7 +31226,7 @@
     </row>
     <row r="165" customFormat="false" ht="16.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A165" s="58" t="s">
-        <v>1177</v>
+        <v>1178</v>
       </c>
       <c r="B165" s="59" t="n">
         <v>50</v>
@@ -31263,7 +31253,7 @@
     </row>
     <row r="166" customFormat="false" ht="16.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A166" s="58" t="s">
-        <v>1177</v>
+        <v>1178</v>
       </c>
       <c r="B166" s="59" t="n">
         <v>51</v>
@@ -31290,7 +31280,7 @@
     </row>
     <row r="167" customFormat="false" ht="16.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A167" s="58" t="s">
-        <v>1177</v>
+        <v>1178</v>
       </c>
       <c r="B167" s="59" t="n">
         <v>52</v>
@@ -31317,7 +31307,7 @@
     </row>
     <row r="168" customFormat="false" ht="16.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A168" s="58" t="s">
-        <v>1177</v>
+        <v>1178</v>
       </c>
       <c r="B168" s="59" t="n">
         <v>53</v>
@@ -31344,7 +31334,7 @@
     </row>
     <row r="169" customFormat="false" ht="16.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A169" s="58" t="s">
-        <v>1177</v>
+        <v>1178</v>
       </c>
       <c r="B169" s="59" t="n">
         <v>54</v>
@@ -31371,7 +31361,7 @@
     </row>
     <row r="170" customFormat="false" ht="16.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A170" s="58" t="s">
-        <v>1177</v>
+        <v>1178</v>
       </c>
       <c r="B170" s="59" t="n">
         <v>55</v>
@@ -31398,7 +31388,7 @@
     </row>
     <row r="171" customFormat="false" ht="16.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A171" s="58" t="s">
-        <v>1177</v>
+        <v>1178</v>
       </c>
       <c r="B171" s="59" t="n">
         <v>56</v>
@@ -31425,7 +31415,7 @@
     </row>
     <row r="172" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A172" s="58" t="s">
-        <v>1177</v>
+        <v>1178</v>
       </c>
       <c r="B172" s="59" t="n">
         <v>57</v>
@@ -31434,7 +31424,7 @@
         <v>978</v>
       </c>
       <c r="D172" s="61" t="s">
-        <v>1196</v>
+        <v>1198</v>
       </c>
       <c r="E172" s="60" t="s">
         <v>1083</v>
@@ -31452,7 +31442,7 @@
     </row>
     <row r="173" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A173" s="58" t="s">
-        <v>1177</v>
+        <v>1178</v>
       </c>
       <c r="B173" s="59" t="n">
         <v>58</v>
@@ -31461,7 +31451,7 @@
         <v>978</v>
       </c>
       <c r="D173" s="61" t="s">
-        <v>1197</v>
+        <v>1199</v>
       </c>
       <c r="E173" s="60" t="s">
         <v>1125</v>
@@ -31479,7 +31469,7 @@
     </row>
     <row r="174" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A174" s="58" t="s">
-        <v>1177</v>
+        <v>1178</v>
       </c>
       <c r="B174" s="59" t="n">
         <v>59</v>
@@ -31488,7 +31478,7 @@
         <v>980</v>
       </c>
       <c r="D174" s="61" t="s">
-        <v>1197</v>
+        <v>1199</v>
       </c>
       <c r="E174" s="60" t="s">
         <v>1125</v>
@@ -31506,7 +31496,7 @@
     </row>
     <row r="175" customFormat="false" ht="16.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A175" s="58" t="s">
-        <v>1177</v>
+        <v>1178</v>
       </c>
       <c r="B175" s="59" t="n">
         <v>60</v>
@@ -31515,7 +31505,7 @@
         <v>462</v>
       </c>
       <c r="D175" s="61" t="s">
-        <v>1198</v>
+        <v>1200</v>
       </c>
       <c r="E175" s="60" t="s">
         <v>17</v>
@@ -31524,7 +31514,7 @@
         <v>462</v>
       </c>
       <c r="G175" s="61" t="s">
-        <v>1198</v>
+        <v>1200</v>
       </c>
       <c r="H175" s="59" t="n">
         <v>243</v>
@@ -31533,7 +31523,7 @@
     </row>
     <row r="176" customFormat="false" ht="43.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A176" s="58" t="s">
-        <v>1177</v>
+        <v>1178</v>
       </c>
       <c r="B176" s="59" t="n">
         <v>61</v>
@@ -31542,7 +31532,7 @@
         <v>1015</v>
       </c>
       <c r="D176" s="61" t="s">
-        <v>1199</v>
+        <v>1201</v>
       </c>
       <c r="E176" s="60" t="s">
         <v>1083</v>
@@ -31557,12 +31547,12 @@
         <v>138</v>
       </c>
       <c r="I176" s="61" t="s">
-        <v>1200</v>
+        <v>1202</v>
       </c>
     </row>
     <row r="177" customFormat="false" ht="43.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A177" s="58" t="s">
-        <v>1177</v>
+        <v>1178</v>
       </c>
       <c r="B177" s="59" t="n">
         <v>62</v>
@@ -31571,7 +31561,7 @@
         <v>1015</v>
       </c>
       <c r="D177" s="61" t="s">
-        <v>1201</v>
+        <v>1203</v>
       </c>
       <c r="E177" s="60" t="s">
         <v>1083</v>
@@ -31589,7 +31579,7 @@
     </row>
     <row r="178" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A178" s="58" t="s">
-        <v>1177</v>
+        <v>1178</v>
       </c>
       <c r="B178" s="59" t="n">
         <v>63</v>
@@ -31598,7 +31588,7 @@
         <v>1015</v>
       </c>
       <c r="D178" s="61" t="s">
-        <v>1202</v>
+        <v>1204</v>
       </c>
       <c r="E178" s="60" t="s">
         <v>1083</v>
@@ -31616,7 +31606,7 @@
     </row>
     <row r="179" customFormat="false" ht="16.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A179" s="58" t="s">
-        <v>1177</v>
+        <v>1178</v>
       </c>
       <c r="B179" s="59" t="n">
         <v>64</v>
@@ -31625,10 +31615,10 @@
         <v>1024</v>
       </c>
       <c r="D179" s="61" t="s">
-        <v>1203</v>
+        <v>1205</v>
       </c>
       <c r="E179" s="60" t="s">
-        <v>1083</v>
+        <v>1182</v>
       </c>
       <c r="F179" s="60" t="s">
         <v>301</v>
@@ -31643,7 +31633,7 @@
     </row>
     <row r="180" customFormat="false" ht="16.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A180" s="58" t="s">
-        <v>1177</v>
+        <v>1178</v>
       </c>
       <c r="B180" s="59" t="n">
         <v>65</v>
@@ -31670,7 +31660,7 @@
     </row>
     <row r="181" customFormat="false" ht="16.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A181" s="58" t="s">
-        <v>1177</v>
+        <v>1178</v>
       </c>
       <c r="B181" s="59" t="n">
         <v>66</v>
@@ -31697,7 +31687,7 @@
     </row>
     <row r="182" customFormat="false" ht="16.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A182" s="58" t="s">
-        <v>1177</v>
+        <v>1178</v>
       </c>
       <c r="B182" s="59" t="n">
         <v>68</v>
@@ -31724,7 +31714,7 @@
     </row>
     <row r="183" customFormat="false" ht="16.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A183" s="58" t="s">
-        <v>1177</v>
+        <v>1178</v>
       </c>
       <c r="B183" s="59" t="n">
         <v>69</v>
@@ -31751,7 +31741,7 @@
     </row>
     <row r="184" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A184" s="58" t="s">
-        <v>1177</v>
+        <v>1178</v>
       </c>
       <c r="B184" s="59" t="n">
         <v>70</v>
@@ -31760,7 +31750,7 @@
         <v>1045</v>
       </c>
       <c r="D184" s="61" t="s">
-        <v>1204</v>
+        <v>1206</v>
       </c>
       <c r="E184" s="60" t="s">
         <v>1083</v>
@@ -31778,7 +31768,7 @@
     </row>
     <row r="185" customFormat="false" ht="16.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A185" s="58" t="s">
-        <v>1177</v>
+        <v>1178</v>
       </c>
       <c r="B185" s="59" t="n">
         <v>71</v>
@@ -31805,7 +31795,7 @@
     </row>
     <row r="186" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A186" s="58" t="s">
-        <v>1177</v>
+        <v>1178</v>
       </c>
       <c r="B186" s="59" t="n">
         <v>72</v>
@@ -31814,10 +31804,10 @@
         <v>504</v>
       </c>
       <c r="D186" s="61" t="s">
-        <v>1205</v>
+        <v>1207</v>
       </c>
       <c r="E186" s="60" t="s">
-        <v>1184</v>
+        <v>1186</v>
       </c>
       <c r="F186" s="60" t="s">
         <v>504</v>
@@ -31832,7 +31822,7 @@
     </row>
     <row r="187" customFormat="false" ht="16.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A187" s="58" t="s">
-        <v>1177</v>
+        <v>1178</v>
       </c>
       <c r="B187" s="59" t="n">
         <v>73</v>
@@ -31859,7 +31849,7 @@
     </row>
     <row r="188" customFormat="false" ht="16.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A188" s="58" t="s">
-        <v>1177</v>
+        <v>1178</v>
       </c>
       <c r="B188" s="59" t="n">
         <v>74</v>
@@ -31886,7 +31876,7 @@
     </row>
     <row r="189" customFormat="false" ht="43.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A189" s="58" t="s">
-        <v>1177</v>
+        <v>1178</v>
       </c>
       <c r="B189" s="59" t="n">
         <v>75</v>
@@ -31913,7 +31903,7 @@
     </row>
     <row r="190" customFormat="false" ht="16.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A190" s="58" t="s">
-        <v>1177</v>
+        <v>1178</v>
       </c>
       <c r="B190" s="59" t="n">
         <v>76</v>
@@ -31922,10 +31912,10 @@
         <v>499</v>
       </c>
       <c r="D190" s="61" t="s">
-        <v>1206</v>
+        <v>1208</v>
       </c>
       <c r="E190" s="60" t="s">
-        <v>1125</v>
+        <v>1182</v>
       </c>
       <c r="F190" s="60" t="s">
         <v>499</v>
@@ -31940,7 +31930,7 @@
     </row>
     <row r="191" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A191" s="58" t="s">
-        <v>1177</v>
+        <v>1178</v>
       </c>
       <c r="B191" s="59" t="n">
         <v>77</v>
@@ -31949,10 +31939,10 @@
         <v>499</v>
       </c>
       <c r="D191" s="61" t="s">
-        <v>1207</v>
+        <v>1209</v>
       </c>
       <c r="E191" s="60" t="s">
-        <v>1184</v>
+        <v>1186</v>
       </c>
       <c r="F191" s="60" t="s">
         <v>499</v>
@@ -31967,7 +31957,7 @@
     </row>
     <row r="192" customFormat="false" ht="43.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A192" s="58" t="s">
-        <v>1177</v>
+        <v>1178</v>
       </c>
       <c r="B192" s="59" t="n">
         <v>78</v>
@@ -31976,7 +31966,7 @@
         <v>382</v>
       </c>
       <c r="D192" s="61" t="s">
-        <v>1208</v>
+        <v>1210</v>
       </c>
       <c r="E192" s="60" t="s">
         <v>1068</v>
@@ -31994,7 +31984,7 @@
     </row>
     <row r="193" customFormat="false" ht="43.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A193" s="58" t="s">
-        <v>1177</v>
+        <v>1178</v>
       </c>
       <c r="B193" s="59" t="n">
         <v>79</v>
@@ -32021,7 +32011,7 @@
     </row>
     <row r="194" customFormat="false" ht="43.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A194" s="58" t="s">
-        <v>1177</v>
+        <v>1178</v>
       </c>
       <c r="B194" s="59" t="n">
         <v>80</v>
@@ -32030,7 +32020,7 @@
         <v>382</v>
       </c>
       <c r="D194" s="61" t="s">
-        <v>1209</v>
+        <v>1211</v>
       </c>
       <c r="E194" s="60" t="s">
         <v>1068</v>
@@ -32048,7 +32038,7 @@
     </row>
     <row r="195" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A195" s="58" t="s">
-        <v>1177</v>
+        <v>1178</v>
       </c>
       <c r="B195" s="59" t="n">
         <v>81</v>
@@ -32057,7 +32047,7 @@
         <v>382</v>
       </c>
       <c r="D195" s="61" t="s">
-        <v>1210</v>
+        <v>1212</v>
       </c>
       <c r="E195" s="60" t="s">
         <v>1068</v>
@@ -32075,7 +32065,7 @@
     </row>
     <row r="196" customFormat="false" ht="43.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A196" s="58" t="s">
-        <v>1177</v>
+        <v>1178</v>
       </c>
       <c r="B196" s="59" t="n">
         <v>82</v>
@@ -32084,7 +32074,7 @@
         <v>382</v>
       </c>
       <c r="D196" s="61" t="s">
-        <v>1211</v>
+        <v>1213</v>
       </c>
       <c r="E196" s="60" t="s">
         <v>1068</v>
@@ -32102,7 +32092,7 @@
     </row>
     <row r="197" customFormat="false" ht="57" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A197" s="58" t="s">
-        <v>1177</v>
+        <v>1178</v>
       </c>
       <c r="B197" s="59" t="n">
         <v>83</v>
@@ -32111,7 +32101,7 @@
         <v>382</v>
       </c>
       <c r="D197" s="61" t="s">
-        <v>1212</v>
+        <v>1214</v>
       </c>
       <c r="E197" s="60" t="s">
         <v>1068</v>
@@ -32129,7 +32119,7 @@
     </row>
     <row r="198" customFormat="false" ht="57" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A198" s="58" t="s">
-        <v>1177</v>
+        <v>1178</v>
       </c>
       <c r="B198" s="59" t="n">
         <v>84</v>
@@ -32138,10 +32128,10 @@
         <v>382</v>
       </c>
       <c r="D198" s="61" t="s">
-        <v>1212</v>
+        <v>1214</v>
       </c>
       <c r="E198" s="60" t="s">
-        <v>1173</v>
+        <v>1174</v>
       </c>
       <c r="F198" s="60" t="s">
         <v>382</v>
@@ -32156,7 +32146,7 @@
     </row>
     <row r="199" customFormat="false" ht="16.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A199" s="58" t="s">
-        <v>1177</v>
+        <v>1178</v>
       </c>
       <c r="B199" s="59" t="n">
         <v>85</v>
@@ -32183,7 +32173,7 @@
     </row>
     <row r="200" customFormat="false" ht="16.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A200" s="58" t="s">
-        <v>1177</v>
+        <v>1178</v>
       </c>
       <c r="B200" s="59" t="n">
         <v>86</v>
@@ -32210,7 +32200,7 @@
     </row>
     <row r="201" customFormat="false" ht="16.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A201" s="58" t="s">
-        <v>1177</v>
+        <v>1178</v>
       </c>
       <c r="B201" s="59" t="n">
         <v>89</v>
@@ -32237,7 +32227,7 @@
     </row>
     <row r="202" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A202" s="58" t="s">
-        <v>1177</v>
+        <v>1178</v>
       </c>
       <c r="B202" s="59" t="n">
         <v>90</v>
@@ -32246,10 +32236,10 @@
         <v>911</v>
       </c>
       <c r="D202" s="61" t="s">
-        <v>1213</v>
+        <v>1215</v>
       </c>
       <c r="E202" s="60" t="s">
-        <v>1184</v>
+        <v>1186</v>
       </c>
       <c r="F202" s="60" t="s">
         <v>911</v>
@@ -32264,7 +32254,7 @@
     </row>
     <row r="203" customFormat="false" ht="16.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A203" s="58" t="s">
-        <v>1177</v>
+        <v>1178</v>
       </c>
       <c r="B203" s="59" t="n">
         <v>91</v>
@@ -32291,7 +32281,7 @@
     </row>
     <row r="204" customFormat="false" ht="16.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A204" s="58" t="s">
-        <v>1177</v>
+        <v>1178</v>
       </c>
       <c r="B204" s="59" t="n">
         <v>92</v>
@@ -32318,7 +32308,7 @@
     </row>
     <row r="205" customFormat="false" ht="16.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A205" s="58" t="s">
-        <v>1177</v>
+        <v>1178</v>
       </c>
       <c r="B205" s="59" t="n">
         <v>93</v>
@@ -32345,7 +32335,7 @@
     </row>
     <row r="206" customFormat="false" ht="16.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A206" s="58" t="s">
-        <v>1177</v>
+        <v>1178</v>
       </c>
       <c r="B206" s="59" t="n">
         <v>94</v>
@@ -32372,7 +32362,7 @@
     </row>
     <row r="207" customFormat="false" ht="16.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A207" s="58" t="s">
-        <v>1177</v>
+        <v>1178</v>
       </c>
       <c r="B207" s="59" t="n">
         <v>95</v>
@@ -32399,7 +32389,7 @@
     </row>
     <row r="208" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A208" s="58" t="s">
-        <v>1177</v>
+        <v>1178</v>
       </c>
       <c r="B208" s="59" t="n">
         <v>97</v>
@@ -32408,7 +32398,7 @@
         <v>972</v>
       </c>
       <c r="D208" s="61" t="s">
-        <v>1214</v>
+        <v>1216</v>
       </c>
       <c r="E208" s="60" t="s">
         <v>1083</v>
@@ -32426,7 +32416,7 @@
     </row>
     <row r="209" customFormat="false" ht="16.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A209" s="58" t="s">
-        <v>1177</v>
+        <v>1178</v>
       </c>
       <c r="B209" s="59" t="n">
         <v>98</v>
@@ -32453,7 +32443,7 @@
     </row>
     <row r="210" customFormat="false" ht="16.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A210" s="58" t="s">
-        <v>1177</v>
+        <v>1178</v>
       </c>
       <c r="B210" s="59" t="n">
         <v>99</v>
@@ -32480,7 +32470,7 @@
     </row>
     <row r="211" customFormat="false" ht="16.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A211" s="58" t="s">
-        <v>1177</v>
+        <v>1178</v>
       </c>
       <c r="B211" s="59" t="n">
         <v>101</v>
@@ -32489,10 +32479,10 @@
         <v>874</v>
       </c>
       <c r="D211" s="62" t="s">
-        <v>1215</v>
+        <v>1217</v>
       </c>
       <c r="E211" s="60" t="s">
-        <v>1184</v>
+        <v>1186</v>
       </c>
       <c r="F211" s="60" t="s">
         <v>874</v>
@@ -32507,7 +32497,7 @@
     </row>
     <row r="212" customFormat="false" ht="16.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A212" s="58" t="s">
-        <v>1177</v>
+        <v>1178</v>
       </c>
       <c r="B212" s="59" t="n">
         <v>102</v>
@@ -32516,7 +32506,7 @@
         <v>1026</v>
       </c>
       <c r="D212" s="61" t="s">
-        <v>1216</v>
+        <v>1218</v>
       </c>
       <c r="E212" s="60" t="s">
         <v>1083</v>
@@ -32534,7 +32524,7 @@
     </row>
     <row r="213" customFormat="false" ht="16.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A213" s="58" t="s">
-        <v>1177</v>
+        <v>1178</v>
       </c>
       <c r="B213" s="59" t="n">
         <v>103</v>
@@ -32543,10 +32533,10 @@
         <v>551</v>
       </c>
       <c r="D213" s="61" t="s">
-        <v>1217</v>
+        <v>1219</v>
       </c>
       <c r="E213" s="60" t="s">
-        <v>1184</v>
+        <v>1186</v>
       </c>
       <c r="F213" s="60" t="s">
         <v>551</v>
@@ -32561,7 +32551,7 @@
     </row>
     <row r="214" customFormat="false" ht="16.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A214" s="58" t="s">
-        <v>1177</v>
+        <v>1178</v>
       </c>
       <c r="B214" s="59" t="n">
         <v>104</v>
@@ -32570,7 +32560,7 @@
         <v>1032</v>
       </c>
       <c r="D214" s="61" t="s">
-        <v>1218</v>
+        <v>1220</v>
       </c>
       <c r="E214" s="60" t="s">
         <v>1083</v>
@@ -32588,7 +32578,7 @@
     </row>
     <row r="215" customFormat="false" ht="16.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A215" s="58" t="s">
-        <v>1177</v>
+        <v>1178</v>
       </c>
       <c r="B215" s="59" t="n">
         <v>105</v>
@@ -32597,7 +32587,7 @@
         <v>891</v>
       </c>
       <c r="D215" s="62" t="s">
-        <v>1219</v>
+        <v>1221</v>
       </c>
       <c r="E215" s="60" t="s">
         <v>17</v>
@@ -32606,7 +32596,7 @@
         <v>891</v>
       </c>
       <c r="G215" s="62" t="s">
-        <v>1219</v>
+        <v>1221</v>
       </c>
       <c r="H215" s="59" t="n">
         <v>440</v>
@@ -32615,7 +32605,7 @@
     </row>
     <row r="216" customFormat="false" ht="16.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A216" s="58" t="s">
-        <v>1177</v>
+        <v>1178</v>
       </c>
       <c r="B216" s="59" t="n">
         <v>106</v>
@@ -32642,7 +32632,7 @@
     </row>
     <row r="217" customFormat="false" ht="16.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A217" s="58" t="s">
-        <v>1177</v>
+        <v>1178</v>
       </c>
       <c r="B217" s="59" t="n">
         <v>109</v>
@@ -32651,10 +32641,10 @@
         <v>705</v>
       </c>
       <c r="D217" s="61" t="s">
-        <v>1220</v>
+        <v>1222</v>
       </c>
       <c r="E217" s="60" t="s">
-        <v>1184</v>
+        <v>1182</v>
       </c>
       <c r="F217" s="60" t="s">
         <v>705</v>
@@ -32669,7 +32659,7 @@
     </row>
     <row r="218" customFormat="false" ht="16.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A218" s="58" t="s">
-        <v>1177</v>
+        <v>1178</v>
       </c>
       <c r="B218" s="59" t="n">
         <v>110</v>
@@ -32681,7 +32671,7 @@
         <v>699</v>
       </c>
       <c r="E218" s="60" t="s">
-        <v>1125</v>
+        <v>17</v>
       </c>
       <c r="F218" s="60" t="s">
         <v>705</v>
@@ -32696,7 +32686,7 @@
     </row>
     <row r="219" customFormat="false" ht="16.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A219" s="58" t="s">
-        <v>1177</v>
+        <v>1178</v>
       </c>
       <c r="B219" s="59" t="n">
         <v>111</v>
@@ -32723,7 +32713,7 @@
     </row>
     <row r="220" customFormat="false" ht="16.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A220" s="58" t="s">
-        <v>1177</v>
+        <v>1178</v>
       </c>
       <c r="B220" s="59" t="n">
         <v>112</v>
@@ -32732,10 +32722,10 @@
         <v>703</v>
       </c>
       <c r="D220" s="61" t="s">
-        <v>1220</v>
+        <v>1222</v>
       </c>
       <c r="E220" s="60" t="s">
-        <v>1184</v>
+        <v>1186</v>
       </c>
       <c r="F220" s="60" t="s">
         <v>703</v>
@@ -32750,7 +32740,7 @@
     </row>
     <row r="221" customFormat="false" ht="16.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A221" s="58" t="s">
-        <v>1177</v>
+        <v>1178</v>
       </c>
       <c r="B221" s="59" t="n">
         <v>113</v>
@@ -32759,10 +32749,10 @@
         <v>698</v>
       </c>
       <c r="D221" s="61" t="s">
-        <v>1220</v>
+        <v>1222</v>
       </c>
       <c r="E221" s="60" t="s">
-        <v>1184</v>
+        <v>1186</v>
       </c>
       <c r="F221" s="60" t="s">
         <v>698</v>
@@ -32777,7 +32767,7 @@
     </row>
     <row r="222" customFormat="false" ht="16.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A222" s="58" t="s">
-        <v>1177</v>
+        <v>1178</v>
       </c>
       <c r="B222" s="59" t="n">
         <v>116</v>
@@ -32804,7 +32794,7 @@
     </row>
     <row r="223" customFormat="false" ht="16.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A223" s="58" t="s">
-        <v>1177</v>
+        <v>1178</v>
       </c>
       <c r="B223" s="59" t="n">
         <v>117</v>
@@ -32831,7 +32821,7 @@
     </row>
     <row r="224" customFormat="false" ht="16.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A224" s="58" t="s">
-        <v>1177</v>
+        <v>1178</v>
       </c>
       <c r="B224" s="59" t="n">
         <v>118</v>
@@ -32858,7 +32848,7 @@
     </row>
     <row r="225" customFormat="false" ht="16.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A225" s="58" t="s">
-        <v>1177</v>
+        <v>1178</v>
       </c>
       <c r="B225" s="59" t="n">
         <v>119</v>
@@ -32885,7 +32875,7 @@
     </row>
     <row r="226" customFormat="false" ht="16.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A226" s="58" t="s">
-        <v>1177</v>
+        <v>1178</v>
       </c>
       <c r="B226" s="59" t="n">
         <v>120</v>
@@ -32912,7 +32902,7 @@
     </row>
     <row r="227" customFormat="false" ht="16.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A227" s="58" t="s">
-        <v>1177</v>
+        <v>1178</v>
       </c>
       <c r="B227" s="59" t="n">
         <v>121</v>
@@ -32939,7 +32929,7 @@
     </row>
     <row r="228" customFormat="false" ht="16.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A228" s="58" t="s">
-        <v>1177</v>
+        <v>1178</v>
       </c>
       <c r="B228" s="59" t="n">
         <v>122</v>
@@ -32966,7 +32956,7 @@
     </row>
     <row r="229" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A229" s="58" t="s">
-        <v>1177</v>
+        <v>1178</v>
       </c>
       <c r="B229" s="59" t="n">
         <v>124</v>
@@ -32975,7 +32965,7 @@
         <v>326</v>
       </c>
       <c r="D229" s="61" t="s">
-        <v>1221</v>
+        <v>1223</v>
       </c>
       <c r="E229" s="60" t="s">
         <v>1068</v>
@@ -32993,7 +32983,7 @@
     </row>
     <row r="230" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A230" s="58" t="s">
-        <v>1177</v>
+        <v>1178</v>
       </c>
       <c r="B230" s="59" t="n">
         <v>125</v>
@@ -33002,7 +32992,7 @@
         <v>326</v>
       </c>
       <c r="D230" s="61" t="s">
-        <v>1222</v>
+        <v>1224</v>
       </c>
       <c r="E230" s="60" t="s">
         <v>1068</v>
@@ -33020,7 +33010,7 @@
     </row>
     <row r="231" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A231" s="58" t="s">
-        <v>1177</v>
+        <v>1178</v>
       </c>
       <c r="B231" s="59" t="n">
         <v>126</v>
@@ -33029,7 +33019,7 @@
         <v>326</v>
       </c>
       <c r="D231" s="61" t="s">
-        <v>1223</v>
+        <v>1225</v>
       </c>
       <c r="E231" s="60" t="s">
         <v>1068</v>
@@ -33047,7 +33037,7 @@
     </row>
     <row r="232" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A232" s="58" t="s">
-        <v>1177</v>
+        <v>1178</v>
       </c>
       <c r="B232" s="59" t="n">
         <v>127</v>
@@ -33074,7 +33064,7 @@
     </row>
     <row r="233" customFormat="false" ht="16.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A233" s="58" t="s">
-        <v>1177</v>
+        <v>1178</v>
       </c>
       <c r="B233" s="59" t="n">
         <v>128</v>
@@ -33101,7 +33091,7 @@
     </row>
     <row r="234" customFormat="false" ht="16.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A234" s="58" t="s">
-        <v>1177</v>
+        <v>1178</v>
       </c>
       <c r="B234" s="59" t="n">
         <v>129</v>
@@ -33128,7 +33118,7 @@
     </row>
     <row r="235" customFormat="false" ht="43.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A235" s="58" t="s">
-        <v>1177</v>
+        <v>1178</v>
       </c>
       <c r="B235" s="59" t="n">
         <v>130</v>
@@ -33137,7 +33127,7 @@
         <v>983</v>
       </c>
       <c r="D235" s="61" t="s">
-        <v>1224</v>
+        <v>1226</v>
       </c>
       <c r="E235" s="60" t="s">
         <v>1125</v>
@@ -33155,7 +33145,7 @@
     </row>
     <row r="236" customFormat="false" ht="43.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A236" s="58" t="s">
-        <v>1177</v>
+        <v>1178</v>
       </c>
       <c r="B236" s="59" t="n">
         <v>131</v>
@@ -33164,7 +33154,7 @@
         <v>983</v>
       </c>
       <c r="D236" s="61" t="s">
-        <v>1225</v>
+        <v>1227</v>
       </c>
       <c r="E236" s="60" t="s">
         <v>1125</v>
@@ -33182,7 +33172,7 @@
     </row>
     <row r="237" customFormat="false" ht="16.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A237" s="58" t="s">
-        <v>1177</v>
+        <v>1178</v>
       </c>
       <c r="B237" s="59" t="n">
         <v>132</v>
@@ -33209,7 +33199,7 @@
     </row>
     <row r="238" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A238" s="58" t="s">
-        <v>1177</v>
+        <v>1178</v>
       </c>
       <c r="B238" s="59" t="n">
         <v>133</v>
@@ -33218,7 +33208,7 @@
         <v>1051</v>
       </c>
       <c r="D238" s="61" t="s">
-        <v>1226</v>
+        <v>1228</v>
       </c>
       <c r="E238" s="60" t="s">
         <v>1083</v>
@@ -33236,7 +33226,7 @@
     </row>
     <row r="239" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A239" s="58" t="s">
-        <v>1177</v>
+        <v>1178</v>
       </c>
       <c r="B239" s="59" t="n">
         <v>134</v>
@@ -33245,10 +33235,10 @@
         <v>1049</v>
       </c>
       <c r="D239" s="61" t="s">
-        <v>1227</v>
+        <v>1229</v>
       </c>
       <c r="E239" s="60" t="s">
-        <v>1083</v>
+        <v>1125</v>
       </c>
       <c r="F239" s="60" t="s">
         <v>394</v>
@@ -33263,7 +33253,7 @@
     </row>
     <row r="240" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A240" s="58" t="s">
-        <v>1177</v>
+        <v>1178</v>
       </c>
       <c r="B240" s="59" t="n">
         <v>135</v>
@@ -33272,7 +33262,7 @@
         <v>1049</v>
       </c>
       <c r="D240" s="61" t="s">
-        <v>1228</v>
+        <v>1230</v>
       </c>
       <c r="E240" s="60" t="s">
         <v>1083</v>
@@ -33290,7 +33280,7 @@
     </row>
     <row r="241" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A241" s="58" t="s">
-        <v>1177</v>
+        <v>1178</v>
       </c>
       <c r="B241" s="59" t="n">
         <v>136</v>
@@ -33299,10 +33289,10 @@
         <v>394</v>
       </c>
       <c r="D241" s="61" t="s">
-        <v>1229</v>
+        <v>1231</v>
       </c>
       <c r="E241" s="60" t="s">
-        <v>1125</v>
+        <v>1068</v>
       </c>
       <c r="F241" s="60" t="s">
         <v>394</v>
@@ -33317,7 +33307,7 @@
     </row>
     <row r="242" customFormat="false" ht="16.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A242" s="58" t="s">
-        <v>1177</v>
+        <v>1178</v>
       </c>
       <c r="B242" s="59" t="n">
         <v>138</v>
@@ -33326,10 +33316,10 @@
         <v>766</v>
       </c>
       <c r="D242" s="61" t="s">
-        <v>1230</v>
+        <v>1232</v>
       </c>
       <c r="E242" s="60" t="s">
-        <v>1184</v>
+        <v>1186</v>
       </c>
       <c r="F242" s="60" t="s">
         <v>766</v>
@@ -33344,7 +33334,7 @@
     </row>
     <row r="243" customFormat="false" ht="16.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A243" s="58" t="s">
-        <v>1177</v>
+        <v>1178</v>
       </c>
       <c r="B243" s="59" t="n">
         <v>139</v>
@@ -33371,7 +33361,7 @@
     </row>
     <row r="244" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A244" s="58" t="s">
-        <v>1177</v>
+        <v>1178</v>
       </c>
       <c r="B244" s="59" t="n">
         <v>140</v>
@@ -33380,10 +33370,10 @@
         <v>992</v>
       </c>
       <c r="D244" s="61" t="s">
-        <v>1162</v>
+        <v>1163</v>
       </c>
       <c r="E244" s="60" t="s">
-        <v>1125</v>
+        <v>1158</v>
       </c>
       <c r="F244" s="60" t="s">
         <v>180</v>
@@ -33398,7 +33388,7 @@
     </row>
     <row r="245" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A245" s="58" t="s">
-        <v>1177</v>
+        <v>1178</v>
       </c>
       <c r="B245" s="59" t="n">
         <v>141</v>
@@ -33407,7 +33397,7 @@
         <v>992</v>
       </c>
       <c r="D245" s="61" t="s">
-        <v>1231</v>
+        <v>1233</v>
       </c>
       <c r="E245" s="60" t="s">
         <v>1125</v>
@@ -33425,7 +33415,7 @@
     </row>
     <row r="246" customFormat="false" ht="16.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A246" s="58" t="s">
-        <v>1177</v>
+        <v>1178</v>
       </c>
       <c r="B246" s="59" t="n">
         <v>142</v>
@@ -33437,7 +33427,7 @@
         <v>275</v>
       </c>
       <c r="E246" s="60" t="s">
-        <v>1195</v>
+        <v>1197</v>
       </c>
       <c r="F246" s="60" t="s">
         <v>274</v>
@@ -33452,7 +33442,7 @@
     </row>
     <row r="247" customFormat="false" ht="57" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A247" s="58" t="s">
-        <v>1177</v>
+        <v>1178</v>
       </c>
       <c r="B247" s="59" t="n">
         <v>143</v>
@@ -33461,10 +33451,10 @@
         <v>1018</v>
       </c>
       <c r="D247" s="61" t="s">
-        <v>1232</v>
+        <v>1234</v>
       </c>
       <c r="E247" s="60" t="s">
-        <v>1083</v>
+        <v>1235</v>
       </c>
       <c r="F247" s="60" t="s">
         <v>274</v>
@@ -33476,12 +33466,12 @@
         <v>149</v>
       </c>
       <c r="I247" s="61" t="s">
-        <v>1233</v>
+        <v>1236</v>
       </c>
     </row>
     <row r="248" customFormat="false" ht="57" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A248" s="58" t="s">
-        <v>1177</v>
+        <v>1178</v>
       </c>
       <c r="B248" s="59" t="n">
         <v>144</v>
@@ -33490,7 +33480,7 @@
         <v>1020</v>
       </c>
       <c r="D248" s="61" t="s">
-        <v>1234</v>
+        <v>1237</v>
       </c>
       <c r="E248" s="60" t="s">
         <v>1083</v>
@@ -33505,12 +33495,12 @@
         <v>153</v>
       </c>
       <c r="I248" s="61" t="s">
-        <v>1233</v>
+        <v>1236</v>
       </c>
     </row>
     <row r="249" customFormat="false" ht="57" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A249" s="58" t="s">
-        <v>1177</v>
+        <v>1178</v>
       </c>
       <c r="B249" s="59" t="n">
         <v>145</v>
@@ -33519,7 +33509,7 @@
         <v>1020</v>
       </c>
       <c r="D249" s="61" t="s">
-        <v>1235</v>
+        <v>1238</v>
       </c>
       <c r="E249" s="60" t="s">
         <v>1083</v>
@@ -33534,12 +33524,12 @@
         <v>154</v>
       </c>
       <c r="I249" s="61" t="s">
-        <v>1233</v>
+        <v>1236</v>
       </c>
     </row>
     <row r="250" customFormat="false" ht="43.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A250" s="58" t="s">
-        <v>1177</v>
+        <v>1178</v>
       </c>
       <c r="B250" s="59" t="n">
         <v>146</v>
@@ -33548,7 +33538,7 @@
         <v>415</v>
       </c>
       <c r="D250" s="61" t="s">
-        <v>1236</v>
+        <v>1239</v>
       </c>
       <c r="E250" s="60" t="s">
         <v>1068</v>
@@ -33566,7 +33556,7 @@
     </row>
     <row r="251" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A251" s="58" t="s">
-        <v>1177</v>
+        <v>1178</v>
       </c>
       <c r="B251" s="59" t="n">
         <v>147</v>
@@ -33575,7 +33565,7 @@
         <v>415</v>
       </c>
       <c r="D251" s="61" t="s">
-        <v>1237</v>
+        <v>1240</v>
       </c>
       <c r="E251" s="60" t="s">
         <v>1068</v>
@@ -33593,7 +33583,7 @@
     </row>
     <row r="252" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A252" s="58" t="s">
-        <v>1177</v>
+        <v>1178</v>
       </c>
       <c r="B252" s="59" t="n">
         <v>148</v>
@@ -33602,7 +33592,7 @@
         <v>415</v>
       </c>
       <c r="D252" s="61" t="s">
-        <v>1238</v>
+        <v>1241</v>
       </c>
       <c r="E252" s="60" t="s">
         <v>1068</v>
@@ -33620,7 +33610,7 @@
     </row>
     <row r="253" customFormat="false" ht="43.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A253" s="58" t="s">
-        <v>1177</v>
+        <v>1178</v>
       </c>
       <c r="B253" s="59" t="n">
         <v>149</v>
@@ -33629,7 +33619,7 @@
         <v>415</v>
       </c>
       <c r="D253" s="61" t="s">
-        <v>1239</v>
+        <v>1242</v>
       </c>
       <c r="E253" s="60" t="s">
         <v>1125</v>
@@ -33647,7 +33637,7 @@
     </row>
     <row r="254" customFormat="false" ht="43.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A254" s="58" t="s">
-        <v>1177</v>
+        <v>1178</v>
       </c>
       <c r="B254" s="59" t="n">
         <v>150</v>
@@ -33656,7 +33646,7 @@
         <v>415</v>
       </c>
       <c r="D254" s="61" t="s">
-        <v>1240</v>
+        <v>1243</v>
       </c>
       <c r="E254" s="60" t="s">
         <v>1068</v>
@@ -33674,7 +33664,7 @@
     </row>
     <row r="255" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A255" s="58" t="s">
-        <v>1177</v>
+        <v>1178</v>
       </c>
       <c r="B255" s="59" t="n">
         <v>151</v>
@@ -33683,7 +33673,7 @@
         <v>415</v>
       </c>
       <c r="D255" s="61" t="s">
-        <v>1241</v>
+        <v>1244</v>
       </c>
       <c r="E255" s="60" t="s">
         <v>1125</v>
@@ -33701,7 +33691,7 @@
     </row>
     <row r="256" customFormat="false" ht="16.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A256" s="58" t="s">
-        <v>1177</v>
+        <v>1178</v>
       </c>
       <c r="B256" s="59" t="n">
         <v>152</v>
@@ -33710,7 +33700,7 @@
         <v>1007</v>
       </c>
       <c r="D256" s="61" t="s">
-        <v>1242</v>
+        <v>1245</v>
       </c>
       <c r="E256" s="60" t="s">
         <v>1083</v>
@@ -33728,7 +33718,7 @@
     </row>
     <row r="257" customFormat="false" ht="43.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A257" s="58" t="s">
-        <v>1177</v>
+        <v>1178</v>
       </c>
       <c r="B257" s="59" t="n">
         <v>153</v>
@@ -33737,10 +33727,10 @@
         <v>1010</v>
       </c>
       <c r="D257" s="61" t="s">
-        <v>1243</v>
+        <v>1246</v>
       </c>
       <c r="E257" s="60" t="s">
-        <v>1083</v>
+        <v>1235</v>
       </c>
       <c r="F257" s="60" t="s">
         <v>238</v>
@@ -33752,12 +33742,12 @@
         <v>132</v>
       </c>
       <c r="I257" s="61" t="s">
-        <v>1233</v>
+        <v>1236</v>
       </c>
     </row>
     <row r="258" customFormat="false" ht="43.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A258" s="58" t="s">
-        <v>1177</v>
+        <v>1178</v>
       </c>
       <c r="B258" s="59" t="n">
         <v>154</v>
@@ -33766,10 +33756,10 @@
         <v>1010</v>
       </c>
       <c r="D258" s="61" t="s">
-        <v>1244</v>
+        <v>1247</v>
       </c>
       <c r="E258" s="60" t="s">
-        <v>1083</v>
+        <v>1235</v>
       </c>
       <c r="F258" s="60" t="s">
         <v>238</v>
@@ -33781,12 +33771,12 @@
         <v>130</v>
       </c>
       <c r="I258" s="61" t="s">
-        <v>1233</v>
+        <v>1236</v>
       </c>
     </row>
     <row r="259" customFormat="false" ht="16.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A259" s="58" t="s">
-        <v>1177</v>
+        <v>1178</v>
       </c>
       <c r="B259" s="59" t="n">
         <v>155</v>
@@ -33813,7 +33803,7 @@
     </row>
     <row r="260" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A260" s="58" t="s">
-        <v>1177</v>
+        <v>1178</v>
       </c>
       <c r="B260" s="59" t="n">
         <v>156</v>
@@ -33822,7 +33812,7 @@
         <v>1009</v>
       </c>
       <c r="D260" s="61" t="s">
-        <v>1245</v>
+        <v>1248</v>
       </c>
       <c r="E260" s="60" t="s">
         <v>1083</v>
@@ -33840,7 +33830,7 @@
     </row>
     <row r="261" customFormat="false" ht="16.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A261" s="58" t="s">
-        <v>1177</v>
+        <v>1178</v>
       </c>
       <c r="B261" s="59" t="n">
         <v>157</v>
@@ -33849,10 +33839,10 @@
         <v>301</v>
       </c>
       <c r="D261" s="61" t="s">
-        <v>1246</v>
+        <v>1249</v>
       </c>
       <c r="E261" s="60" t="s">
-        <v>1125</v>
+        <v>1068</v>
       </c>
       <c r="F261" s="60" t="s">
         <v>301</v>
@@ -33864,12 +33854,12 @@
         <v>159</v>
       </c>
       <c r="I261" s="61" t="s">
-        <v>1247</v>
+        <v>1250</v>
       </c>
     </row>
     <row r="262" customFormat="false" ht="16.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A262" s="58" t="s">
-        <v>1177</v>
+        <v>1178</v>
       </c>
       <c r="B262" s="59" t="n">
         <v>158</v>
@@ -33878,10 +33868,10 @@
         <v>301</v>
       </c>
       <c r="D262" s="61" t="s">
-        <v>1203</v>
+        <v>1205</v>
       </c>
       <c r="E262" s="60" t="s">
-        <v>1125</v>
+        <v>1182</v>
       </c>
       <c r="F262" s="60" t="s">
         <v>301</v>
@@ -33896,7 +33886,7 @@
     </row>
     <row r="263" customFormat="false" ht="43.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A263" s="58" t="s">
-        <v>1177</v>
+        <v>1178</v>
       </c>
       <c r="B263" s="59" t="n">
         <v>159</v>
@@ -33905,10 +33895,10 @@
         <v>1011</v>
       </c>
       <c r="D263" s="61" t="s">
-        <v>1248</v>
+        <v>1251</v>
       </c>
       <c r="E263" s="60" t="s">
-        <v>1083</v>
+        <v>1235</v>
       </c>
       <c r="F263" s="60" t="s">
         <v>238</v>
@@ -33920,12 +33910,12 @@
         <v>136</v>
       </c>
       <c r="I263" s="61" t="s">
-        <v>1233</v>
+        <v>1236</v>
       </c>
     </row>
     <row r="264" customFormat="false" ht="16.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A264" s="58" t="s">
-        <v>1177</v>
+        <v>1178</v>
       </c>
       <c r="B264" s="59" t="n">
         <v>160</v>
@@ -33952,7 +33942,7 @@
     </row>
     <row r="265" customFormat="false" ht="16.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A265" s="58" t="s">
-        <v>1177</v>
+        <v>1178</v>
       </c>
       <c r="B265" s="59" t="n">
         <v>161</v>
@@ -33979,7 +33969,7 @@
     </row>
     <row r="266" customFormat="false" ht="16.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A266" s="58" t="s">
-        <v>1177</v>
+        <v>1178</v>
       </c>
       <c r="B266" s="59" t="n">
         <v>162</v>
@@ -34006,7 +33996,7 @@
     </row>
     <row r="267" customFormat="false" ht="16.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A267" s="58" t="s">
-        <v>1177</v>
+        <v>1178</v>
       </c>
       <c r="B267" s="59" t="n">
         <v>163</v>
@@ -34015,16 +34005,16 @@
         <v>593</v>
       </c>
       <c r="D267" s="61" t="s">
-        <v>1249</v>
+        <v>1252</v>
       </c>
       <c r="E267" s="60" t="s">
-        <v>1184</v>
+        <v>1186</v>
       </c>
       <c r="F267" s="60" t="s">
         <v>593</v>
       </c>
       <c r="G267" s="61" t="s">
-        <v>1250</v>
+        <v>1253</v>
       </c>
       <c r="H267" s="59" t="n">
         <v>304</v>
@@ -34033,7 +34023,7 @@
     </row>
     <row r="268" customFormat="false" ht="16.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A268" s="58" t="s">
-        <v>1177</v>
+        <v>1178</v>
       </c>
       <c r="B268" s="59" t="n">
         <v>164</v>
@@ -34042,7 +34032,7 @@
         <v>591</v>
       </c>
       <c r="D268" s="61" t="s">
-        <v>1251</v>
+        <v>1254</v>
       </c>
       <c r="E268" s="60" t="s">
         <v>17</v>
@@ -34051,7 +34041,7 @@
         <v>591</v>
       </c>
       <c r="G268" s="61" t="s">
-        <v>1251</v>
+        <v>1254</v>
       </c>
       <c r="H268" s="59" t="n">
         <v>303</v>
@@ -34060,7 +34050,7 @@
     </row>
     <row r="269" customFormat="false" ht="16.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A269" s="58" t="s">
-        <v>1177</v>
+        <v>1178</v>
       </c>
       <c r="B269" s="59" t="n">
         <v>165</v>
@@ -34087,7 +34077,7 @@
     </row>
     <row r="270" customFormat="false" ht="16.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A270" s="58" t="s">
-        <v>1177</v>
+        <v>1178</v>
       </c>
       <c r="B270" s="59" t="n">
         <v>166</v>
@@ -34096,16 +34086,16 @@
         <v>587</v>
       </c>
       <c r="D270" s="61" t="s">
-        <v>1249</v>
+        <v>1252</v>
       </c>
       <c r="E270" s="60" t="s">
-        <v>1184</v>
+        <v>1186</v>
       </c>
       <c r="F270" s="60" t="s">
         <v>587</v>
       </c>
       <c r="G270" s="61" t="s">
-        <v>1250</v>
+        <v>1253</v>
       </c>
       <c r="H270" s="59" t="n">
         <v>302</v>
@@ -34114,7 +34104,7 @@
     </row>
     <row r="271" customFormat="false" ht="16.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A271" s="58" t="s">
-        <v>1177</v>
+        <v>1178</v>
       </c>
       <c r="B271" s="59" t="n">
         <v>168</v>
@@ -34123,7 +34113,7 @@
         <v>669</v>
       </c>
       <c r="D271" s="62" t="s">
-        <v>1252</v>
+        <v>1255</v>
       </c>
       <c r="E271" s="60" t="s">
         <v>17</v>
@@ -34132,7 +34122,7 @@
         <v>669</v>
       </c>
       <c r="G271" s="62" t="s">
-        <v>1252</v>
+        <v>1255</v>
       </c>
       <c r="H271" s="59" t="n">
         <v>340</v>
@@ -34141,7 +34131,7 @@
     </row>
     <row r="272" customFormat="false" ht="16.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A272" s="58" t="s">
-        <v>1177</v>
+        <v>1178</v>
       </c>
       <c r="B272" s="59" t="n">
         <v>169</v>
@@ -34168,7 +34158,7 @@
     </row>
     <row r="273" customFormat="false" ht="16.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A273" s="58" t="s">
-        <v>1177</v>
+        <v>1178</v>
       </c>
       <c r="B273" s="59" t="n">
         <v>170</v>
@@ -34195,7 +34185,7 @@
     </row>
     <row r="274" customFormat="false" ht="16.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A274" s="58" t="s">
-        <v>1177</v>
+        <v>1178</v>
       </c>
       <c r="B274" s="59" t="n">
         <v>171</v>
@@ -34222,7 +34212,7 @@
     </row>
     <row r="275" customFormat="false" ht="16.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A275" s="58" t="s">
-        <v>1177</v>
+        <v>1178</v>
       </c>
       <c r="B275" s="59" t="n">
         <v>172</v>
@@ -34249,7 +34239,7 @@
     </row>
     <row r="276" customFormat="false" ht="16.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A276" s="58" t="s">
-        <v>1177</v>
+        <v>1178</v>
       </c>
       <c r="B276" s="59" t="n">
         <v>173</v>
@@ -34276,7 +34266,7 @@
     </row>
     <row r="277" customFormat="false" ht="16.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A277" s="58" t="s">
-        <v>1177</v>
+        <v>1178</v>
       </c>
       <c r="B277" s="59" t="n">
         <v>174</v>
@@ -34303,7 +34293,7 @@
     </row>
     <row r="278" customFormat="false" ht="16.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A278" s="58" t="s">
-        <v>1177</v>
+        <v>1178</v>
       </c>
       <c r="B278" s="59" t="n">
         <v>175</v>
@@ -34330,7 +34320,7 @@
     </row>
     <row r="279" customFormat="false" ht="16.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A279" s="58" t="s">
-        <v>1177</v>
+        <v>1178</v>
       </c>
       <c r="B279" s="59" t="n">
         <v>176</v>
@@ -34357,7 +34347,7 @@
     </row>
     <row r="280" customFormat="false" ht="16.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A280" s="58" t="s">
-        <v>1177</v>
+        <v>1178</v>
       </c>
       <c r="B280" s="59" t="n">
         <v>178</v>
@@ -34366,10 +34356,10 @@
         <v>675</v>
       </c>
       <c r="D280" s="61" t="s">
-        <v>1253</v>
+        <v>1256</v>
       </c>
       <c r="E280" s="60" t="s">
-        <v>1184</v>
+        <v>1186</v>
       </c>
       <c r="F280" s="60" t="s">
         <v>675</v>
@@ -34384,7 +34374,7 @@
     </row>
     <row r="281" customFormat="false" ht="16.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A281" s="58" t="s">
-        <v>1177</v>
+        <v>1178</v>
       </c>
       <c r="B281" s="59" t="n">
         <v>179</v>
@@ -34411,7 +34401,7 @@
     </row>
     <row r="282" customFormat="false" ht="16.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A282" s="58" t="s">
-        <v>1177</v>
+        <v>1178</v>
       </c>
       <c r="B282" s="59" t="n">
         <v>182</v>
@@ -34420,10 +34410,10 @@
         <v>871</v>
       </c>
       <c r="D282" s="62" t="s">
-        <v>1215</v>
+        <v>1217</v>
       </c>
       <c r="E282" s="60" t="s">
-        <v>1184</v>
+        <v>1186</v>
       </c>
       <c r="F282" s="60" t="s">
         <v>871</v>
@@ -34438,7 +34428,7 @@
     </row>
     <row r="283" customFormat="false" ht="16.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A283" s="58" t="s">
-        <v>1177</v>
+        <v>1178</v>
       </c>
       <c r="B283" s="59" t="n">
         <v>183</v>
@@ -34465,7 +34455,7 @@
     </row>
     <row r="284" customFormat="false" ht="16.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A284" s="58" t="s">
-        <v>1177</v>
+        <v>1178</v>
       </c>
       <c r="B284" s="59" t="n">
         <v>184</v>
@@ -34492,7 +34482,7 @@
     </row>
     <row r="285" customFormat="false" ht="16.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A285" s="58" t="s">
-        <v>1177</v>
+        <v>1178</v>
       </c>
       <c r="B285" s="59" t="n">
         <v>185</v>
@@ -34519,7 +34509,7 @@
     </row>
     <row r="286" customFormat="false" ht="16.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A286" s="58" t="s">
-        <v>1177</v>
+        <v>1178</v>
       </c>
       <c r="B286" s="59" t="n">
         <v>186</v>
@@ -34546,7 +34536,7 @@
     </row>
     <row r="287" customFormat="false" ht="43.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A287" s="58" t="s">
-        <v>1177</v>
+        <v>1178</v>
       </c>
       <c r="B287" s="59" t="n">
         <v>188</v>
@@ -34555,7 +34545,7 @@
         <v>985</v>
       </c>
       <c r="D287" s="61" t="s">
-        <v>1254</v>
+        <v>1257</v>
       </c>
       <c r="E287" s="60" t="s">
         <v>1125</v>
@@ -34573,7 +34563,7 @@
     </row>
     <row r="288" customFormat="false" ht="16.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A288" s="58" t="s">
-        <v>1177</v>
+        <v>1178</v>
       </c>
       <c r="B288" s="59" t="n">
         <v>189</v>
@@ -34600,7 +34590,7 @@
     </row>
     <row r="289" customFormat="false" ht="16.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A289" s="58" t="s">
-        <v>1177</v>
+        <v>1178</v>
       </c>
       <c r="B289" s="59" t="n">
         <v>191</v>
@@ -34627,7 +34617,7 @@
     </row>
     <row r="290" customFormat="false" ht="16.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A290" s="58" t="s">
-        <v>1177</v>
+        <v>1178</v>
       </c>
       <c r="B290" s="59" t="n">
         <v>192</v>
@@ -34639,7 +34629,7 @@
         <v>341</v>
       </c>
       <c r="E290" s="60" t="s">
-        <v>1195</v>
+        <v>1197</v>
       </c>
       <c r="F290" s="60" t="s">
         <v>339</v>
@@ -34654,7 +34644,7 @@
     </row>
     <row r="291" customFormat="false" ht="16.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A291" s="58" t="s">
-        <v>1177</v>
+        <v>1178</v>
       </c>
       <c r="B291" s="59" t="n">
         <v>193</v>
@@ -34666,7 +34656,7 @@
         <v>341</v>
       </c>
       <c r="E291" s="60" t="s">
-        <v>1125</v>
+        <v>1158</v>
       </c>
       <c r="F291" s="60" t="s">
         <v>339</v>
@@ -34681,7 +34671,7 @@
     </row>
     <row r="292" customFormat="false" ht="57" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A292" s="58" t="s">
-        <v>1177</v>
+        <v>1178</v>
       </c>
       <c r="B292" s="59" t="n">
         <v>194</v>
@@ -34690,10 +34680,10 @@
         <v>1005</v>
       </c>
       <c r="D292" s="61" t="s">
-        <v>1255</v>
+        <v>1258</v>
       </c>
       <c r="E292" s="60" t="s">
-        <v>1083</v>
+        <v>1235</v>
       </c>
       <c r="F292" s="60" t="s">
         <v>221</v>
@@ -34705,12 +34695,12 @@
         <v>119</v>
       </c>
       <c r="I292" s="61" t="s">
-        <v>1233</v>
+        <v>1236</v>
       </c>
     </row>
     <row r="293" customFormat="false" ht="43.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A293" s="58" t="s">
-        <v>1177</v>
+        <v>1178</v>
       </c>
       <c r="B293" s="59" t="n">
         <v>196</v>
@@ -34719,10 +34709,10 @@
         <v>408</v>
       </c>
       <c r="D293" s="61" t="s">
-        <v>1256</v>
+        <v>1259</v>
       </c>
       <c r="E293" s="60" t="s">
-        <v>1068</v>
+        <v>1125</v>
       </c>
       <c r="F293" s="60" t="s">
         <v>408</v>
@@ -34734,12 +34724,12 @@
         <v>214</v>
       </c>
       <c r="I293" s="61" t="s">
-        <v>1233</v>
+        <v>1236</v>
       </c>
     </row>
     <row r="294" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A294" s="58" t="s">
-        <v>1177</v>
+        <v>1178</v>
       </c>
       <c r="B294" s="59" t="n">
         <v>197</v>
@@ -34748,7 +34738,7 @@
         <v>408</v>
       </c>
       <c r="D294" s="61" t="s">
-        <v>1257</v>
+        <v>1260</v>
       </c>
       <c r="E294" s="60" t="s">
         <v>1068</v>
@@ -34766,7 +34756,7 @@
     </row>
     <row r="295" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A295" s="58" t="s">
-        <v>1177</v>
+        <v>1178</v>
       </c>
       <c r="B295" s="59" t="n">
         <v>198</v>
@@ -34775,7 +34765,7 @@
         <v>408</v>
       </c>
       <c r="D295" s="61" t="s">
-        <v>1258</v>
+        <v>1261</v>
       </c>
       <c r="E295" s="60" t="s">
         <v>1068</v>
@@ -34793,7 +34783,7 @@
     </row>
     <row r="296" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A296" s="58" t="s">
-        <v>1177</v>
+        <v>1178</v>
       </c>
       <c r="B296" s="59" t="n">
         <v>199</v>
@@ -34802,7 +34792,7 @@
         <v>408</v>
       </c>
       <c r="D296" s="61" t="s">
-        <v>1259</v>
+        <v>1262</v>
       </c>
       <c r="E296" s="60" t="s">
         <v>1068</v>
@@ -34820,7 +34810,7 @@
     </row>
     <row r="297" customFormat="false" ht="43.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A297" s="58" t="s">
-        <v>1177</v>
+        <v>1178</v>
       </c>
       <c r="B297" s="59" t="n">
         <v>200</v>
@@ -34829,10 +34819,10 @@
         <v>1006</v>
       </c>
       <c r="D297" s="61" t="s">
-        <v>1260</v>
+        <v>1263</v>
       </c>
       <c r="E297" s="60" t="s">
-        <v>1083</v>
+        <v>1235</v>
       </c>
       <c r="F297" s="60" t="s">
         <v>221</v>
@@ -34844,12 +34834,12 @@
         <v>122</v>
       </c>
       <c r="I297" s="61" t="s">
-        <v>1233</v>
+        <v>1236</v>
       </c>
     </row>
     <row r="298" customFormat="false" ht="43.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A298" s="58" t="s">
-        <v>1177</v>
+        <v>1178</v>
       </c>
       <c r="B298" s="59" t="n">
         <v>201</v>
@@ -34858,10 +34848,10 @@
         <v>1053</v>
       </c>
       <c r="D298" s="61" t="s">
-        <v>1261</v>
+        <v>1264</v>
       </c>
       <c r="E298" s="60" t="s">
-        <v>1125</v>
+        <v>1083</v>
       </c>
       <c r="F298" s="60" t="s">
         <v>408</v>
@@ -34876,7 +34866,7 @@
     </row>
     <row r="299" customFormat="false" ht="16.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A299" s="58" t="s">
-        <v>1177</v>
+        <v>1178</v>
       </c>
       <c r="B299" s="59" t="n">
         <v>202</v>
@@ -34903,7 +34893,7 @@
     </row>
     <row r="300" customFormat="false" ht="16.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A300" s="58" t="s">
-        <v>1177</v>
+        <v>1178</v>
       </c>
       <c r="B300" s="59" t="n">
         <v>203</v>
@@ -34930,7 +34920,7 @@
     </row>
     <row r="301" customFormat="false" ht="16.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A301" s="58" t="s">
-        <v>1177</v>
+        <v>1178</v>
       </c>
       <c r="B301" s="59" t="n">
         <v>205</v>
@@ -34957,7 +34947,7 @@
     </row>
     <row r="302" customFormat="false" ht="16.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A302" s="58" t="s">
-        <v>1177</v>
+        <v>1178</v>
       </c>
       <c r="B302" s="59" t="n">
         <v>210</v>
@@ -34966,7 +34956,7 @@
         <v>376</v>
       </c>
       <c r="D302" s="61" t="s">
-        <v>1262</v>
+        <v>1265</v>
       </c>
       <c r="E302" s="60" t="s">
         <v>1068</v>
@@ -34984,7 +34974,7 @@
     </row>
     <row r="303" customFormat="false" ht="16.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A303" s="58" t="s">
-        <v>1177</v>
+        <v>1178</v>
       </c>
       <c r="B303" s="59" t="n">
         <v>211</v>
@@ -35011,7 +35001,7 @@
     </row>
     <row r="304" customFormat="false" ht="16.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A304" s="58" t="s">
-        <v>1177</v>
+        <v>1178</v>
       </c>
       <c r="B304" s="59" t="n">
         <v>212</v>
@@ -35038,7 +35028,7 @@
     </row>
     <row r="305" customFormat="false" ht="16.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A305" s="58" t="s">
-        <v>1177</v>
+        <v>1178</v>
       </c>
       <c r="B305" s="59" t="n">
         <v>213</v>
@@ -35047,7 +35037,7 @@
         <v>585</v>
       </c>
       <c r="D305" s="61" t="s">
-        <v>1263</v>
+        <v>1266</v>
       </c>
       <c r="E305" s="60" t="s">
         <v>17</v>
@@ -35056,7 +35046,7 @@
         <v>585</v>
       </c>
       <c r="G305" s="61" t="s">
-        <v>1263</v>
+        <v>1266</v>
       </c>
       <c r="H305" s="59" t="n">
         <v>300</v>
@@ -35065,7 +35055,7 @@
     </row>
     <row r="306" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A306" s="58" t="s">
-        <v>1177</v>
+        <v>1178</v>
       </c>
       <c r="B306" s="59" t="n">
         <v>214</v>
@@ -35074,7 +35064,7 @@
         <v>997</v>
       </c>
       <c r="D306" s="61" t="s">
-        <v>1264</v>
+        <v>1267</v>
       </c>
       <c r="E306" s="60" t="s">
         <v>1125</v>
@@ -35092,7 +35082,7 @@
     </row>
     <row r="307" customFormat="false" ht="43.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A307" s="58" t="s">
-        <v>1177</v>
+        <v>1178</v>
       </c>
       <c r="B307" s="59" t="n">
         <v>215</v>
@@ -35101,10 +35091,10 @@
         <v>967</v>
       </c>
       <c r="D307" s="61" t="s">
-        <v>1265</v>
+        <v>1268</v>
       </c>
       <c r="E307" s="60" t="s">
-        <v>1083</v>
+        <v>1235</v>
       </c>
       <c r="F307" s="60" t="s">
         <v>105</v>
@@ -35116,12 +35106,12 @@
         <v>56</v>
       </c>
       <c r="I307" s="61" t="s">
-        <v>1233</v>
+        <v>1236</v>
       </c>
     </row>
     <row r="308" customFormat="false" ht="43.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A308" s="58" t="s">
-        <v>1177</v>
+        <v>1178</v>
       </c>
       <c r="B308" s="59" t="n">
         <v>216</v>
@@ -35130,7 +35120,7 @@
         <v>967</v>
       </c>
       <c r="D308" s="61" t="s">
-        <v>1266</v>
+        <v>1269</v>
       </c>
       <c r="E308" s="60" t="s">
         <v>1125</v>
@@ -35145,12 +35135,12 @@
         <v>56</v>
       </c>
       <c r="I308" s="61" t="s">
-        <v>1233</v>
+        <v>1236</v>
       </c>
     </row>
     <row r="309" customFormat="false" ht="16.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A309" s="58" t="s">
-        <v>1177</v>
+        <v>1178</v>
       </c>
       <c r="B309" s="59" t="n">
         <v>217</v>
@@ -35177,7 +35167,7 @@
     </row>
     <row r="310" customFormat="false" ht="16.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A310" s="58" t="s">
-        <v>1177</v>
+        <v>1178</v>
       </c>
       <c r="B310" s="59" t="n">
         <v>218</v>
@@ -35204,7 +35194,7 @@
     </row>
     <row r="311" customFormat="false" ht="43.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A311" s="58" t="s">
-        <v>1177</v>
+        <v>1178</v>
       </c>
       <c r="B311" s="59" t="n">
         <v>219</v>
@@ -35213,10 +35203,10 @@
         <v>968</v>
       </c>
       <c r="D311" s="61" t="s">
-        <v>1265</v>
+        <v>1268</v>
       </c>
       <c r="E311" s="60" t="s">
-        <v>1125</v>
+        <v>1235</v>
       </c>
       <c r="F311" s="60" t="s">
         <v>105</v>
@@ -35228,12 +35218,12 @@
         <v>56</v>
       </c>
       <c r="I311" s="61" t="s">
-        <v>1233</v>
+        <v>1236</v>
       </c>
     </row>
     <row r="312" customFormat="false" ht="43.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A312" s="58" t="s">
-        <v>1177</v>
+        <v>1178</v>
       </c>
       <c r="B312" s="59" t="n">
         <v>220</v>
@@ -35242,7 +35232,7 @@
         <v>969</v>
       </c>
       <c r="D312" s="61" t="s">
-        <v>1267</v>
+        <v>1270</v>
       </c>
       <c r="E312" s="60" t="s">
         <v>1125</v>
@@ -35257,12 +35247,12 @@
         <v>56</v>
       </c>
       <c r="I312" s="61" t="s">
-        <v>1233</v>
+        <v>1236</v>
       </c>
     </row>
     <row r="313" customFormat="false" ht="16.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A313" s="58" t="s">
-        <v>1177</v>
+        <v>1178</v>
       </c>
       <c r="B313" s="59" t="n">
         <v>222</v>
@@ -35289,7 +35279,7 @@
     </row>
     <row r="314" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A314" s="58" t="s">
-        <v>1177</v>
+        <v>1178</v>
       </c>
       <c r="B314" s="59" t="n">
         <v>223</v>
@@ -35298,7 +35288,7 @@
         <v>1003</v>
       </c>
       <c r="D314" s="61" t="s">
-        <v>1268</v>
+        <v>1271</v>
       </c>
       <c r="E314" s="60" t="s">
         <v>1083</v>
@@ -35316,7 +35306,7 @@
     </row>
     <row r="315" customFormat="false" ht="16.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A315" s="58" t="s">
-        <v>1177</v>
+        <v>1178</v>
       </c>
       <c r="B315" s="59" t="n">
         <v>224</v>
@@ -35343,7 +35333,7 @@
     </row>
     <row r="316" customFormat="false" ht="16.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A316" s="58" t="s">
-        <v>1177</v>
+        <v>1178</v>
       </c>
       <c r="B316" s="59" t="n">
         <v>225</v>
@@ -35370,7 +35360,7 @@
     </row>
     <row r="317" customFormat="false" ht="16.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A317" s="58" t="s">
-        <v>1177</v>
+        <v>1178</v>
       </c>
       <c r="B317" s="59" t="n">
         <v>226</v>
@@ -35379,7 +35369,7 @@
         <v>1044</v>
       </c>
       <c r="D317" s="61" t="s">
-        <v>1269</v>
+        <v>1272</v>
       </c>
       <c r="E317" s="60" t="s">
         <v>1083</v>
@@ -35397,7 +35387,7 @@
     </row>
     <row r="318" customFormat="false" ht="16.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A318" s="58" t="s">
-        <v>1177</v>
+        <v>1178</v>
       </c>
       <c r="B318" s="59" t="n">
         <v>227</v>
@@ -35424,7 +35414,7 @@
     </row>
     <row r="319" customFormat="false" ht="16.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A319" s="58" t="s">
-        <v>1177</v>
+        <v>1178</v>
       </c>
       <c r="B319" s="59" t="n">
         <v>229</v>
@@ -35433,7 +35423,7 @@
         <v>889</v>
       </c>
       <c r="D319" s="62" t="s">
-        <v>1270</v>
+        <v>1273</v>
       </c>
       <c r="E319" s="60" t="s">
         <v>17</v>
@@ -35442,7 +35432,7 @@
         <v>889</v>
       </c>
       <c r="G319" s="62" t="s">
-        <v>1270</v>
+        <v>1273</v>
       </c>
       <c r="H319" s="59" t="n">
         <v>439</v>
@@ -35451,7 +35441,7 @@
     </row>
     <row r="320" customFormat="false" ht="16.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A320" s="58" t="s">
-        <v>1177</v>
+        <v>1178</v>
       </c>
       <c r="B320" s="59" t="n">
         <v>230</v>
@@ -35460,10 +35450,10 @@
         <v>369</v>
       </c>
       <c r="D320" s="61" t="s">
-        <v>1271</v>
+        <v>1274</v>
       </c>
       <c r="E320" s="60" t="s">
-        <v>1068</v>
+        <v>1125</v>
       </c>
       <c r="F320" s="60" t="s">
         <v>369</v>
@@ -35478,7 +35468,7 @@
     </row>
     <row r="321" customFormat="false" ht="16.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A321" s="58" t="s">
-        <v>1177</v>
+        <v>1178</v>
       </c>
       <c r="B321" s="59" t="n">
         <v>231</v>
@@ -35490,7 +35480,7 @@
         <v>370</v>
       </c>
       <c r="E321" s="60" t="s">
-        <v>1125</v>
+        <v>17</v>
       </c>
       <c r="F321" s="60" t="s">
         <v>369</v>
@@ -35505,7 +35495,7 @@
     </row>
     <row r="322" customFormat="false" ht="16.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A322" s="58" t="s">
-        <v>1177</v>
+        <v>1178</v>
       </c>
       <c r="B322" s="59" t="n">
         <v>232</v>
@@ -35514,10 +35504,10 @@
         <v>369</v>
       </c>
       <c r="D322" s="61" t="s">
-        <v>1272</v>
+        <v>1275</v>
       </c>
       <c r="E322" s="60" t="s">
-        <v>1125</v>
+        <v>1182</v>
       </c>
       <c r="F322" s="60" t="s">
         <v>369</v>
@@ -35532,7 +35522,7 @@
     </row>
     <row r="323" customFormat="false" ht="16.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A323" s="58" t="s">
-        <v>1177</v>
+        <v>1178</v>
       </c>
       <c r="B323" s="59" t="n">
         <v>233</v>
@@ -35541,7 +35531,7 @@
         <v>369</v>
       </c>
       <c r="D323" s="61" t="s">
-        <v>1273</v>
+        <v>1276</v>
       </c>
       <c r="E323" s="60" t="s">
         <v>1068</v>
@@ -35559,7 +35549,7 @@
     </row>
     <row r="324" customFormat="false" ht="43.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A324" s="58" t="s">
-        <v>1177</v>
+        <v>1178</v>
       </c>
       <c r="B324" s="59" t="n">
         <v>235</v>
@@ -35568,7 +35558,7 @@
         <v>421</v>
       </c>
       <c r="D324" s="61" t="s">
-        <v>1274</v>
+        <v>1277</v>
       </c>
       <c r="E324" s="60" t="s">
         <v>1068</v>
@@ -35586,7 +35576,7 @@
     </row>
     <row r="325" customFormat="false" ht="16.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A325" s="58" t="s">
-        <v>1177</v>
+        <v>1178</v>
       </c>
       <c r="B325" s="59" t="n">
         <v>236</v>
@@ -35613,7 +35603,7 @@
     </row>
     <row r="326" customFormat="false" ht="16.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A326" s="58" t="s">
-        <v>1177</v>
+        <v>1178</v>
       </c>
       <c r="B326" s="59" t="n">
         <v>238</v>
@@ -35640,7 +35630,7 @@
     </row>
     <row r="327" customFormat="false" ht="16.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A327" s="58" t="s">
-        <v>1177</v>
+        <v>1178</v>
       </c>
       <c r="B327" s="59" t="n">
         <v>241</v>
@@ -35649,10 +35639,10 @@
         <v>531</v>
       </c>
       <c r="D327" s="61" t="s">
-        <v>1275</v>
+        <v>1278</v>
       </c>
       <c r="E327" s="60" t="s">
-        <v>1184</v>
+        <v>1186</v>
       </c>
       <c r="F327" s="60" t="s">
         <v>531</v>
@@ -35667,7 +35657,7 @@
     </row>
     <row r="328" customFormat="false" ht="16.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A328" s="58" t="s">
-        <v>1177</v>
+        <v>1178</v>
       </c>
       <c r="B328" s="59" t="n">
         <v>242</v>
@@ -35694,7 +35684,7 @@
     </row>
     <row r="329" customFormat="false" ht="16.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A329" s="58" t="s">
-        <v>1177</v>
+        <v>1178</v>
       </c>
       <c r="B329" s="59" t="n">
         <v>243</v>
@@ -35703,7 +35693,7 @@
         <v>404</v>
       </c>
       <c r="D329" s="61" t="s">
-        <v>1276</v>
+        <v>1279</v>
       </c>
       <c r="E329" s="60" t="s">
         <v>1068</v>
@@ -35721,7 +35711,7 @@
     </row>
     <row r="330" customFormat="false" ht="16.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A330" s="58" t="s">
-        <v>1177</v>
+        <v>1178</v>
       </c>
       <c r="B330" s="59" t="n">
         <v>244</v>
@@ -35730,10 +35720,10 @@
         <v>528</v>
       </c>
       <c r="D330" s="61" t="s">
-        <v>1277</v>
+        <v>1280</v>
       </c>
       <c r="E330" s="60" t="s">
-        <v>1184</v>
+        <v>1182</v>
       </c>
       <c r="F330" s="60" t="s">
         <v>528</v>
@@ -35748,7 +35738,7 @@
     </row>
     <row r="331" customFormat="false" ht="16.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A331" s="58" t="s">
-        <v>1177</v>
+        <v>1178</v>
       </c>
       <c r="B331" s="59" t="n">
         <v>245</v>
@@ -35760,7 +35750,7 @@
         <v>529</v>
       </c>
       <c r="E331" s="60" t="s">
-        <v>1125</v>
+        <v>17</v>
       </c>
       <c r="F331" s="60" t="s">
         <v>528</v>
@@ -35775,7 +35765,7 @@
     </row>
     <row r="332" customFormat="false" ht="16.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A332" s="58" t="s">
-        <v>1177</v>
+        <v>1178</v>
       </c>
       <c r="B332" s="59" t="n">
         <v>246</v>
@@ -35802,7 +35792,7 @@
     </row>
     <row r="333" customFormat="false" ht="16.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A333" s="58" t="s">
-        <v>1177</v>
+        <v>1178</v>
       </c>
       <c r="B333" s="59" t="n">
         <v>247</v>
@@ -35811,7 +35801,7 @@
         <v>1055</v>
       </c>
       <c r="D333" s="61" t="s">
-        <v>1278</v>
+        <v>1281</v>
       </c>
       <c r="E333" s="60" t="s">
         <v>1083</v>
@@ -35829,7 +35819,7 @@
     </row>
     <row r="334" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A334" s="58" t="s">
-        <v>1177</v>
+        <v>1178</v>
       </c>
       <c r="B334" s="59" t="n">
         <v>248</v>
@@ -35838,10 +35828,10 @@
         <v>1014</v>
       </c>
       <c r="D334" s="61" t="s">
-        <v>1199</v>
+        <v>1201</v>
       </c>
       <c r="E334" s="60" t="s">
-        <v>1125</v>
+        <v>1158</v>
       </c>
       <c r="F334" s="60" t="s">
         <v>254</v>
@@ -35856,7 +35846,7 @@
     </row>
     <row r="335" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A335" s="58" t="s">
-        <v>1177</v>
+        <v>1178</v>
       </c>
       <c r="B335" s="59" t="n">
         <v>249</v>
@@ -35865,7 +35855,7 @@
         <v>1014</v>
       </c>
       <c r="D335" s="61" t="s">
-        <v>1279</v>
+        <v>1282</v>
       </c>
       <c r="E335" s="60" t="s">
         <v>1083</v>
@@ -35883,7 +35873,7 @@
     </row>
     <row r="336" customFormat="false" ht="16.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A336" s="58" t="s">
-        <v>1177</v>
+        <v>1178</v>
       </c>
       <c r="B336" s="59" t="n">
         <v>251</v>
@@ -35910,7 +35900,7 @@
     </row>
     <row r="337" customFormat="false" ht="16.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A337" s="58" t="s">
-        <v>1177</v>
+        <v>1178</v>
       </c>
       <c r="B337" s="59" t="n">
         <v>252</v>
@@ -35919,10 +35909,10 @@
         <v>520</v>
       </c>
       <c r="D337" s="61" t="s">
-        <v>1280</v>
+        <v>1283</v>
       </c>
       <c r="E337" s="60" t="s">
-        <v>1184</v>
+        <v>1186</v>
       </c>
       <c r="F337" s="60" t="s">
         <v>520</v>
@@ -35937,7 +35927,7 @@
     </row>
     <row r="338" customFormat="false" ht="16.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A338" s="58" t="s">
-        <v>1177</v>
+        <v>1178</v>
       </c>
       <c r="B338" s="59" t="n">
         <v>253</v>
@@ -35946,10 +35936,10 @@
         <v>520</v>
       </c>
       <c r="D338" s="61" t="s">
-        <v>1281</v>
+        <v>1284</v>
       </c>
       <c r="E338" s="60" t="s">
-        <v>1184</v>
+        <v>1186</v>
       </c>
       <c r="F338" s="60" t="s">
         <v>520</v>
@@ -35964,7 +35954,7 @@
     </row>
     <row r="339" customFormat="false" ht="16.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A339" s="58" t="s">
-        <v>1177</v>
+        <v>1178</v>
       </c>
       <c r="B339" s="59" t="n">
         <v>254</v>
@@ -35991,7 +35981,7 @@
     </row>
     <row r="340" customFormat="false" ht="16.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A340" s="58" t="s">
-        <v>1177</v>
+        <v>1178</v>
       </c>
       <c r="B340" s="59" t="n">
         <v>255</v>
@@ -36000,10 +35990,10 @@
         <v>515</v>
       </c>
       <c r="D340" s="61" t="s">
-        <v>1282</v>
+        <v>1285</v>
       </c>
       <c r="E340" s="60" t="s">
-        <v>1184</v>
+        <v>1186</v>
       </c>
       <c r="F340" s="60" t="s">
         <v>515</v>
@@ -36018,7 +36008,7 @@
     </row>
     <row r="341" customFormat="false" ht="16.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A341" s="58" t="s">
-        <v>1177</v>
+        <v>1178</v>
       </c>
       <c r="B341" s="59" t="n">
         <v>256</v>
@@ -36030,7 +36020,7 @@
         <v>255</v>
       </c>
       <c r="E341" s="60" t="s">
-        <v>1195</v>
+        <v>1197</v>
       </c>
       <c r="F341" s="60" t="s">
         <v>254</v>
@@ -36045,7 +36035,7 @@
     </row>
     <row r="342" customFormat="false" ht="16.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A342" s="58" t="s">
-        <v>1177</v>
+        <v>1178</v>
       </c>
       <c r="B342" s="59" t="n">
         <v>257</v>
@@ -36054,7 +36044,7 @@
         <v>304</v>
       </c>
       <c r="D342" s="61" t="s">
-        <v>1283</v>
+        <v>1286</v>
       </c>
       <c r="E342" s="60" t="s">
         <v>1068</v>
@@ -36072,7 +36062,7 @@
     </row>
     <row r="343" customFormat="false" ht="57" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A343" s="58" t="s">
-        <v>1177</v>
+        <v>1178</v>
       </c>
       <c r="B343" s="59" t="n">
         <v>258</v>
@@ -36081,10 +36071,10 @@
         <v>1017</v>
       </c>
       <c r="D343" s="61" t="s">
-        <v>1284</v>
+        <v>1287</v>
       </c>
       <c r="E343" s="60" t="s">
-        <v>1083</v>
+        <v>1235</v>
       </c>
       <c r="F343" s="60" t="s">
         <v>254</v>
@@ -36096,12 +36086,12 @@
         <v>141</v>
       </c>
       <c r="I343" s="61" t="s">
-        <v>1233</v>
+        <v>1236</v>
       </c>
     </row>
     <row r="344" customFormat="false" ht="57" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A344" s="58" t="s">
-        <v>1177</v>
+        <v>1178</v>
       </c>
       <c r="B344" s="59" t="n">
         <v>259</v>
@@ -36110,10 +36100,10 @@
         <v>1017</v>
       </c>
       <c r="D344" s="61" t="s">
-        <v>1285</v>
+        <v>1288</v>
       </c>
       <c r="E344" s="60" t="s">
-        <v>1083</v>
+        <v>1235</v>
       </c>
       <c r="F344" s="60" t="s">
         <v>254</v>
@@ -36125,12 +36115,12 @@
         <v>146</v>
       </c>
       <c r="I344" s="61" t="s">
-        <v>1233</v>
+        <v>1236</v>
       </c>
     </row>
     <row r="345" customFormat="false" ht="43.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A345" s="58" t="s">
-        <v>1177</v>
+        <v>1178</v>
       </c>
       <c r="B345" s="59" t="n">
         <v>260</v>
@@ -36139,10 +36129,10 @@
         <v>1017</v>
       </c>
       <c r="D345" s="61" t="s">
-        <v>1286</v>
+        <v>1289</v>
       </c>
       <c r="E345" s="60" t="s">
-        <v>1083</v>
+        <v>1235</v>
       </c>
       <c r="F345" s="60" t="s">
         <v>254</v>
@@ -36154,12 +36144,12 @@
         <v>143</v>
       </c>
       <c r="I345" s="61" t="s">
-        <v>1233</v>
+        <v>1236</v>
       </c>
     </row>
     <row r="346" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A346" s="58" t="s">
-        <v>1177</v>
+        <v>1178</v>
       </c>
       <c r="B346" s="59" t="n">
         <v>261</v>
@@ -36168,7 +36158,7 @@
         <v>1016</v>
       </c>
       <c r="D346" s="61" t="s">
-        <v>1287</v>
+        <v>1290</v>
       </c>
       <c r="E346" s="60" t="s">
         <v>1083</v>
@@ -36186,7 +36176,7 @@
     </row>
     <row r="347" customFormat="false" ht="16.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A347" s="58" t="s">
-        <v>1177</v>
+        <v>1178</v>
       </c>
       <c r="B347" s="59" t="n">
         <v>262</v>
@@ -36213,7 +36203,7 @@
     </row>
     <row r="348" customFormat="false" ht="16.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A348" s="58" t="s">
-        <v>1177</v>
+        <v>1178</v>
       </c>
       <c r="B348" s="59" t="n">
         <v>263</v>
@@ -36240,7 +36230,7 @@
     </row>
     <row r="349" customFormat="false" ht="16.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A349" s="58" t="s">
-        <v>1177</v>
+        <v>1178</v>
       </c>
       <c r="B349" s="59" t="n">
         <v>265</v>
@@ -36267,7 +36257,7 @@
     </row>
     <row r="350" customFormat="false" ht="16.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A350" s="58" t="s">
-        <v>1177</v>
+        <v>1178</v>
       </c>
       <c r="B350" s="59" t="n">
         <v>266</v>
@@ -36294,7 +36284,7 @@
     </row>
     <row r="351" customFormat="false" ht="16.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A351" s="58" t="s">
-        <v>1177</v>
+        <v>1178</v>
       </c>
       <c r="B351" s="59" t="n">
         <v>267</v>
@@ -36321,7 +36311,7 @@
     </row>
     <row r="352" customFormat="false" ht="16.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A352" s="58" t="s">
-        <v>1177</v>
+        <v>1178</v>
       </c>
       <c r="B352" s="59" t="n">
         <v>268</v>
@@ -36330,7 +36320,7 @@
         <v>583</v>
       </c>
       <c r="D352" s="61" t="s">
-        <v>1288</v>
+        <v>1291</v>
       </c>
       <c r="E352" s="60" t="s">
         <v>17</v>
@@ -36339,7 +36329,7 @@
         <v>583</v>
       </c>
       <c r="G352" s="61" t="s">
-        <v>1288</v>
+        <v>1291</v>
       </c>
       <c r="H352" s="59" t="n">
         <v>299</v>
@@ -36348,7 +36338,7 @@
     </row>
     <row r="353" customFormat="false" ht="43.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A353" s="58" t="s">
-        <v>1177</v>
+        <v>1178</v>
       </c>
       <c r="B353" s="59" t="n">
         <v>269</v>
@@ -36357,10 +36347,10 @@
         <v>492</v>
       </c>
       <c r="D353" s="61" t="s">
-        <v>1289</v>
+        <v>1292</v>
       </c>
       <c r="E353" s="60" t="s">
-        <v>1184</v>
+        <v>1186</v>
       </c>
       <c r="F353" s="60" t="s">
         <v>492</v>
@@ -36375,7 +36365,7 @@
     </row>
     <row r="354" customFormat="false" ht="16.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A354" s="58" t="s">
-        <v>1177</v>
+        <v>1178</v>
       </c>
       <c r="B354" s="59" t="n">
         <v>270</v>
@@ -36402,7 +36392,7 @@
     </row>
     <row r="355" customFormat="false" ht="16.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A355" s="58" t="s">
-        <v>1177</v>
+        <v>1178</v>
       </c>
       <c r="B355" s="59" t="n">
         <v>272</v>
@@ -36429,7 +36419,7 @@
     </row>
     <row r="356" customFormat="false" ht="43.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A356" s="58" t="s">
-        <v>1177</v>
+        <v>1178</v>
       </c>
       <c r="B356" s="59" t="n">
         <v>274</v>
@@ -36438,7 +36428,7 @@
         <v>976</v>
       </c>
       <c r="D356" s="61" t="s">
-        <v>1290</v>
+        <v>1293</v>
       </c>
       <c r="E356" s="60" t="s">
         <v>1125</v>
@@ -36456,7 +36446,7 @@
     </row>
     <row r="357" customFormat="false" ht="16.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A357" s="58" t="s">
-        <v>1177</v>
+        <v>1178</v>
       </c>
       <c r="B357" s="59" t="n">
         <v>276</v>
@@ -36483,7 +36473,7 @@
     </row>
     <row r="358" customFormat="false" ht="16.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A358" s="58" t="s">
-        <v>1177</v>
+        <v>1178</v>
       </c>
       <c r="B358" s="59" t="n">
         <v>277</v>
@@ -36510,7 +36500,7 @@
     </row>
     <row r="359" customFormat="false" ht="16.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A359" s="58" t="s">
-        <v>1177</v>
+        <v>1178</v>
       </c>
       <c r="B359" s="59" t="n">
         <v>278</v>
@@ -36537,7 +36527,7 @@
     </row>
     <row r="360" customFormat="false" ht="16.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A360" s="58" t="s">
-        <v>1177</v>
+        <v>1178</v>
       </c>
       <c r="B360" s="59" t="n">
         <v>279</v>
@@ -36564,7 +36554,7 @@
     </row>
     <row r="361" customFormat="false" ht="16.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A361" s="58" t="s">
-        <v>1177</v>
+        <v>1178</v>
       </c>
       <c r="B361" s="59" t="n">
         <v>280</v>
@@ -36591,7 +36581,7 @@
     </row>
     <row r="362" customFormat="false" ht="16.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A362" s="58" t="s">
-        <v>1177</v>
+        <v>1178</v>
       </c>
       <c r="B362" s="59" t="n">
         <v>281</v>
@@ -36618,7 +36608,7 @@
     </row>
     <row r="363" customFormat="false" ht="16.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A363" s="58" t="s">
-        <v>1177</v>
+        <v>1178</v>
       </c>
       <c r="B363" s="59" t="n">
         <v>282</v>
@@ -36645,7 +36635,7 @@
     </row>
     <row r="364" customFormat="false" ht="16.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A364" s="58" t="s">
-        <v>1177</v>
+        <v>1178</v>
       </c>
       <c r="B364" s="59" t="n">
         <v>283</v>
@@ -36672,7 +36662,7 @@
     </row>
     <row r="365" customFormat="false" ht="16.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A365" s="58" t="s">
-        <v>1177</v>
+        <v>1178</v>
       </c>
       <c r="B365" s="59" t="n">
         <v>284</v>
@@ -36699,7 +36689,7 @@
     </row>
     <row r="366" customFormat="false" ht="16.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A366" s="58" t="s">
-        <v>1177</v>
+        <v>1178</v>
       </c>
       <c r="B366" s="59" t="n">
         <v>285</v>
@@ -36726,7 +36716,7 @@
     </row>
     <row r="367" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A367" s="58" t="s">
-        <v>1177</v>
+        <v>1178</v>
       </c>
       <c r="B367" s="59" t="n">
         <v>286</v>
@@ -36735,7 +36725,7 @@
         <v>1034</v>
       </c>
       <c r="D367" s="61" t="s">
-        <v>1291</v>
+        <v>1294</v>
       </c>
       <c r="E367" s="60" t="s">
         <v>1083</v>
@@ -36753,7 +36743,7 @@
     </row>
     <row r="368" customFormat="false" ht="16.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A368" s="58" t="s">
-        <v>1177</v>
+        <v>1178</v>
       </c>
       <c r="B368" s="59" t="n">
         <v>289</v>
@@ -36780,7 +36770,7 @@
     </row>
     <row r="369" customFormat="false" ht="16.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A369" s="58" t="s">
-        <v>1177</v>
+        <v>1178</v>
       </c>
       <c r="B369" s="59" t="n">
         <v>290</v>
@@ -36807,7 +36797,7 @@
     </row>
     <row r="370" customFormat="false" ht="16.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A370" s="58" t="s">
-        <v>1177</v>
+        <v>1178</v>
       </c>
       <c r="B370" s="59" t="n">
         <v>292</v>
@@ -36834,7 +36824,7 @@
     </row>
     <row r="371" customFormat="false" ht="16.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A371" s="58" t="s">
-        <v>1177</v>
+        <v>1178</v>
       </c>
       <c r="B371" s="59" t="n">
         <v>293</v>
@@ -36861,7 +36851,7 @@
     </row>
     <row r="372" customFormat="false" ht="16.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A372" s="58" t="s">
-        <v>1177</v>
+        <v>1178</v>
       </c>
       <c r="B372" s="59" t="n">
         <v>294</v>
@@ -36888,7 +36878,7 @@
     </row>
     <row r="373" customFormat="false" ht="16.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A373" s="58" t="s">
-        <v>1177</v>
+        <v>1178</v>
       </c>
       <c r="B373" s="59" t="n">
         <v>295</v>
@@ -36915,7 +36905,7 @@
     </row>
     <row r="374" customFormat="false" ht="16.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A374" s="58" t="s">
-        <v>1177</v>
+        <v>1178</v>
       </c>
       <c r="B374" s="59" t="n">
         <v>296</v>
@@ -36942,7 +36932,7 @@
     </row>
     <row r="375" customFormat="false" ht="16.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A375" s="58" t="s">
-        <v>1177</v>
+        <v>1178</v>
       </c>
       <c r="B375" s="59" t="n">
         <v>297</v>
@@ -36951,7 +36941,7 @@
         <v>1047</v>
       </c>
       <c r="D375" s="61" t="s">
-        <v>1292</v>
+        <v>1295</v>
       </c>
       <c r="E375" s="60" t="s">
         <v>1125</v>
@@ -36969,7 +36959,7 @@
     </row>
     <row r="376" customFormat="false" ht="16.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A376" s="58" t="s">
-        <v>1177</v>
+        <v>1178</v>
       </c>
       <c r="B376" s="59" t="n">
         <v>298</v>
@@ -36978,7 +36968,7 @@
         <v>1047</v>
       </c>
       <c r="D376" s="61" t="s">
-        <v>1293</v>
+        <v>1296</v>
       </c>
       <c r="E376" s="60" t="s">
         <v>1083</v>
@@ -36996,7 +36986,7 @@
     </row>
     <row r="377" customFormat="false" ht="16.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A377" s="58" t="s">
-        <v>1177</v>
+        <v>1178</v>
       </c>
       <c r="B377" s="59" t="n">
         <v>299</v>
@@ -37023,7 +37013,7 @@
     </row>
     <row r="378" customFormat="false" ht="16.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A378" s="58" t="s">
-        <v>1177</v>
+        <v>1178</v>
       </c>
       <c r="B378" s="59" t="n">
         <v>301</v>
@@ -37050,7 +37040,7 @@
     </row>
     <row r="379" customFormat="false" ht="16.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A379" s="58" t="s">
-        <v>1177</v>
+        <v>1178</v>
       </c>
       <c r="B379" s="59" t="n">
         <v>302</v>
@@ -37059,7 +37049,7 @@
         <v>309</v>
       </c>
       <c r="D379" s="61" t="s">
-        <v>1294</v>
+        <v>1297</v>
       </c>
       <c r="E379" s="60" t="s">
         <v>1068</v>
@@ -37077,7 +37067,7 @@
     </row>
     <row r="380" customFormat="false" ht="16.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A380" s="58" t="s">
-        <v>1177</v>
+        <v>1178</v>
       </c>
       <c r="B380" s="59" t="n">
         <v>303</v>
@@ -37104,7 +37094,7 @@
     </row>
     <row r="381" customFormat="false" ht="16.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A381" s="58" t="s">
-        <v>1177</v>
+        <v>1178</v>
       </c>
       <c r="B381" s="59" t="n">
         <v>304</v>
@@ -37113,16 +37103,16 @@
         <v>581</v>
       </c>
       <c r="D381" s="61" t="s">
-        <v>1295</v>
+        <v>1298</v>
       </c>
       <c r="E381" s="60" t="s">
-        <v>1184</v>
+        <v>1186</v>
       </c>
       <c r="F381" s="60" t="s">
         <v>581</v>
       </c>
       <c r="G381" s="61" t="s">
-        <v>1296</v>
+        <v>1299</v>
       </c>
       <c r="H381" s="59" t="n">
         <v>298</v>
@@ -37131,7 +37121,7 @@
     </row>
     <row r="382" customFormat="false" ht="16.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A382" s="58" t="s">
-        <v>1177</v>
+        <v>1178</v>
       </c>
       <c r="B382" s="59" t="n">
         <v>305</v>
@@ -37140,16 +37130,16 @@
         <v>581</v>
       </c>
       <c r="D382" s="61" t="s">
-        <v>1297</v>
+        <v>1300</v>
       </c>
       <c r="E382" s="60" t="s">
-        <v>1125</v>
+        <v>1182</v>
       </c>
       <c r="F382" s="60" t="s">
         <v>581</v>
       </c>
       <c r="G382" s="61" t="s">
-        <v>1296</v>
+        <v>1299</v>
       </c>
       <c r="H382" s="59" t="n">
         <v>298</v>
@@ -37158,7 +37148,7 @@
     </row>
     <row r="383" customFormat="false" ht="16.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A383" s="58" t="s">
-        <v>1177</v>
+        <v>1178</v>
       </c>
       <c r="B383" s="59" t="n">
         <v>306</v>
@@ -37167,16 +37157,16 @@
         <v>581</v>
       </c>
       <c r="D383" s="61" t="s">
-        <v>1298</v>
+        <v>1301</v>
       </c>
       <c r="E383" s="60" t="s">
-        <v>1125</v>
+        <v>1182</v>
       </c>
       <c r="F383" s="60" t="s">
         <v>581</v>
       </c>
       <c r="G383" s="61" t="s">
-        <v>1296</v>
+        <v>1299</v>
       </c>
       <c r="H383" s="59" t="n">
         <v>298</v>
@@ -37185,7 +37175,7 @@
     </row>
     <row r="384" customFormat="false" ht="16.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A384" s="58" t="s">
-        <v>1177</v>
+        <v>1178</v>
       </c>
       <c r="B384" s="59" t="n">
         <v>307</v>
@@ -37212,7 +37202,7 @@
     </row>
     <row r="385" customFormat="false" ht="16.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A385" s="58" t="s">
-        <v>1177</v>
+        <v>1178</v>
       </c>
       <c r="B385" s="59" t="n">
         <v>308</v>
@@ -37239,7 +37229,7 @@
     </row>
     <row r="386" customFormat="false" ht="16.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A386" s="58" t="s">
-        <v>1177</v>
+        <v>1178</v>
       </c>
       <c r="B386" s="59" t="n">
         <v>309</v>
@@ -37266,7 +37256,7 @@
     </row>
     <row r="387" customFormat="false" ht="16.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A387" s="58" t="s">
-        <v>1177</v>
+        <v>1178</v>
       </c>
       <c r="B387" s="59" t="n">
         <v>310</v>
@@ -37293,7 +37283,7 @@
     </row>
     <row r="388" customFormat="false" ht="16.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A388" s="58" t="s">
-        <v>1177</v>
+        <v>1178</v>
       </c>
       <c r="B388" s="59" t="n">
         <v>311</v>
@@ -37302,7 +37292,7 @@
         <v>1033</v>
       </c>
       <c r="D388" s="61" t="s">
-        <v>1299</v>
+        <v>1302</v>
       </c>
       <c r="E388" s="60" t="s">
         <v>1083</v>
@@ -37320,7 +37310,7 @@
     </row>
     <row r="389" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A389" s="58" t="s">
-        <v>1177</v>
+        <v>1178</v>
       </c>
       <c r="B389" s="59" t="n">
         <v>312</v>
@@ -37329,10 +37319,10 @@
         <v>513</v>
       </c>
       <c r="D389" s="61" t="s">
-        <v>1300</v>
+        <v>1303</v>
       </c>
       <c r="E389" s="60" t="s">
-        <v>1184</v>
+        <v>1186</v>
       </c>
       <c r="F389" s="60" t="s">
         <v>513</v>
@@ -37347,7 +37337,7 @@
     </row>
     <row r="390" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A390" s="58" t="s">
-        <v>1177</v>
+        <v>1178</v>
       </c>
       <c r="B390" s="59" t="n">
         <v>313</v>
@@ -37356,10 +37346,10 @@
         <v>510</v>
       </c>
       <c r="D390" s="61" t="s">
-        <v>1300</v>
+        <v>1303</v>
       </c>
       <c r="E390" s="60" t="s">
-        <v>1184</v>
+        <v>1186</v>
       </c>
       <c r="F390" s="60" t="s">
         <v>510</v>
@@ -37374,7 +37364,7 @@
     </row>
     <row r="391" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A391" s="58" t="s">
-        <v>1177</v>
+        <v>1178</v>
       </c>
       <c r="B391" s="59" t="n">
         <v>314</v>
@@ -37383,10 +37373,10 @@
         <v>510</v>
       </c>
       <c r="D391" s="61" t="s">
-        <v>1301</v>
+        <v>1304</v>
       </c>
       <c r="E391" s="60" t="s">
-        <v>1184</v>
+        <v>1186</v>
       </c>
       <c r="F391" s="60" t="s">
         <v>510</v>
@@ -37401,7 +37391,7 @@
     </row>
     <row r="392" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A392" s="58" t="s">
-        <v>1177</v>
+        <v>1178</v>
       </c>
       <c r="B392" s="59" t="n">
         <v>315</v>
@@ -37410,10 +37400,10 @@
         <v>507</v>
       </c>
       <c r="D392" s="61" t="s">
-        <v>1302</v>
+        <v>1305</v>
       </c>
       <c r="E392" s="60" t="s">
-        <v>1184</v>
+        <v>1186</v>
       </c>
       <c r="F392" s="60" t="s">
         <v>507</v>
@@ -37428,7 +37418,7 @@
     </row>
     <row r="393" customFormat="false" ht="16.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A393" s="58" t="s">
-        <v>1177</v>
+        <v>1178</v>
       </c>
       <c r="B393" s="59" t="n">
         <v>317</v>
@@ -37437,16 +37427,16 @@
         <v>578</v>
       </c>
       <c r="D393" s="61" t="s">
-        <v>1303</v>
+        <v>1306</v>
       </c>
       <c r="E393" s="60" t="s">
-        <v>1184</v>
+        <v>1186</v>
       </c>
       <c r="F393" s="60" t="s">
         <v>578</v>
       </c>
       <c r="G393" s="61" t="s">
-        <v>1296</v>
+        <v>1299</v>
       </c>
       <c r="H393" s="59" t="n">
         <v>297</v>
@@ -37455,7 +37445,7 @@
     </row>
     <row r="394" customFormat="false" ht="16.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A394" s="58" t="s">
-        <v>1177</v>
+        <v>1178</v>
       </c>
       <c r="B394" s="59" t="n">
         <v>318</v>
@@ -37464,16 +37454,16 @@
         <v>578</v>
       </c>
       <c r="D394" s="61" t="s">
-        <v>1295</v>
+        <v>1298</v>
       </c>
       <c r="E394" s="60" t="s">
-        <v>1125</v>
+        <v>1182</v>
       </c>
       <c r="F394" s="60" t="s">
         <v>578</v>
       </c>
       <c r="G394" s="61" t="s">
-        <v>1296</v>
+        <v>1299</v>
       </c>
       <c r="H394" s="59" t="n">
         <v>297</v>
@@ -37482,7 +37472,7 @@
     </row>
     <row r="395" customFormat="false" ht="16.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A395" s="58" t="s">
-        <v>1177</v>
+        <v>1178</v>
       </c>
       <c r="B395" s="59" t="n">
         <v>319</v>
@@ -37509,7 +37499,7 @@
     </row>
     <row r="396" customFormat="false" ht="16.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A396" s="58" t="s">
-        <v>1177</v>
+        <v>1178</v>
       </c>
       <c r="B396" s="59" t="n">
         <v>320</v>
@@ -37536,7 +37526,7 @@
     </row>
     <row r="397" customFormat="false" ht="16.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A397" s="58" t="s">
-        <v>1177</v>
+        <v>1178</v>
       </c>
       <c r="B397" s="59" t="n">
         <v>321</v>
@@ -37545,10 +37535,10 @@
         <v>661</v>
       </c>
       <c r="D397" s="62" t="s">
-        <v>1304</v>
+        <v>1307</v>
       </c>
       <c r="E397" s="60" t="s">
-        <v>1184</v>
+        <v>1186</v>
       </c>
       <c r="F397" s="60" t="s">
         <v>661</v>
@@ -37563,7 +37553,7 @@
     </row>
     <row r="398" customFormat="false" ht="16.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A398" s="58" t="s">
-        <v>1177</v>
+        <v>1178</v>
       </c>
       <c r="B398" s="59" t="n">
         <v>323</v>
@@ -37590,25 +37580,25 @@
     </row>
     <row r="399" customFormat="false" ht="16.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A399" s="58" t="s">
-        <v>1177</v>
+        <v>1178</v>
       </c>
       <c r="B399" s="59" t="n">
         <v>324</v>
       </c>
       <c r="C399" s="60" t="s">
-        <v>1305</v>
+        <v>1308</v>
       </c>
       <c r="D399" s="61" t="s">
-        <v>1306</v>
+        <v>1309</v>
       </c>
       <c r="E399" s="60" t="s">
-        <v>1184</v>
+        <v>1186</v>
       </c>
       <c r="F399" s="60" t="s">
-        <v>1305</v>
+        <v>1308</v>
       </c>
       <c r="G399" s="62" t="s">
-        <v>1307</v>
+        <v>1310</v>
       </c>
       <c r="H399" s="59" t="n">
         <v>295</v>
@@ -37617,7 +37607,7 @@
     </row>
     <row r="400" customFormat="false" ht="16.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A400" s="58" t="s">
-        <v>1177</v>
+        <v>1178</v>
       </c>
       <c r="B400" s="59" t="n">
         <v>325</v>
@@ -37626,10 +37616,10 @@
         <v>1039</v>
       </c>
       <c r="D400" s="61" t="s">
-        <v>1308</v>
+        <v>1311</v>
       </c>
       <c r="E400" s="60" t="s">
-        <v>1083</v>
+        <v>1182</v>
       </c>
       <c r="F400" s="60" t="s">
         <v>349</v>
@@ -37644,7 +37634,7 @@
     </row>
     <row r="401" customFormat="false" ht="16.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A401" s="58" t="s">
-        <v>1177</v>
+        <v>1178</v>
       </c>
       <c r="B401" s="59" t="n">
         <v>326</v>
@@ -37656,7 +37646,7 @@
         <v>355</v>
       </c>
       <c r="E401" s="60" t="s">
-        <v>1195</v>
+        <v>1197</v>
       </c>
       <c r="F401" s="60" t="s">
         <v>349</v>
@@ -37671,7 +37661,7 @@
     </row>
     <row r="402" customFormat="false" ht="16.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A402" s="58" t="s">
-        <v>1177</v>
+        <v>1178</v>
       </c>
       <c r="B402" s="59" t="n">
         <v>327</v>
@@ -37698,7 +37688,7 @@
     </row>
     <row r="403" customFormat="false" ht="16.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A403" s="58" t="s">
-        <v>1177</v>
+        <v>1178</v>
       </c>
       <c r="B403" s="59" t="n">
         <v>328</v>
@@ -37710,7 +37700,7 @@
         <v>350</v>
       </c>
       <c r="E403" s="60" t="s">
-        <v>1125</v>
+        <v>17</v>
       </c>
       <c r="F403" s="60" t="s">
         <v>349</v>
@@ -37725,7 +37715,7 @@
     </row>
     <row r="404" customFormat="false" ht="16.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A404" s="58" t="s">
-        <v>1177</v>
+        <v>1178</v>
       </c>
       <c r="B404" s="59" t="n">
         <v>329</v>
@@ -37752,7 +37742,7 @@
     </row>
     <row r="405" customFormat="false" ht="16.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A405" s="58" t="s">
-        <v>1177</v>
+        <v>1178</v>
       </c>
       <c r="B405" s="59" t="n">
         <v>330</v>
@@ -37779,7 +37769,7 @@
     </row>
     <row r="406" customFormat="false" ht="16.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A406" s="58" t="s">
-        <v>1177</v>
+        <v>1178</v>
       </c>
       <c r="B406" s="59" t="n">
         <v>331</v>
@@ -37788,7 +37778,7 @@
         <v>887</v>
       </c>
       <c r="D406" s="62" t="s">
-        <v>1309</v>
+        <v>1312</v>
       </c>
       <c r="E406" s="60" t="s">
         <v>17</v>
@@ -37797,7 +37787,7 @@
         <v>887</v>
       </c>
       <c r="G406" s="62" t="s">
-        <v>1309</v>
+        <v>1312</v>
       </c>
       <c r="H406" s="59" t="n">
         <v>438</v>
@@ -37806,7 +37796,7 @@
     </row>
     <row r="407" customFormat="false" ht="16.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A407" s="58" t="s">
-        <v>1177</v>
+        <v>1178</v>
       </c>
       <c r="B407" s="59" t="n">
         <v>332</v>
@@ -37815,7 +37805,7 @@
         <v>426</v>
       </c>
       <c r="D407" s="61" t="s">
-        <v>1310</v>
+        <v>1313</v>
       </c>
       <c r="E407" s="60" t="s">
         <v>1068</v>
@@ -37833,7 +37823,7 @@
     </row>
     <row r="408" customFormat="false" ht="16.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A408" s="58" t="s">
-        <v>1177</v>
+        <v>1178</v>
       </c>
       <c r="B408" s="59" t="n">
         <v>335</v>
@@ -37860,7 +37850,7 @@
     </row>
     <row r="409" customFormat="false" ht="16.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A409" s="58" t="s">
-        <v>1177</v>
+        <v>1178</v>
       </c>
       <c r="B409" s="59" t="n">
         <v>336</v>
@@ -37869,16 +37859,16 @@
         <v>572</v>
       </c>
       <c r="D409" s="61" t="s">
-        <v>1311</v>
+        <v>1314</v>
       </c>
       <c r="E409" s="60" t="s">
-        <v>1184</v>
+        <v>1186</v>
       </c>
       <c r="F409" s="60" t="s">
         <v>572</v>
       </c>
       <c r="G409" s="61" t="s">
-        <v>1312</v>
+        <v>1315</v>
       </c>
       <c r="H409" s="59" t="n">
         <v>294</v>
@@ -37887,7 +37877,7 @@
     </row>
     <row r="410" customFormat="false" ht="16.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A410" s="58" t="s">
-        <v>1177</v>
+        <v>1178</v>
       </c>
       <c r="B410" s="59" t="n">
         <v>338</v>
@@ -37896,16 +37886,16 @@
         <v>569</v>
       </c>
       <c r="D410" s="61" t="s">
-        <v>1311</v>
+        <v>1314</v>
       </c>
       <c r="E410" s="60" t="s">
-        <v>1184</v>
+        <v>1186</v>
       </c>
       <c r="F410" s="60" t="s">
         <v>569</v>
       </c>
       <c r="G410" s="61" t="s">
-        <v>1312</v>
+        <v>1315</v>
       </c>
       <c r="H410" s="59" t="n">
         <v>293</v>
@@ -37914,16 +37904,16 @@
     </row>
     <row r="411" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A411" s="58" t="s">
-        <v>1177</v>
+        <v>1178</v>
       </c>
       <c r="B411" s="59" t="n">
         <v>339</v>
       </c>
       <c r="C411" s="58" t="s">
-        <v>1313</v>
+        <v>1316</v>
       </c>
       <c r="D411" s="61" t="s">
-        <v>1314</v>
+        <v>1317</v>
       </c>
       <c r="E411" s="60" t="s">
         <v>1083</v>
@@ -37941,7 +37931,7 @@
     </row>
     <row r="412" customFormat="false" ht="16.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A412" s="58" t="s">
-        <v>1177</v>
+        <v>1178</v>
       </c>
       <c r="B412" s="59" t="n">
         <v>340</v>
@@ -37950,7 +37940,7 @@
         <v>567</v>
       </c>
       <c r="D412" s="61" t="s">
-        <v>1315</v>
+        <v>1318</v>
       </c>
       <c r="E412" s="60" t="s">
         <v>17</v>
@@ -37959,7 +37949,7 @@
         <v>567</v>
       </c>
       <c r="G412" s="61" t="s">
-        <v>1315</v>
+        <v>1318</v>
       </c>
       <c r="H412" s="59" t="n">
         <v>292</v>
@@ -37968,7 +37958,7 @@
     </row>
     <row r="413" customFormat="false" ht="16.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A413" s="58" t="s">
-        <v>1177</v>
+        <v>1178</v>
       </c>
       <c r="B413" s="59" t="n">
         <v>342</v>
@@ -37987,7 +37977,7 @@
     </row>
     <row r="414" customFormat="false" ht="57" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A414" s="58" t="s">
-        <v>1177</v>
+        <v>1178</v>
       </c>
       <c r="B414" s="59" t="n">
         <v>343</v>
@@ -37996,7 +37986,7 @@
         <v>221</v>
       </c>
       <c r="D414" s="61" t="s">
-        <v>1316</v>
+        <v>1319</v>
       </c>
       <c r="E414" s="60" t="s">
         <v>1068</v>
@@ -38014,7 +38004,7 @@
     </row>
     <row r="415" customFormat="false" ht="43.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A415" s="58" t="s">
-        <v>1177</v>
+        <v>1178</v>
       </c>
       <c r="B415" s="59" t="n">
         <v>344</v>
@@ -38023,7 +38013,7 @@
         <v>956</v>
       </c>
       <c r="D415" s="61" t="s">
-        <v>1317</v>
+        <v>1320</v>
       </c>
       <c r="E415" s="60" t="s">
         <v>1083</v>
@@ -38041,7 +38031,7 @@
     </row>
     <row r="416" customFormat="false" ht="16.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A416" s="58" t="s">
-        <v>1177</v>
+        <v>1178</v>
       </c>
       <c r="B416" s="59" t="n">
         <v>346</v>
@@ -38068,7 +38058,7 @@
     </row>
     <row r="417" customFormat="false" ht="16.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A417" s="58" t="s">
-        <v>1177</v>
+        <v>1178</v>
       </c>
       <c r="B417" s="59" t="n">
         <v>347</v>
@@ -38095,7 +38085,7 @@
     </row>
     <row r="418" customFormat="false" ht="16.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A418" s="58" t="s">
-        <v>1177</v>
+        <v>1178</v>
       </c>
       <c r="B418" s="59" t="n">
         <v>348</v>
@@ -38122,7 +38112,7 @@
     </row>
     <row r="419" customFormat="false" ht="16.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A419" s="58" t="s">
-        <v>1177</v>
+        <v>1178</v>
       </c>
       <c r="B419" s="59" t="n">
         <v>349</v>
@@ -38149,7 +38139,7 @@
     </row>
     <row r="420" customFormat="false" ht="16.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A420" s="58" t="s">
-        <v>1177</v>
+        <v>1178</v>
       </c>
       <c r="B420" s="59" t="n">
         <v>350</v>
@@ -38176,16 +38166,16 @@
     </row>
     <row r="421" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A421" s="58" t="s">
-        <v>1177</v>
+        <v>1178</v>
       </c>
       <c r="B421" s="59" t="n">
         <v>351</v>
       </c>
       <c r="C421" s="58" t="s">
-        <v>1318</v>
+        <v>1321</v>
       </c>
       <c r="D421" s="61" t="s">
-        <v>1319</v>
+        <v>1322</v>
       </c>
       <c r="E421" s="60" t="s">
         <v>1083</v>
@@ -38203,7 +38193,7 @@
     </row>
     <row r="422" customFormat="false" ht="16.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A422" s="58" t="s">
-        <v>1177</v>
+        <v>1178</v>
       </c>
       <c r="B422" s="59" t="n">
         <v>352</v>
@@ -38230,7 +38220,7 @@
     </row>
     <row r="423" customFormat="false" ht="16.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A423" s="58" t="s">
-        <v>1320</v>
+        <v>1323</v>
       </c>
       <c r="B423" s="59" t="n">
         <v>1</v>
@@ -38249,7 +38239,7 @@
     </row>
     <row r="424" customFormat="false" ht="57" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A424" s="58" t="s">
-        <v>1320</v>
+        <v>1323</v>
       </c>
       <c r="B424" s="59" t="n">
         <v>2</v>
@@ -38276,7 +38266,7 @@
     </row>
     <row r="425" customFormat="false" ht="57" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A425" s="58" t="s">
-        <v>1320</v>
+        <v>1323</v>
       </c>
       <c r="B425" s="59" t="n">
         <v>3</v>
@@ -38288,7 +38278,7 @@
         <v>226</v>
       </c>
       <c r="E425" s="60" t="s">
-        <v>1125</v>
+        <v>17</v>
       </c>
       <c r="F425" s="60" t="s">
         <v>221</v>
@@ -38303,7 +38293,7 @@
     </row>
     <row r="426" customFormat="false" ht="43.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A426" s="58" t="s">
-        <v>1320</v>
+        <v>1323</v>
       </c>
       <c r="B426" s="59" t="n">
         <v>4</v>
@@ -38330,7 +38320,7 @@
     </row>
     <row r="427" customFormat="false" ht="43.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A427" s="58" t="s">
-        <v>1320</v>
+        <v>1323</v>
       </c>
       <c r="B427" s="59" t="n">
         <v>5</v>
@@ -38357,7 +38347,7 @@
     </row>
     <row r="428" customFormat="false" ht="43.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A428" s="58" t="s">
-        <v>1320</v>
+        <v>1323</v>
       </c>
       <c r="B428" s="59" t="n">
         <v>6</v>
@@ -38369,7 +38359,7 @@
         <v>243</v>
       </c>
       <c r="E428" s="60" t="s">
-        <v>1125</v>
+        <v>17</v>
       </c>
       <c r="F428" s="60" t="s">
         <v>238</v>
@@ -38384,7 +38374,7 @@
     </row>
     <row r="429" customFormat="false" ht="57" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A429" s="58" t="s">
-        <v>1320</v>
+        <v>1323</v>
       </c>
       <c r="B429" s="59" t="n">
         <v>7</v>
@@ -38393,7 +38383,7 @@
         <v>238</v>
       </c>
       <c r="D429" s="61" t="s">
-        <v>1321</v>
+        <v>1324</v>
       </c>
       <c r="E429" s="60" t="s">
         <v>1068</v>
@@ -38411,7 +38401,7 @@
     </row>
     <row r="430" customFormat="false" ht="43.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A430" s="58" t="s">
-        <v>1320</v>
+        <v>1323</v>
       </c>
       <c r="B430" s="59" t="n">
         <v>8</v>
@@ -38423,7 +38413,7 @@
         <v>246</v>
       </c>
       <c r="E430" s="60" t="s">
-        <v>1125</v>
+        <v>17</v>
       </c>
       <c r="F430" s="60" t="s">
         <v>238</v>
@@ -38438,7 +38428,7 @@
     </row>
     <row r="431" customFormat="false" ht="57" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A431" s="58" t="s">
-        <v>1320</v>
+        <v>1323</v>
       </c>
       <c r="B431" s="59" t="n">
         <v>9</v>
@@ -38447,7 +38437,7 @@
         <v>238</v>
       </c>
       <c r="D431" s="61" t="s">
-        <v>1322</v>
+        <v>1325</v>
       </c>
       <c r="E431" s="60" t="s">
         <v>1068</v>
@@ -38465,7 +38455,7 @@
     </row>
     <row r="432" customFormat="false" ht="57" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A432" s="58" t="s">
-        <v>1320</v>
+        <v>1323</v>
       </c>
       <c r="B432" s="59" t="n">
         <v>10</v>
@@ -38477,7 +38467,7 @@
         <v>263</v>
       </c>
       <c r="E432" s="60" t="s">
-        <v>1125</v>
+        <v>17</v>
       </c>
       <c r="F432" s="60" t="s">
         <v>254</v>
@@ -38492,7 +38482,7 @@
     </row>
     <row r="433" customFormat="false" ht="43.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A433" s="58" t="s">
-        <v>1320</v>
+        <v>1323</v>
       </c>
       <c r="B433" s="59" t="n">
         <v>11</v>
@@ -38519,7 +38509,7 @@
     </row>
     <row r="434" customFormat="false" ht="57" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A434" s="58" t="s">
-        <v>1320</v>
+        <v>1323</v>
       </c>
       <c r="B434" s="59" t="n">
         <v>12</v>
@@ -38531,7 +38521,7 @@
         <v>263</v>
       </c>
       <c r="E434" s="60" t="s">
-        <v>1125</v>
+        <v>1174</v>
       </c>
       <c r="F434" s="60" t="s">
         <v>254</v>
@@ -38546,7 +38536,7 @@
     </row>
     <row r="435" customFormat="false" ht="57" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A435" s="58" t="s">
-        <v>1320</v>
+        <v>1323</v>
       </c>
       <c r="B435" s="59" t="n">
         <v>13</v>
@@ -38555,10 +38545,10 @@
         <v>254</v>
       </c>
       <c r="D435" s="61" t="s">
-        <v>1323</v>
+        <v>1326</v>
       </c>
       <c r="E435" s="60" t="s">
-        <v>1125</v>
+        <v>1068</v>
       </c>
       <c r="F435" s="60" t="s">
         <v>254</v>
@@ -38573,7 +38563,7 @@
     </row>
     <row r="436" customFormat="false" ht="43.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A436" s="58" t="s">
-        <v>1320</v>
+        <v>1323</v>
       </c>
       <c r="B436" s="59" t="n">
         <v>14</v>
@@ -38600,7 +38590,7 @@
     </row>
     <row r="437" customFormat="false" ht="57" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A437" s="58" t="s">
-        <v>1320</v>
+        <v>1323</v>
       </c>
       <c r="B437" s="59" t="n">
         <v>15</v>
@@ -38609,10 +38599,10 @@
         <v>274</v>
       </c>
       <c r="D437" s="61" t="s">
-        <v>1324</v>
+        <v>1327</v>
       </c>
       <c r="E437" s="60" t="s">
-        <v>1068</v>
+        <v>1125</v>
       </c>
       <c r="F437" s="60" t="s">
         <v>274</v>
@@ -38624,12 +38614,12 @@
         <v>148</v>
       </c>
       <c r="I437" s="61" t="s">
-        <v>1233</v>
+        <v>1236</v>
       </c>
     </row>
     <row r="438" customFormat="false" ht="57" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A438" s="58" t="s">
-        <v>1320</v>
+        <v>1323</v>
       </c>
       <c r="B438" s="59" t="n">
         <v>16</v>
@@ -38641,7 +38631,7 @@
         <v>279</v>
       </c>
       <c r="E438" s="60" t="s">
-        <v>1125</v>
+        <v>17</v>
       </c>
       <c r="F438" s="60" t="s">
         <v>274</v>
@@ -38656,7 +38646,7 @@
     </row>
     <row r="439" customFormat="false" ht="57" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A439" s="58" t="s">
-        <v>1320</v>
+        <v>1323</v>
       </c>
       <c r="B439" s="59" t="n">
         <v>17</v>
@@ -38665,7 +38655,7 @@
         <v>274</v>
       </c>
       <c r="D439" s="61" t="s">
-        <v>1325</v>
+        <v>1328</v>
       </c>
       <c r="E439" s="60" t="s">
         <v>1068</v>
@@ -38680,12 +38670,12 @@
         <v>151</v>
       </c>
       <c r="I439" s="61" t="s">
-        <v>1233</v>
+        <v>1236</v>
       </c>
     </row>
     <row r="440" customFormat="false" ht="57" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A440" s="58" t="s">
-        <v>1320</v>
+        <v>1323</v>
       </c>
       <c r="B440" s="59" t="n">
         <v>18</v>
@@ -38694,10 +38684,10 @@
         <v>274</v>
       </c>
       <c r="D440" s="61" t="s">
-        <v>1325</v>
+        <v>1328</v>
       </c>
       <c r="E440" s="60" t="s">
-        <v>1173</v>
+        <v>1174</v>
       </c>
       <c r="F440" s="60" t="s">
         <v>274</v>
@@ -38709,12 +38699,12 @@
         <v>151</v>
       </c>
       <c r="I440" s="61" t="s">
-        <v>1233</v>
+        <v>1236</v>
       </c>
     </row>
     <row r="441" customFormat="false" ht="57" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A441" s="58" t="s">
-        <v>1320</v>
+        <v>1323</v>
       </c>
       <c r="B441" s="59" t="n">
         <v>19</v>
@@ -38723,10 +38713,10 @@
         <v>274</v>
       </c>
       <c r="D441" s="61" t="s">
-        <v>1326</v>
+        <v>1329</v>
       </c>
       <c r="E441" s="60" t="s">
-        <v>1068</v>
+        <v>1182</v>
       </c>
       <c r="F441" s="60" t="s">
         <v>274</v>
@@ -38738,12 +38728,12 @@
         <v>150</v>
       </c>
       <c r="I441" s="61" t="s">
-        <v>1233</v>
+        <v>1236</v>
       </c>
     </row>
     <row r="442" customFormat="false" ht="57" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A442" s="58" t="s">
-        <v>1320</v>
+        <v>1323</v>
       </c>
       <c r="B442" s="59" t="n">
         <v>20</v>
@@ -38752,7 +38742,7 @@
         <v>274</v>
       </c>
       <c r="D442" s="61" t="s">
-        <v>1327</v>
+        <v>1330</v>
       </c>
       <c r="E442" s="60" t="s">
         <v>1068</v>
@@ -38767,12 +38757,12 @@
         <v>152</v>
       </c>
       <c r="I442" s="61" t="s">
-        <v>1233</v>
+        <v>1236</v>
       </c>
     </row>
     <row r="443" customFormat="false" ht="43.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A443" s="58" t="s">
-        <v>1320</v>
+        <v>1323</v>
       </c>
       <c r="B443" s="59" t="n">
         <v>21</v>
@@ -38784,7 +38774,7 @@
         <v>230</v>
       </c>
       <c r="E443" s="60" t="s">
-        <v>1125</v>
+        <v>17</v>
       </c>
       <c r="F443" s="60" t="s">
         <v>221</v>
@@ -38799,7 +38789,7 @@
     </row>
     <row r="444" customFormat="false" ht="43.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A444" s="58" t="s">
-        <v>1320</v>
+        <v>1323</v>
       </c>
       <c r="B444" s="59" t="n">
         <v>22</v>
@@ -38808,7 +38798,7 @@
         <v>221</v>
       </c>
       <c r="D444" s="61" t="s">
-        <v>1328</v>
+        <v>1331</v>
       </c>
       <c r="E444" s="60" t="s">
         <v>1068</v>
@@ -38826,7 +38816,7 @@
     </row>
     <row r="445" customFormat="false" ht="43.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A445" s="58" t="s">
-        <v>1320</v>
+        <v>1323</v>
       </c>
       <c r="B445" s="59" t="n">
         <v>23</v>
@@ -38835,7 +38825,7 @@
         <v>221</v>
       </c>
       <c r="D445" s="61" t="s">
-        <v>1329</v>
+        <v>1332</v>
       </c>
       <c r="E445" s="60" t="s">
         <v>1068</v>
@@ -38853,7 +38843,7 @@
     </row>
     <row r="446" customFormat="false" ht="43.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A446" s="58" t="s">
-        <v>1320</v>
+        <v>1323</v>
       </c>
       <c r="B446" s="59" t="n">
         <v>24</v>
@@ -38880,7 +38870,7 @@
     </row>
     <row r="447" customFormat="false" ht="57" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A447" s="58" t="s">
-        <v>1320</v>
+        <v>1323</v>
       </c>
       <c r="B447" s="59" t="n">
         <v>25</v>
@@ -38889,7 +38879,7 @@
         <v>221</v>
       </c>
       <c r="D447" s="61" t="s">
-        <v>1330</v>
+        <v>1333</v>
       </c>
       <c r="E447" s="60" t="s">
         <v>1068</v>
@@ -38907,7 +38897,7 @@
     </row>
     <row r="448" customFormat="false" ht="57" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A448" s="58" t="s">
-        <v>1320</v>
+        <v>1323</v>
       </c>
       <c r="B448" s="59" t="n">
         <v>26</v>
@@ -38934,7 +38924,7 @@
     </row>
     <row r="449" customFormat="false" ht="57" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A449" s="58" t="s">
-        <v>1320</v>
+        <v>1323</v>
       </c>
       <c r="B449" s="59" t="n">
         <v>27</v>
@@ -38946,7 +38936,7 @@
         <v>269</v>
       </c>
       <c r="E449" s="60" t="s">
-        <v>1173</v>
+        <v>1174</v>
       </c>
       <c r="F449" s="60" t="s">
         <v>254</v>
@@ -38961,7 +38951,7 @@
     </row>
     <row r="450" customFormat="false" ht="57" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A450" s="58" t="s">
-        <v>1320</v>
+        <v>1323</v>
       </c>
       <c r="B450" s="59" t="n">
         <v>28</v>
@@ -38973,7 +38963,7 @@
         <v>271</v>
       </c>
       <c r="E450" s="60" t="s">
-        <v>1125</v>
+        <v>17</v>
       </c>
       <c r="F450" s="60" t="s">
         <v>254</v>
@@ -38988,7 +38978,7 @@
     </row>
     <row r="451" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A451" s="58" t="s">
-        <v>1320</v>
+        <v>1323</v>
       </c>
       <c r="B451" s="59" t="n">
         <v>29</v>
@@ -38997,10 +38987,10 @@
         <v>326</v>
       </c>
       <c r="D451" s="61" t="s">
-        <v>1221</v>
+        <v>1223</v>
       </c>
       <c r="E451" s="60" t="s">
-        <v>1173</v>
+        <v>1174</v>
       </c>
       <c r="F451" s="60" t="s">
         <v>326</v>
@@ -39015,7 +39005,7 @@
     </row>
     <row r="452" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A452" s="58" t="s">
-        <v>1320</v>
+        <v>1323</v>
       </c>
       <c r="B452" s="59" t="n">
         <v>30</v>
@@ -39024,7 +39014,7 @@
         <v>326</v>
       </c>
       <c r="D452" s="61" t="s">
-        <v>1331</v>
+        <v>1334</v>
       </c>
       <c r="E452" s="60" t="s">
         <v>1068</v>
@@ -39042,7 +39032,7 @@
     </row>
     <row r="453" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A453" s="58" t="s">
-        <v>1320</v>
+        <v>1323</v>
       </c>
       <c r="B453" s="59" t="n">
         <v>31</v>
@@ -39054,7 +39044,7 @@
         <v>331</v>
       </c>
       <c r="E453" s="60" t="s">
-        <v>1173</v>
+        <v>1174</v>
       </c>
       <c r="F453" s="60" t="s">
         <v>326</v>
@@ -39069,7 +39059,7 @@
     </row>
     <row r="454" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A454" s="58" t="s">
-        <v>1320</v>
+        <v>1323</v>
       </c>
       <c r="B454" s="59" t="n">
         <v>32</v>
@@ -39078,7 +39068,7 @@
         <v>326</v>
       </c>
       <c r="D454" s="61" t="s">
-        <v>1332</v>
+        <v>1335</v>
       </c>
       <c r="E454" s="60" t="s">
         <v>1068</v>
@@ -39096,7 +39086,7 @@
     </row>
     <row r="455" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A455" s="58" t="s">
-        <v>1320</v>
+        <v>1323</v>
       </c>
       <c r="B455" s="59" t="n">
         <v>33</v>
@@ -39105,10 +39095,10 @@
         <v>326</v>
       </c>
       <c r="D455" s="61" t="s">
-        <v>1223</v>
+        <v>1225</v>
       </c>
       <c r="E455" s="60" t="s">
-        <v>1173</v>
+        <v>1174</v>
       </c>
       <c r="F455" s="60" t="s">
         <v>326</v>
@@ -39123,7 +39113,7 @@
     </row>
     <row r="456" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A456" s="58" t="s">
-        <v>1320</v>
+        <v>1323</v>
       </c>
       <c r="B456" s="59" t="n">
         <v>34</v>
@@ -39132,7 +39122,7 @@
         <v>326</v>
       </c>
       <c r="D456" s="61" t="s">
-        <v>1333</v>
+        <v>1336</v>
       </c>
       <c r="E456" s="60" t="s">
         <v>1068</v>
@@ -39150,7 +39140,7 @@
     </row>
     <row r="457" customFormat="false" ht="43.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A457" s="58" t="s">
-        <v>1320</v>
+        <v>1323</v>
       </c>
       <c r="B457" s="59" t="n">
         <v>35</v>
@@ -39162,7 +39152,7 @@
         <v>384</v>
       </c>
       <c r="E457" s="60" t="s">
-        <v>1173</v>
+        <v>1174</v>
       </c>
       <c r="F457" s="60" t="s">
         <v>382</v>
@@ -39177,7 +39167,7 @@
     </row>
     <row r="458" customFormat="false" ht="43.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A458" s="58" t="s">
-        <v>1320</v>
+        <v>1323</v>
       </c>
       <c r="B458" s="59" t="n">
         <v>36</v>
@@ -39189,7 +39179,7 @@
         <v>384</v>
       </c>
       <c r="E458" s="60" t="s">
-        <v>1173</v>
+        <v>1174</v>
       </c>
       <c r="F458" s="60" t="s">
         <v>382</v>
@@ -39204,7 +39194,7 @@
     </row>
     <row r="459" customFormat="false" ht="43.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A459" s="58" t="s">
-        <v>1320</v>
+        <v>1323</v>
       </c>
       <c r="B459" s="59" t="n">
         <v>37</v>
@@ -39213,10 +39203,10 @@
         <v>382</v>
       </c>
       <c r="D459" s="61" t="s">
-        <v>1209</v>
+        <v>1211</v>
       </c>
       <c r="E459" s="60" t="s">
-        <v>1173</v>
+        <v>1174</v>
       </c>
       <c r="F459" s="60" t="s">
         <v>382</v>
@@ -39231,7 +39221,7 @@
     </row>
     <row r="460" customFormat="false" ht="57" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A460" s="58" t="s">
-        <v>1320</v>
+        <v>1323</v>
       </c>
       <c r="B460" s="59" t="n">
         <v>38</v>
@@ -39240,10 +39230,10 @@
         <v>382</v>
       </c>
       <c r="D460" s="61" t="s">
-        <v>1212</v>
+        <v>1214</v>
       </c>
       <c r="E460" s="60" t="s">
-        <v>1173</v>
+        <v>1174</v>
       </c>
       <c r="F460" s="60" t="s">
         <v>382</v>
@@ -39258,7 +39248,7 @@
     </row>
     <row r="461" customFormat="false" ht="43.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A461" s="58" t="s">
-        <v>1320</v>
+        <v>1323</v>
       </c>
       <c r="B461" s="59" t="n">
         <v>39</v>
@@ -39267,10 +39257,10 @@
         <v>382</v>
       </c>
       <c r="D461" s="61" t="s">
-        <v>1209</v>
+        <v>1211</v>
       </c>
       <c r="E461" s="60" t="s">
-        <v>1173</v>
+        <v>1174</v>
       </c>
       <c r="F461" s="60" t="s">
         <v>382</v>
@@ -39285,7 +39275,7 @@
     </row>
     <row r="462" customFormat="false" ht="43.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A462" s="58" t="s">
-        <v>1320</v>
+        <v>1323</v>
       </c>
       <c r="B462" s="59" t="n">
         <v>40</v>
@@ -39297,7 +39287,7 @@
         <v>384</v>
       </c>
       <c r="E462" s="60" t="s">
-        <v>1173</v>
+        <v>1174</v>
       </c>
       <c r="F462" s="60" t="s">
         <v>382</v>
@@ -39312,7 +39302,7 @@
     </row>
     <row r="463" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A463" s="58" t="s">
-        <v>1320</v>
+        <v>1323</v>
       </c>
       <c r="B463" s="59" t="n">
         <v>41</v>
@@ -39321,7 +39311,7 @@
         <v>430</v>
       </c>
       <c r="D463" s="61" t="s">
-        <v>1334</v>
+        <v>1337</v>
       </c>
       <c r="E463" s="60" t="s">
         <v>1068</v>
@@ -39339,7 +39329,7 @@
     </row>
     <row r="464" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A464" s="58" t="s">
-        <v>1320</v>
+        <v>1323</v>
       </c>
       <c r="B464" s="59" t="n">
         <v>42</v>
@@ -39348,7 +39338,7 @@
         <v>430</v>
       </c>
       <c r="D464" s="61" t="s">
-        <v>1335</v>
+        <v>1338</v>
       </c>
       <c r="E464" s="60" t="s">
         <v>1068</v>
@@ -39366,7 +39356,7 @@
     </row>
     <row r="465" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A465" s="58" t="s">
-        <v>1320</v>
+        <v>1323</v>
       </c>
       <c r="B465" s="59" t="n">
         <v>43</v>
@@ -39375,7 +39365,7 @@
         <v>430</v>
       </c>
       <c r="D465" s="61" t="s">
-        <v>1336</v>
+        <v>1339</v>
       </c>
       <c r="E465" s="60" t="s">
         <v>1068</v>
@@ -39393,7 +39383,7 @@
     </row>
     <row r="466" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A466" s="58" t="s">
-        <v>1320</v>
+        <v>1323</v>
       </c>
       <c r="B466" s="59" t="n">
         <v>44</v>
@@ -39402,7 +39392,7 @@
         <v>430</v>
       </c>
       <c r="D466" s="61" t="s">
-        <v>1337</v>
+        <v>1340</v>
       </c>
       <c r="E466" s="60" t="s">
         <v>1068</v>
@@ -39420,7 +39410,7 @@
     </row>
     <row r="467" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A467" s="58" t="s">
-        <v>1320</v>
+        <v>1323</v>
       </c>
       <c r="B467" s="59" t="n">
         <v>45</v>
@@ -39429,7 +39419,7 @@
         <v>430</v>
       </c>
       <c r="D467" s="61" t="s">
-        <v>1338</v>
+        <v>1341</v>
       </c>
       <c r="E467" s="60" t="s">
         <v>1068</v>
@@ -39447,7 +39437,7 @@
     </row>
     <row r="468" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A468" s="58" t="s">
-        <v>1320</v>
+        <v>1323</v>
       </c>
       <c r="B468" s="59" t="n">
         <v>46</v>
@@ -39456,7 +39446,7 @@
         <v>430</v>
       </c>
       <c r="D468" s="61" t="s">
-        <v>1339</v>
+        <v>1342</v>
       </c>
       <c r="E468" s="60" t="s">
         <v>1068</v>
@@ -39474,7 +39464,7 @@
     </row>
     <row r="469" customFormat="false" ht="43.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A469" s="58" t="s">
-        <v>1320</v>
+        <v>1323</v>
       </c>
       <c r="B469" s="59" t="n">
         <v>47</v>
@@ -39483,7 +39473,7 @@
         <v>430</v>
       </c>
       <c r="D469" s="61" t="s">
-        <v>1340</v>
+        <v>1343</v>
       </c>
       <c r="E469" s="60" t="s">
         <v>1068</v>
@@ -39501,7 +39491,7 @@
     </row>
     <row r="470" customFormat="false" ht="43.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A470" s="58" t="s">
-        <v>1320</v>
+        <v>1323</v>
       </c>
       <c r="B470" s="59" t="n">
         <v>48</v>
@@ -39510,7 +39500,7 @@
         <v>430</v>
       </c>
       <c r="D470" s="61" t="s">
-        <v>1341</v>
+        <v>1344</v>
       </c>
       <c r="E470" s="60" t="s">
         <v>1068</v>
@@ -39528,7 +39518,7 @@
     </row>
     <row r="471" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A471" s="58" t="s">
-        <v>1320</v>
+        <v>1323</v>
       </c>
       <c r="B471" s="59" t="n">
         <v>49</v>
@@ -39537,7 +39527,7 @@
         <v>430</v>
       </c>
       <c r="D471" s="61" t="s">
-        <v>1342</v>
+        <v>1345</v>
       </c>
       <c r="E471" s="60" t="s">
         <v>1068</v>
@@ -39555,7 +39545,7 @@
     </row>
     <row r="472" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A472" s="58" t="s">
-        <v>1320</v>
+        <v>1323</v>
       </c>
       <c r="B472" s="59" t="n">
         <v>50</v>
@@ -39564,7 +39554,7 @@
         <v>430</v>
       </c>
       <c r="D472" s="61" t="s">
-        <v>1343</v>
+        <v>1346</v>
       </c>
       <c r="E472" s="60" t="s">
         <v>1068</v>
@@ -39582,7 +39572,7 @@
     </row>
     <row r="473" customFormat="false" ht="43.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A473" s="58" t="s">
-        <v>1320</v>
+        <v>1323</v>
       </c>
       <c r="B473" s="59" t="n">
         <v>51</v>
@@ -39591,7 +39581,7 @@
         <v>382</v>
       </c>
       <c r="D473" s="61" t="s">
-        <v>1344</v>
+        <v>1347</v>
       </c>
       <c r="E473" s="60" t="s">
         <v>1068</v>
@@ -39609,7 +39599,7 @@
     </row>
     <row r="474" customFormat="false" ht="43.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A474" s="58" t="s">
-        <v>1320</v>
+        <v>1323</v>
       </c>
       <c r="B474" s="59" t="n">
         <v>52</v>
@@ -39618,7 +39608,7 @@
         <v>382</v>
       </c>
       <c r="D474" s="61" t="s">
-        <v>1345</v>
+        <v>1348</v>
       </c>
       <c r="E474" s="60" t="s">
         <v>1125</v>
@@ -39636,7 +39626,7 @@
     </row>
     <row r="475" customFormat="false" ht="57" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A475" s="58" t="s">
-        <v>1320</v>
+        <v>1323</v>
       </c>
       <c r="B475" s="59" t="n">
         <v>53</v>
@@ -39645,10 +39635,10 @@
         <v>382</v>
       </c>
       <c r="D475" s="61" t="s">
-        <v>1212</v>
+        <v>1214</v>
       </c>
       <c r="E475" s="60" t="s">
-        <v>1173</v>
+        <v>1174</v>
       </c>
       <c r="F475" s="60" t="s">
         <v>382</v>
@@ -39663,7 +39653,7 @@
     </row>
     <row r="476" customFormat="false" ht="57" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A476" s="58" t="s">
-        <v>1320</v>
+        <v>1323</v>
       </c>
       <c r="B476" s="59" t="n">
         <v>54</v>
@@ -39672,10 +39662,10 @@
         <v>238</v>
       </c>
       <c r="D476" s="61" t="s">
-        <v>1322</v>
+        <v>1325</v>
       </c>
       <c r="E476" s="60" t="s">
-        <v>1173</v>
+        <v>1174</v>
       </c>
       <c r="F476" s="60" t="s">
         <v>238</v>
@@ -39690,7 +39680,7 @@
     </row>
     <row r="477" customFormat="false" ht="57" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A477" s="58" t="s">
-        <v>1320</v>
+        <v>1323</v>
       </c>
       <c r="B477" s="59" t="n">
         <v>55</v>
@@ -39699,7 +39689,7 @@
         <v>238</v>
       </c>
       <c r="D477" s="61" t="s">
-        <v>1346</v>
+        <v>1349</v>
       </c>
       <c r="E477" s="60" t="s">
         <v>1068</v>
@@ -39717,7 +39707,7 @@
     </row>
     <row r="478" customFormat="false" ht="43.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A478" s="58" t="s">
-        <v>1320</v>
+        <v>1323</v>
       </c>
       <c r="B478" s="59" t="n">
         <v>56</v>
@@ -39744,7 +39734,7 @@
     </row>
     <row r="479" customFormat="false" ht="43.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A479" s="58" t="s">
-        <v>1320</v>
+        <v>1323</v>
       </c>
       <c r="B479" s="59" t="n">
         <v>57</v>
@@ -39756,7 +39746,7 @@
         <v>251</v>
       </c>
       <c r="E479" s="60" t="s">
-        <v>1125</v>
+        <v>17</v>
       </c>
       <c r="F479" s="60" t="s">
         <v>238</v>
@@ -39771,7 +39761,7 @@
     </row>
     <row r="480" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A480" s="58" t="s">
-        <v>1320</v>
+        <v>1323</v>
       </c>
       <c r="B480" s="59" t="n">
         <v>58</v>
@@ -39780,16 +39770,16 @@
         <v>339</v>
       </c>
       <c r="D480" s="61" t="s">
-        <v>1166</v>
+        <v>1167</v>
       </c>
       <c r="E480" s="60" t="s">
-        <v>1173</v>
+        <v>1174</v>
       </c>
       <c r="F480" s="60" t="s">
         <v>339</v>
       </c>
       <c r="G480" s="61" t="s">
-        <v>1166</v>
+        <v>1167</v>
       </c>
       <c r="H480" s="59" t="n">
         <v>180</v>
@@ -39798,7 +39788,7 @@
     </row>
     <row r="481" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A481" s="58" t="s">
-        <v>1320</v>
+        <v>1323</v>
       </c>
       <c r="B481" s="59" t="n">
         <v>59</v>
@@ -39807,16 +39797,16 @@
         <v>339</v>
       </c>
       <c r="D481" s="61" t="s">
-        <v>1167</v>
+        <v>1168</v>
       </c>
       <c r="E481" s="60" t="s">
-        <v>1173</v>
+        <v>1174</v>
       </c>
       <c r="F481" s="60" t="s">
         <v>339</v>
       </c>
       <c r="G481" s="61" t="s">
-        <v>1167</v>
+        <v>1168</v>
       </c>
       <c r="H481" s="59" t="n">
         <v>181</v>
@@ -39825,7 +39815,7 @@
     </row>
     <row r="482" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A482" s="58" t="s">
-        <v>1320</v>
+        <v>1323</v>
       </c>
       <c r="B482" s="59" t="n">
         <v>60</v>
@@ -39834,16 +39824,16 @@
         <v>339</v>
       </c>
       <c r="D482" s="61" t="s">
-        <v>1168</v>
+        <v>1169</v>
       </c>
       <c r="E482" s="60" t="s">
-        <v>1173</v>
+        <v>1174</v>
       </c>
       <c r="F482" s="60" t="s">
         <v>339</v>
       </c>
       <c r="G482" s="61" t="s">
-        <v>1169</v>
+        <v>1170</v>
       </c>
       <c r="H482" s="59" t="n">
         <v>182</v>
@@ -39852,7 +39842,7 @@
     </row>
     <row r="483" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A483" s="58" t="s">
-        <v>1320</v>
+        <v>1323</v>
       </c>
       <c r="B483" s="59" t="n">
         <v>61</v>
@@ -39861,16 +39851,16 @@
         <v>339</v>
       </c>
       <c r="D483" s="61" t="s">
-        <v>1170</v>
+        <v>1171</v>
       </c>
       <c r="E483" s="60" t="s">
-        <v>1173</v>
+        <v>1174</v>
       </c>
       <c r="F483" s="60" t="s">
         <v>339</v>
       </c>
       <c r="G483" s="61" t="s">
-        <v>1170</v>
+        <v>1171</v>
       </c>
       <c r="H483" s="59" t="n">
         <v>183</v>
@@ -39879,7 +39869,7 @@
     </row>
     <row r="484" customFormat="false" ht="16.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A484" s="58" t="s">
-        <v>1320</v>
+        <v>1323</v>
       </c>
       <c r="B484" s="59" t="n">
         <v>62</v>
@@ -39888,16 +39878,16 @@
         <v>339</v>
       </c>
       <c r="D484" s="61" t="s">
-        <v>1171</v>
+        <v>1172</v>
       </c>
       <c r="E484" s="60" t="s">
-        <v>1173</v>
+        <v>1174</v>
       </c>
       <c r="F484" s="60" t="s">
         <v>339</v>
       </c>
       <c r="G484" s="61" t="s">
-        <v>1171</v>
+        <v>1172</v>
       </c>
       <c r="H484" s="59" t="n">
         <v>184</v>
@@ -39906,7 +39896,7 @@
     </row>
     <row r="485" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A485" s="58" t="s">
-        <v>1320</v>
+        <v>1323</v>
       </c>
       <c r="B485" s="59" t="n">
         <v>63</v>
@@ -39918,7 +39908,7 @@
         <v>352</v>
       </c>
       <c r="E485" s="60" t="s">
-        <v>1173</v>
+        <v>1174</v>
       </c>
       <c r="F485" s="60" t="s">
         <v>349</v>
@@ -39933,7 +39923,7 @@
     </row>
     <row r="486" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A486" s="58" t="s">
-        <v>1320</v>
+        <v>1323</v>
       </c>
       <c r="B486" s="59" t="n">
         <v>64</v>
@@ -39942,10 +39932,10 @@
         <v>349</v>
       </c>
       <c r="D486" s="61" t="s">
-        <v>1172</v>
+        <v>1173</v>
       </c>
       <c r="E486" s="60" t="s">
-        <v>1173</v>
+        <v>1174</v>
       </c>
       <c r="F486" s="60" t="s">
         <v>349</v>
@@ -39960,7 +39950,7 @@
     </row>
     <row r="487" customFormat="false" ht="16.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A487" s="58" t="s">
-        <v>1320</v>
+        <v>1323</v>
       </c>
       <c r="B487" s="59" t="n">
         <v>65</v>
@@ -39972,7 +39962,7 @@
         <v>354</v>
       </c>
       <c r="E487" s="60" t="s">
-        <v>1173</v>
+        <v>1174</v>
       </c>
       <c r="F487" s="60" t="s">
         <v>349</v>
@@ -39987,7 +39977,7 @@
     </row>
     <row r="488" customFormat="false" ht="16.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A488" s="58" t="s">
-        <v>1320</v>
+        <v>1323</v>
       </c>
       <c r="B488" s="59" t="n">
         <v>66</v>
@@ -39999,7 +39989,7 @@
         <v>361</v>
       </c>
       <c r="E488" s="60" t="s">
-        <v>1173</v>
+        <v>1174</v>
       </c>
       <c r="F488" s="60" t="s">
         <v>360</v>
@@ -40014,7 +40004,7 @@
     </row>
     <row r="489" customFormat="false" ht="16.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A489" s="58" t="s">
-        <v>1320</v>
+        <v>1323</v>
       </c>
       <c r="B489" s="59" t="n">
         <v>67</v>
@@ -40026,7 +40016,7 @@
         <v>363</v>
       </c>
       <c r="E489" s="60" t="s">
-        <v>1173</v>
+        <v>1174</v>
       </c>
       <c r="F489" s="60" t="s">
         <v>360</v>
@@ -40041,7 +40031,7 @@
     </row>
     <row r="490" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A490" s="58" t="s">
-        <v>1320</v>
+        <v>1323</v>
       </c>
       <c r="B490" s="59" t="n">
         <v>68</v>
@@ -40050,10 +40040,10 @@
         <v>369</v>
       </c>
       <c r="D490" s="61" t="s">
+        <v>1175</v>
+      </c>
+      <c r="E490" s="60" t="s">
         <v>1174</v>
-      </c>
-      <c r="E490" s="60" t="s">
-        <v>1173</v>
       </c>
       <c r="F490" s="60" t="s">
         <v>369</v>
@@ -40068,7 +40058,7 @@
     </row>
     <row r="491" customFormat="false" ht="43.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A491" s="58" t="s">
-        <v>1320</v>
+        <v>1323</v>
       </c>
       <c r="B491" s="59" t="n">
         <v>69</v>
@@ -40080,7 +40070,7 @@
         <v>361</v>
       </c>
       <c r="E491" s="60" t="s">
-        <v>1125</v>
+        <v>1158</v>
       </c>
       <c r="F491" s="60" t="s">
         <v>360</v>
@@ -40092,12 +40082,12 @@
         <v>191</v>
       </c>
       <c r="I491" s="61" t="s">
-        <v>1175</v>
+        <v>1176</v>
       </c>
     </row>
     <row r="492" customFormat="false" ht="43.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A492" s="58" t="s">
-        <v>1320</v>
+        <v>1323</v>
       </c>
       <c r="B492" s="59" t="n">
         <v>70</v>
@@ -40109,7 +40099,7 @@
         <v>363</v>
       </c>
       <c r="E492" s="60" t="s">
-        <v>1125</v>
+        <v>1158</v>
       </c>
       <c r="F492" s="60" t="s">
         <v>360</v>
@@ -40121,12 +40111,12 @@
         <v>192</v>
       </c>
       <c r="I492" s="61" t="s">
-        <v>1175</v>
+        <v>1176</v>
       </c>
     </row>
     <row r="493" customFormat="false" ht="16.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A493" s="58" t="s">
-        <v>1320</v>
+        <v>1323</v>
       </c>
       <c r="B493" s="59" t="n">
         <v>71</v>
@@ -40153,7 +40143,7 @@
     </row>
     <row r="494" customFormat="false" ht="16.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A494" s="58" t="s">
-        <v>1320</v>
+        <v>1323</v>
       </c>
       <c r="B494" s="59" t="n">
         <v>72</v>
@@ -40162,7 +40152,7 @@
         <v>313</v>
       </c>
       <c r="D494" s="61" t="s">
-        <v>1347</v>
+        <v>1350</v>
       </c>
       <c r="E494" s="60" t="s">
         <v>1068</v>
@@ -40180,7 +40170,7 @@
     </row>
     <row r="495" customFormat="false" ht="16.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A495" s="58" t="s">
-        <v>1320</v>
+        <v>1323</v>
       </c>
       <c r="B495" s="59" t="n">
         <v>73</v>
@@ -40189,7 +40179,7 @@
         <v>313</v>
       </c>
       <c r="D495" s="61" t="s">
-        <v>1348</v>
+        <v>1351</v>
       </c>
       <c r="E495" s="60" t="s">
         <v>1068</v>
@@ -40207,7 +40197,7 @@
     </row>
     <row r="496" customFormat="false" ht="16.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A496" s="58" t="s">
-        <v>1320</v>
+        <v>1323</v>
       </c>
       <c r="B496" s="59" t="n">
         <v>74</v>
@@ -40226,7 +40216,7 @@
     </row>
     <row r="497" customFormat="false" ht="16.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A497" s="58" t="s">
-        <v>1320</v>
+        <v>1323</v>
       </c>
       <c r="B497" s="59" t="n">
         <v>75</v>
@@ -40245,7 +40235,7 @@
     </row>
     <row r="498" customFormat="false" ht="16.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A498" s="58" t="s">
-        <v>1320</v>
+        <v>1323</v>
       </c>
       <c r="B498" s="59" t="n">
         <v>76</v>
@@ -40272,7 +40262,7 @@
     </row>
     <row r="499" customFormat="false" ht="16.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A499" s="58" t="s">
-        <v>1320</v>
+        <v>1323</v>
       </c>
       <c r="B499" s="59" t="n">
         <v>79</v>
@@ -40299,7 +40289,7 @@
     </row>
     <row r="500" customFormat="false" ht="16.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A500" s="58" t="s">
-        <v>1320</v>
+        <v>1323</v>
       </c>
       <c r="B500" s="59" t="n">
         <v>80</v>
@@ -40326,7 +40316,7 @@
     </row>
     <row r="501" customFormat="false" ht="16.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A501" s="58" t="s">
-        <v>1320</v>
+        <v>1323</v>
       </c>
       <c r="B501" s="59" t="n">
         <v>81</v>
@@ -40353,7 +40343,7 @@
     </row>
     <row r="502" customFormat="false" ht="16.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A502" s="58" t="s">
-        <v>1320</v>
+        <v>1323</v>
       </c>
       <c r="B502" s="59" t="n">
         <v>82</v>
@@ -40380,7 +40370,7 @@
     </row>
     <row r="503" customFormat="false" ht="16.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A503" s="58" t="s">
-        <v>1320</v>
+        <v>1323</v>
       </c>
       <c r="B503" s="59" t="n">
         <v>83</v>
@@ -40407,7 +40397,7 @@
     </row>
     <row r="504" customFormat="false" ht="16.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A504" s="58" t="s">
-        <v>1320</v>
+        <v>1323</v>
       </c>
       <c r="B504" s="59" t="n">
         <v>84</v>
@@ -40434,7 +40424,7 @@
     </row>
     <row r="505" customFormat="false" ht="16.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A505" s="58" t="s">
-        <v>1320</v>
+        <v>1323</v>
       </c>
       <c r="B505" s="59" t="n">
         <v>85</v>
@@ -40461,19 +40451,19 @@
     </row>
     <row r="506" customFormat="false" ht="16.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A506" s="58" t="s">
-        <v>1320</v>
+        <v>1323</v>
       </c>
       <c r="B506" s="59" t="n">
         <v>86</v>
       </c>
       <c r="C506" s="60" t="s">
-        <v>1349</v>
+        <v>1352</v>
       </c>
       <c r="D506" s="62" t="s">
         <v>845</v>
       </c>
       <c r="E506" s="60" t="s">
-        <v>1195</v>
+        <v>1197</v>
       </c>
       <c r="F506" s="60" t="s">
         <v>844</v>
@@ -40488,7 +40478,7 @@
     </row>
     <row r="507" customFormat="false" ht="16.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A507" s="58" t="s">
-        <v>1320</v>
+        <v>1323</v>
       </c>
       <c r="B507" s="59" t="n">
         <v>87</v>
@@ -40515,7 +40505,7 @@
     </row>
     <row r="508" customFormat="false" ht="16.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A508" s="58" t="s">
-        <v>1320</v>
+        <v>1323</v>
       </c>
       <c r="B508" s="59" t="n">
         <v>88</v>
@@ -40542,7 +40532,7 @@
     </row>
     <row r="509" customFormat="false" ht="16.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A509" s="58" t="s">
-        <v>1320</v>
+        <v>1323</v>
       </c>
       <c r="B509" s="59" t="n">
         <v>89</v>
@@ -40569,7 +40559,7 @@
     </row>
     <row r="510" customFormat="false" ht="16.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A510" s="58" t="s">
-        <v>1320</v>
+        <v>1323</v>
       </c>
       <c r="B510" s="59" t="n">
         <v>90</v>
@@ -40596,7 +40586,7 @@
     </row>
     <row r="511" customFormat="false" ht="16.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A511" s="58" t="s">
-        <v>1320</v>
+        <v>1323</v>
       </c>
       <c r="B511" s="59" t="n">
         <v>91</v>
@@ -40606,7 +40596,7 @@
       </c>
       <c r="D511" s="62"/>
       <c r="E511" s="60" t="s">
-        <v>1184</v>
+        <v>1186</v>
       </c>
       <c r="F511" s="60" t="s">
         <v>855</v>
@@ -40618,12 +40608,12 @@
         <v>426</v>
       </c>
       <c r="I511" s="61" t="s">
-        <v>1350</v>
+        <v>1353</v>
       </c>
     </row>
     <row r="512" customFormat="false" ht="16.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A512" s="58" t="s">
-        <v>1320</v>
+        <v>1323</v>
       </c>
       <c r="B512" s="59" t="n">
         <v>94</v>
@@ -40650,7 +40640,7 @@
     </row>
     <row r="513" customFormat="false" ht="16.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A513" s="58" t="s">
-        <v>1320</v>
+        <v>1323</v>
       </c>
       <c r="B513" s="59" t="n">
         <v>95</v>
@@ -40659,16 +40649,16 @@
         <v>601</v>
       </c>
       <c r="D513" s="61" t="s">
-        <v>1351</v>
+        <v>1354</v>
       </c>
       <c r="E513" s="60" t="s">
-        <v>1184</v>
+        <v>1186</v>
       </c>
       <c r="F513" s="60" t="s">
         <v>601</v>
       </c>
       <c r="G513" s="61" t="s">
-        <v>1352</v>
+        <v>1355</v>
       </c>
       <c r="H513" s="59" t="n">
         <v>308</v>
@@ -40677,7 +40667,7 @@
     </row>
     <row r="514" customFormat="false" ht="16.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A514" s="58" t="s">
-        <v>1320</v>
+        <v>1323</v>
       </c>
       <c r="B514" s="59" t="n">
         <v>96</v>
@@ -40686,16 +40676,16 @@
         <v>603</v>
       </c>
       <c r="D514" s="61" t="s">
-        <v>1353</v>
+        <v>1356</v>
       </c>
       <c r="E514" s="60" t="s">
-        <v>1184</v>
+        <v>1186</v>
       </c>
       <c r="F514" s="60" t="s">
         <v>603</v>
       </c>
       <c r="G514" s="61" t="s">
-        <v>1354</v>
+        <v>1357</v>
       </c>
       <c r="H514" s="59" t="n">
         <v>309</v>
@@ -40704,7 +40694,7 @@
     </row>
     <row r="515" customFormat="false" ht="16.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A515" s="58" t="s">
-        <v>1320</v>
+        <v>1323</v>
       </c>
       <c r="B515" s="59" t="n">
         <v>97</v>
@@ -40731,7 +40721,7 @@
     </row>
     <row r="516" customFormat="false" ht="16.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A516" s="58" t="s">
-        <v>1320</v>
+        <v>1323</v>
       </c>
       <c r="B516" s="59" t="n">
         <v>98</v>
@@ -40758,7 +40748,7 @@
     </row>
     <row r="517" customFormat="false" ht="16.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A517" s="58" t="s">
-        <v>1320</v>
+        <v>1323</v>
       </c>
       <c r="B517" s="59" t="n">
         <v>99</v>
@@ -40785,7 +40775,7 @@
     </row>
     <row r="518" customFormat="false" ht="16.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A518" s="58" t="s">
-        <v>1320</v>
+        <v>1323</v>
       </c>
       <c r="B518" s="59" t="n">
         <v>100</v>
@@ -40812,7 +40802,7 @@
     </row>
     <row r="519" customFormat="false" ht="16.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A519" s="58" t="s">
-        <v>1320</v>
+        <v>1323</v>
       </c>
       <c r="B519" s="59" t="n">
         <v>101</v>
@@ -40821,10 +40811,10 @@
         <v>701</v>
       </c>
       <c r="D519" s="61" t="s">
-        <v>1355</v>
+        <v>1358</v>
       </c>
       <c r="E519" s="60" t="s">
-        <v>1184</v>
+        <v>1182</v>
       </c>
       <c r="F519" s="60" t="s">
         <v>701</v>
@@ -40839,7 +40829,7 @@
     </row>
     <row r="520" customFormat="false" ht="16.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A520" s="58" t="s">
-        <v>1320</v>
+        <v>1323</v>
       </c>
       <c r="B520" s="59" t="n">
         <v>102</v>
@@ -40851,7 +40841,7 @@
         <v>699</v>
       </c>
       <c r="E520" s="60" t="s">
-        <v>1125</v>
+        <v>17</v>
       </c>
       <c r="F520" s="60" t="s">
         <v>701</v>
@@ -40866,19 +40856,19 @@
     </row>
     <row r="521" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A521" s="58" t="s">
-        <v>1320</v>
+        <v>1323</v>
       </c>
       <c r="B521" s="59" t="n">
         <v>103</v>
       </c>
       <c r="C521" s="58" t="s">
-        <v>1356</v>
+        <v>1359</v>
       </c>
       <c r="D521" s="61" t="s">
-        <v>1314</v>
+        <v>1317</v>
       </c>
       <c r="E521" s="60" t="s">
-        <v>1125</v>
+        <v>1158</v>
       </c>
       <c r="F521" s="60" t="s">
         <v>49</v>
@@ -40893,7 +40883,7 @@
     </row>
     <row r="522" customFormat="false" ht="43.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A522" s="58" t="s">
-        <v>1320</v>
+        <v>1323</v>
       </c>
       <c r="B522" s="59" t="n">
         <v>104</v>
@@ -40902,7 +40892,7 @@
         <v>951</v>
       </c>
       <c r="D522" s="61" t="s">
-        <v>1357</v>
+        <v>1360</v>
       </c>
       <c r="E522" s="60" t="s">
         <v>1083</v>
@@ -40920,7 +40910,7 @@
     </row>
     <row r="523" customFormat="false" ht="43.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A523" s="58" t="s">
-        <v>1320</v>
+        <v>1323</v>
       </c>
       <c r="B523" s="59" t="n">
         <v>105</v>
@@ -40929,10 +40919,10 @@
         <v>953</v>
       </c>
       <c r="D523" s="61" t="s">
-        <v>1357</v>
+        <v>1360</v>
       </c>
       <c r="E523" s="60" t="s">
-        <v>1125</v>
+        <v>1158</v>
       </c>
       <c r="F523" s="60" t="s">
         <v>49</v>
@@ -40947,7 +40937,7 @@
     </row>
     <row r="524" customFormat="false" ht="16.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A524" s="58" t="s">
-        <v>1320</v>
+        <v>1323</v>
       </c>
       <c r="B524" s="59" t="n">
         <v>106</v>
@@ -40966,7 +40956,7 @@
     </row>
     <row r="525" customFormat="false" ht="16.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A525" s="58" t="s">
-        <v>1320</v>
+        <v>1323</v>
       </c>
       <c r="B525" s="59" t="n">
         <v>107</v>
@@ -40985,7 +40975,7 @@
     </row>
     <row r="526" customFormat="false" ht="16.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A526" s="58" t="s">
-        <v>1320</v>
+        <v>1323</v>
       </c>
       <c r="B526" s="59" t="n">
         <v>108</v>
@@ -41012,7 +41002,7 @@
     </row>
     <row r="527" customFormat="false" ht="16.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A527" s="58" t="s">
-        <v>1320</v>
+        <v>1323</v>
       </c>
       <c r="B527" s="59" t="n">
         <v>109</v>
@@ -41039,7 +41029,7 @@
     </row>
     <row r="528" customFormat="false" ht="16.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A528" s="58" t="s">
-        <v>1320</v>
+        <v>1323</v>
       </c>
       <c r="B528" s="59" t="n">
         <v>110</v>
@@ -41066,7 +41056,7 @@
     </row>
     <row r="529" customFormat="false" ht="16.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A529" s="58" t="s">
-        <v>1320</v>
+        <v>1323</v>
       </c>
       <c r="B529" s="59" t="n">
         <v>111</v>
@@ -41093,7 +41083,7 @@
     </row>
     <row r="530" customFormat="false" ht="16.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A530" s="58" t="s">
-        <v>1320</v>
+        <v>1323</v>
       </c>
       <c r="B530" s="59" t="n">
         <v>112</v>
@@ -41120,7 +41110,7 @@
     </row>
     <row r="531" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A531" s="58" t="s">
-        <v>1320</v>
+        <v>1323</v>
       </c>
       <c r="B531" s="59" t="n">
         <v>113</v>
@@ -41132,7 +41122,7 @@
         <v>1067</v>
       </c>
       <c r="E531" s="60" t="s">
-        <v>1125</v>
+        <v>1158</v>
       </c>
       <c r="F531" s="60" t="s">
         <v>105</v>
@@ -41147,7 +41137,7 @@
     </row>
     <row r="532" customFormat="false" ht="43.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A532" s="58" t="s">
-        <v>1320</v>
+        <v>1323</v>
       </c>
       <c r="B532" s="59" t="n">
         <v>114</v>
@@ -41156,7 +41146,7 @@
         <v>965</v>
       </c>
       <c r="D532" s="61" t="s">
-        <v>1358</v>
+        <v>1361</v>
       </c>
       <c r="E532" s="60" t="s">
         <v>1083</v>
@@ -41174,7 +41164,7 @@
     </row>
     <row r="533" customFormat="false" ht="43.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A533" s="58" t="s">
-        <v>1320</v>
+        <v>1323</v>
       </c>
       <c r="B533" s="59" t="n">
         <v>115</v>
@@ -41186,7 +41176,7 @@
         <v>1106</v>
       </c>
       <c r="E533" s="60" t="s">
-        <v>1125</v>
+        <v>1158</v>
       </c>
       <c r="F533" s="60" t="s">
         <v>198</v>
@@ -41201,7 +41191,7 @@
     </row>
     <row r="534" customFormat="false" ht="43.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A534" s="58" t="s">
-        <v>1320</v>
+        <v>1323</v>
       </c>
       <c r="B534" s="59" t="n">
         <v>116</v>
@@ -41213,7 +41203,7 @@
         <v>1105</v>
       </c>
       <c r="E534" s="60" t="s">
-        <v>1125</v>
+        <v>1158</v>
       </c>
       <c r="F534" s="60" t="s">
         <v>198</v>
@@ -41228,7 +41218,7 @@
     </row>
     <row r="535" customFormat="false" ht="16.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A535" s="58" t="s">
-        <v>1320</v>
+        <v>1323</v>
       </c>
       <c r="B535" s="59" t="n">
         <v>117</v>
@@ -41255,7 +41245,7 @@
     </row>
     <row r="536" customFormat="false" ht="16.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A536" s="58" t="s">
-        <v>1320</v>
+        <v>1323</v>
       </c>
       <c r="B536" s="59" t="n">
         <v>118</v>
@@ -41267,7 +41257,7 @@
         <v>104</v>
       </c>
       <c r="E536" s="60" t="s">
-        <v>1173</v>
+        <v>1174</v>
       </c>
       <c r="F536" s="60" t="s">
         <v>557</v>
@@ -41282,7 +41272,7 @@
     </row>
     <row r="537" customFormat="false" ht="16.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A537" s="58" t="s">
-        <v>1320</v>
+        <v>1323</v>
       </c>
       <c r="B537" s="59" t="n">
         <v>119</v>
@@ -41309,7 +41299,7 @@
     </row>
     <row r="538" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A538" s="58" t="s">
-        <v>1320</v>
+        <v>1323</v>
       </c>
       <c r="B538" s="59" t="n">
         <v>120</v>
@@ -41336,7 +41326,7 @@
     </row>
     <row r="539" customFormat="false" ht="16.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A539" s="58" t="s">
-        <v>1320</v>
+        <v>1323</v>
       </c>
       <c r="B539" s="59" t="n">
         <v>121</v>
@@ -41363,7 +41353,7 @@
     </row>
     <row r="540" customFormat="false" ht="57" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A540" s="58" t="s">
-        <v>1320</v>
+        <v>1323</v>
       </c>
       <c r="B540" s="59" t="n">
         <v>124</v>
@@ -41372,10 +41362,10 @@
         <v>967</v>
       </c>
       <c r="D540" s="61" t="s">
-        <v>1359</v>
+        <v>1362</v>
       </c>
       <c r="E540" s="60" t="s">
-        <v>1125</v>
+        <v>1083</v>
       </c>
       <c r="F540" s="60" t="s">
         <v>105</v>
@@ -41390,7 +41380,7 @@
     </row>
     <row r="541" customFormat="false" ht="16.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A541" s="58" t="s">
-        <v>1320</v>
+        <v>1323</v>
       </c>
       <c r="B541" s="59" t="n">
         <v>125</v>
@@ -41417,7 +41407,7 @@
     </row>
     <row r="542" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A542" s="58" t="s">
-        <v>1320</v>
+        <v>1323</v>
       </c>
       <c r="B542" s="59" t="n">
         <v>126</v>
@@ -41444,7 +41434,7 @@
     </row>
     <row r="543" customFormat="false" ht="16.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A543" s="58" t="s">
-        <v>1320</v>
+        <v>1323</v>
       </c>
       <c r="B543" s="59" t="n">
         <v>128</v>
@@ -41456,7 +41446,7 @@
         <v>26</v>
       </c>
       <c r="E543" s="60" t="s">
-        <v>1173</v>
+        <v>1174</v>
       </c>
       <c r="F543" s="60" t="s">
         <v>542</v>
@@ -41471,7 +41461,7 @@
     </row>
     <row r="544" customFormat="false" ht="16.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A544" s="58" t="s">
-        <v>1320</v>
+        <v>1323</v>
       </c>
       <c r="B544" s="59" t="n">
         <v>129</v>
@@ -41483,7 +41473,7 @@
         <v>31</v>
       </c>
       <c r="E544" s="60" t="s">
-        <v>1173</v>
+        <v>1174</v>
       </c>
       <c r="F544" s="60" t="s">
         <v>545</v>
@@ -41498,7 +41488,7 @@
     </row>
     <row r="545" customFormat="false" ht="16.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A545" s="58" t="s">
-        <v>1320</v>
+        <v>1323</v>
       </c>
       <c r="B545" s="59" t="n">
         <v>130</v>
@@ -41525,7 +41515,7 @@
     </row>
     <row r="546" customFormat="false" ht="16.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A546" s="58" t="s">
-        <v>1320</v>
+        <v>1323</v>
       </c>
       <c r="B546" s="59" t="n">
         <v>132</v>
@@ -41552,7 +41542,7 @@
     </row>
     <row r="547" customFormat="false" ht="16.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A547" s="58" t="s">
-        <v>1320</v>
+        <v>1323</v>
       </c>
       <c r="B547" s="59" t="n">
         <v>133</v>
@@ -41564,7 +41554,7 @@
         <v>785</v>
       </c>
       <c r="E547" s="60" t="s">
-        <v>1173</v>
+        <v>1174</v>
       </c>
       <c r="F547" s="60" t="s">
         <v>784</v>
@@ -41579,7 +41569,7 @@
     </row>
     <row r="548" customFormat="false" ht="16.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A548" s="58" t="s">
-        <v>1320</v>
+        <v>1323</v>
       </c>
       <c r="B548" s="59" t="n">
         <v>134</v>
@@ -41606,7 +41596,7 @@
     </row>
     <row r="549" customFormat="false" ht="16.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A549" s="58" t="s">
-        <v>1320</v>
+        <v>1323</v>
       </c>
       <c r="B549" s="59" t="n">
         <v>135</v>
@@ -41615,16 +41605,16 @@
         <v>666</v>
       </c>
       <c r="D549" s="62" t="s">
-        <v>1360</v>
+        <v>1363</v>
       </c>
       <c r="E549" s="60" t="s">
-        <v>1184</v>
+        <v>1186</v>
       </c>
       <c r="F549" s="60" t="s">
         <v>666</v>
       </c>
       <c r="G549" s="62" t="s">
-        <v>1252</v>
+        <v>1255</v>
       </c>
       <c r="H549" s="59" t="n">
         <v>339</v>
@@ -41633,7 +41623,7 @@
     </row>
     <row r="550" customFormat="false" ht="16.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A550" s="58" t="s">
-        <v>1320</v>
+        <v>1323</v>
       </c>
       <c r="B550" s="59" t="n">
         <v>136</v>
@@ -41645,7 +41635,7 @@
         <v>295</v>
       </c>
       <c r="E550" s="60" t="s">
-        <v>1195</v>
+        <v>1197</v>
       </c>
       <c r="F550" s="60" t="s">
         <v>294</v>
@@ -41660,7 +41650,7 @@
     </row>
     <row r="551" customFormat="false" ht="16.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A551" s="58" t="s">
-        <v>1320</v>
+        <v>1323</v>
       </c>
       <c r="B551" s="59" t="n">
         <v>137</v>
@@ -41687,7 +41677,7 @@
     </row>
     <row r="552" customFormat="false" ht="16.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A552" s="58" t="s">
-        <v>1320</v>
+        <v>1323</v>
       </c>
       <c r="B552" s="59" t="n">
         <v>138</v>
@@ -41714,7 +41704,7 @@
     </row>
     <row r="553" customFormat="false" ht="43.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A553" s="58" t="s">
-        <v>1320</v>
+        <v>1323</v>
       </c>
       <c r="B553" s="59" t="n">
         <v>139</v>
@@ -41723,7 +41713,7 @@
         <v>957</v>
       </c>
       <c r="D553" s="61" t="s">
-        <v>1361</v>
+        <v>1364</v>
       </c>
       <c r="E553" s="60" t="s">
         <v>1083</v>
@@ -41741,7 +41731,7 @@
     </row>
     <row r="554" customFormat="false" ht="43.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A554" s="58" t="s">
-        <v>1320</v>
+        <v>1323</v>
       </c>
       <c r="B554" s="59" t="n">
         <v>140</v>
@@ -41750,7 +41740,7 @@
         <v>960</v>
       </c>
       <c r="D554" s="61" t="s">
-        <v>1362</v>
+        <v>1365</v>
       </c>
       <c r="E554" s="60" t="s">
         <v>1083</v>
@@ -41768,7 +41758,7 @@
     </row>
     <row r="555" customFormat="false" ht="16.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A555" s="58" t="s">
-        <v>1320</v>
+        <v>1323</v>
       </c>
       <c r="B555" s="59" t="n">
         <v>144</v>
@@ -41777,16 +41767,16 @@
         <v>884</v>
       </c>
       <c r="D555" s="62" t="s">
-        <v>1363</v>
+        <v>1366</v>
       </c>
       <c r="E555" s="60" t="s">
-        <v>1184</v>
+        <v>1186</v>
       </c>
       <c r="F555" s="60" t="s">
         <v>884</v>
       </c>
       <c r="G555" s="62" t="s">
-        <v>1364</v>
+        <v>1367</v>
       </c>
       <c r="H555" s="59" t="n">
         <v>437</v>
@@ -41795,7 +41785,7 @@
     </row>
     <row r="556" customFormat="false" ht="16.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A556" s="58" t="s">
-        <v>1320</v>
+        <v>1323</v>
       </c>
       <c r="B556" s="59" t="n">
         <v>147</v>
@@ -41822,7 +41812,7 @@
     </row>
     <row r="557" customFormat="false" ht="16.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A557" s="58" t="s">
-        <v>1320</v>
+        <v>1323</v>
       </c>
       <c r="B557" s="59" t="n">
         <v>148</v>
@@ -41849,7 +41839,7 @@
     </row>
     <row r="558" customFormat="false" ht="16.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A558" s="58" t="s">
-        <v>1320</v>
+        <v>1323</v>
       </c>
       <c r="B558" s="59" t="n">
         <v>149</v>
@@ -41876,7 +41866,7 @@
     </row>
     <row r="559" customFormat="false" ht="16.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A559" s="60" t="s">
-        <v>1365</v>
+        <v>1368</v>
       </c>
       <c r="B559" s="59" t="n">
         <v>1</v>
@@ -41895,7 +41885,7 @@
     </row>
     <row r="560" customFormat="false" ht="57" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A560" s="60" t="s">
-        <v>1365</v>
+        <v>1368</v>
       </c>
       <c r="B560" s="59" t="n">
         <v>2</v>
@@ -41907,7 +41897,7 @@
         <v>224</v>
       </c>
       <c r="E560" s="60" t="s">
-        <v>1173</v>
+        <v>1174</v>
       </c>
       <c r="F560" s="60" t="s">
         <v>221</v>
@@ -41922,7 +41912,7 @@
     </row>
     <row r="561" customFormat="false" ht="57" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A561" s="60" t="s">
-        <v>1365</v>
+        <v>1368</v>
       </c>
       <c r="B561" s="59" t="n">
         <v>3</v>
@@ -41934,7 +41924,7 @@
         <v>226</v>
       </c>
       <c r="E561" s="60" t="s">
-        <v>1125</v>
+        <v>1174</v>
       </c>
       <c r="F561" s="60" t="s">
         <v>221</v>
@@ -41949,7 +41939,7 @@
     </row>
     <row r="562" customFormat="false" ht="43.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A562" s="60" t="s">
-        <v>1365</v>
+        <v>1368</v>
       </c>
       <c r="B562" s="59" t="n">
         <v>4</v>
@@ -41961,7 +41951,7 @@
         <v>228</v>
       </c>
       <c r="E562" s="60" t="s">
-        <v>1173</v>
+        <v>1174</v>
       </c>
       <c r="F562" s="60" t="s">
         <v>221</v>
@@ -41976,7 +41966,7 @@
     </row>
     <row r="563" customFormat="false" ht="43.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A563" s="60" t="s">
-        <v>1365</v>
+        <v>1368</v>
       </c>
       <c r="B563" s="59" t="n">
         <v>5</v>
@@ -41988,7 +41978,7 @@
         <v>229</v>
       </c>
       <c r="E563" s="60" t="s">
-        <v>1173</v>
+        <v>1174</v>
       </c>
       <c r="F563" s="60" t="s">
         <v>221</v>
@@ -42003,7 +41993,7 @@
     </row>
     <row r="564" customFormat="false" ht="43.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A564" s="60" t="s">
-        <v>1365</v>
+        <v>1368</v>
       </c>
       <c r="B564" s="59" t="n">
         <v>6</v>
@@ -42015,7 +42005,7 @@
         <v>243</v>
       </c>
       <c r="E564" s="60" t="s">
-        <v>1125</v>
+        <v>1174</v>
       </c>
       <c r="F564" s="60" t="s">
         <v>238</v>
@@ -42030,7 +42020,7 @@
     </row>
     <row r="565" customFormat="false" ht="57" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A565" s="60" t="s">
-        <v>1365</v>
+        <v>1368</v>
       </c>
       <c r="B565" s="59" t="n">
         <v>7</v>
@@ -42039,10 +42029,10 @@
         <v>238</v>
       </c>
       <c r="D565" s="61" t="s">
-        <v>1321</v>
+        <v>1324</v>
       </c>
       <c r="E565" s="60" t="s">
-        <v>1173</v>
+        <v>1174</v>
       </c>
       <c r="F565" s="60" t="s">
         <v>238</v>
@@ -42057,7 +42047,7 @@
     </row>
     <row r="566" customFormat="false" ht="43.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A566" s="60" t="s">
-        <v>1365</v>
+        <v>1368</v>
       </c>
       <c r="B566" s="59" t="n">
         <v>8</v>
@@ -42069,7 +42059,7 @@
         <v>246</v>
       </c>
       <c r="E566" s="60" t="s">
-        <v>1125</v>
+        <v>1174</v>
       </c>
       <c r="F566" s="60" t="s">
         <v>238</v>
@@ -42084,7 +42074,7 @@
     </row>
     <row r="567" customFormat="false" ht="57" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A567" s="60" t="s">
-        <v>1365</v>
+        <v>1368</v>
       </c>
       <c r="B567" s="59" t="n">
         <v>9</v>
@@ -42093,10 +42083,10 @@
         <v>238</v>
       </c>
       <c r="D567" s="61" t="s">
-        <v>1322</v>
+        <v>1325</v>
       </c>
       <c r="E567" s="60" t="s">
-        <v>1173</v>
+        <v>1174</v>
       </c>
       <c r="F567" s="60" t="s">
         <v>238</v>
@@ -42111,7 +42101,7 @@
     </row>
     <row r="568" customFormat="false" ht="57" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A568" s="60" t="s">
-        <v>1365</v>
+        <v>1368</v>
       </c>
       <c r="B568" s="59" t="n">
         <v>10</v>
@@ -42123,7 +42113,7 @@
         <v>263</v>
       </c>
       <c r="E568" s="60" t="s">
-        <v>1125</v>
+        <v>1174</v>
       </c>
       <c r="F568" s="60" t="s">
         <v>254</v>
@@ -42138,7 +42128,7 @@
     </row>
     <row r="569" customFormat="false" ht="43.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A569" s="60" t="s">
-        <v>1365</v>
+        <v>1368</v>
       </c>
       <c r="B569" s="59" t="n">
         <v>11</v>
@@ -42150,7 +42140,7 @@
         <v>265</v>
       </c>
       <c r="E569" s="60" t="s">
-        <v>1173</v>
+        <v>1174</v>
       </c>
       <c r="F569" s="60" t="s">
         <v>254</v>
@@ -42165,7 +42155,7 @@
     </row>
     <row r="570" customFormat="false" ht="57" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A570" s="60" t="s">
-        <v>1365</v>
+        <v>1368</v>
       </c>
       <c r="B570" s="59" t="n">
         <v>12</v>
@@ -42177,7 +42167,7 @@
         <v>263</v>
       </c>
       <c r="E570" s="60" t="s">
-        <v>1125</v>
+        <v>1174</v>
       </c>
       <c r="F570" s="60" t="s">
         <v>254</v>
@@ -42192,7 +42182,7 @@
     </row>
     <row r="571" customFormat="false" ht="57" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A571" s="60" t="s">
-        <v>1365</v>
+        <v>1368</v>
       </c>
       <c r="B571" s="59" t="n">
         <v>13</v>
@@ -42201,10 +42191,10 @@
         <v>254</v>
       </c>
       <c r="D571" s="61" t="s">
-        <v>1323</v>
+        <v>1326</v>
       </c>
       <c r="E571" s="60" t="s">
-        <v>1125</v>
+        <v>1174</v>
       </c>
       <c r="F571" s="60" t="s">
         <v>254</v>
@@ -42219,7 +42209,7 @@
     </row>
     <row r="572" customFormat="false" ht="43.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A572" s="60" t="s">
-        <v>1365</v>
+        <v>1368</v>
       </c>
       <c r="B572" s="59" t="n">
         <v>14</v>
@@ -42231,7 +42221,7 @@
         <v>268</v>
       </c>
       <c r="E572" s="60" t="s">
-        <v>1173</v>
+        <v>1174</v>
       </c>
       <c r="F572" s="60" t="s">
         <v>254</v>
@@ -42246,7 +42236,7 @@
     </row>
     <row r="573" customFormat="false" ht="57" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A573" s="60" t="s">
-        <v>1365</v>
+        <v>1368</v>
       </c>
       <c r="B573" s="59" t="n">
         <v>15</v>
@@ -42255,10 +42245,10 @@
         <v>274</v>
       </c>
       <c r="D573" s="61" t="s">
-        <v>1366</v>
+        <v>1369</v>
       </c>
       <c r="E573" s="60" t="s">
-        <v>1125</v>
+        <v>1068</v>
       </c>
       <c r="F573" s="60" t="s">
         <v>274</v>
@@ -42273,7 +42263,7 @@
     </row>
     <row r="574" customFormat="false" ht="57" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A574" s="60" t="s">
-        <v>1365</v>
+        <v>1368</v>
       </c>
       <c r="B574" s="59" t="n">
         <v>16</v>
@@ -42285,7 +42275,7 @@
         <v>279</v>
       </c>
       <c r="E574" s="60" t="s">
-        <v>1125</v>
+        <v>1174</v>
       </c>
       <c r="F574" s="60" t="s">
         <v>274</v>
@@ -42300,7 +42290,7 @@
     </row>
     <row r="575" customFormat="false" ht="57" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A575" s="60" t="s">
-        <v>1365</v>
+        <v>1368</v>
       </c>
       <c r="B575" s="59" t="n">
         <v>17</v>
@@ -42309,10 +42299,10 @@
         <v>274</v>
       </c>
       <c r="D575" s="61" t="s">
-        <v>1367</v>
+        <v>1370</v>
       </c>
       <c r="E575" s="60" t="s">
-        <v>1125</v>
+        <v>1068</v>
       </c>
       <c r="F575" s="60" t="s">
         <v>274</v>
@@ -42327,7 +42317,7 @@
     </row>
     <row r="576" customFormat="false" ht="43.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A576" s="60" t="s">
-        <v>1365</v>
+        <v>1368</v>
       </c>
       <c r="B576" s="59" t="n">
         <v>18</v>
@@ -42339,7 +42329,7 @@
         <v>230</v>
       </c>
       <c r="E576" s="60" t="s">
-        <v>1125</v>
+        <v>1174</v>
       </c>
       <c r="F576" s="60" t="s">
         <v>221</v>
@@ -42354,7 +42344,7 @@
     </row>
     <row r="577" customFormat="false" ht="43.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A577" s="60" t="s">
-        <v>1365</v>
+        <v>1368</v>
       </c>
       <c r="B577" s="59" t="n">
         <v>19</v>
@@ -42363,10 +42353,10 @@
         <v>221</v>
       </c>
       <c r="D577" s="61" t="s">
-        <v>1328</v>
+        <v>1331</v>
       </c>
       <c r="E577" s="60" t="s">
-        <v>1173</v>
+        <v>1174</v>
       </c>
       <c r="F577" s="60" t="s">
         <v>221</v>
@@ -42381,7 +42371,7 @@
     </row>
     <row r="578" customFormat="false" ht="43.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A578" s="60" t="s">
-        <v>1365</v>
+        <v>1368</v>
       </c>
       <c r="B578" s="59" t="n">
         <v>20</v>
@@ -42390,10 +42380,10 @@
         <v>221</v>
       </c>
       <c r="D578" s="61" t="s">
-        <v>1329</v>
+        <v>1332</v>
       </c>
       <c r="E578" s="60" t="s">
-        <v>1173</v>
+        <v>1174</v>
       </c>
       <c r="F578" s="60" t="s">
         <v>221</v>
@@ -42408,7 +42398,7 @@
     </row>
     <row r="579" customFormat="false" ht="43.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A579" s="60" t="s">
-        <v>1365</v>
+        <v>1368</v>
       </c>
       <c r="B579" s="59" t="n">
         <v>21</v>
@@ -42420,7 +42410,7 @@
         <v>234</v>
       </c>
       <c r="E579" s="60" t="s">
-        <v>1173</v>
+        <v>1174</v>
       </c>
       <c r="F579" s="60" t="s">
         <v>221</v>
@@ -42435,7 +42425,7 @@
     </row>
     <row r="580" customFormat="false" ht="57" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A580" s="60" t="s">
-        <v>1365</v>
+        <v>1368</v>
       </c>
       <c r="B580" s="59" t="n">
         <v>22</v>
@@ -42444,10 +42434,10 @@
         <v>221</v>
       </c>
       <c r="D580" s="61" t="s">
-        <v>1330</v>
+        <v>1333</v>
       </c>
       <c r="E580" s="60" t="s">
-        <v>1173</v>
+        <v>1174</v>
       </c>
       <c r="F580" s="60" t="s">
         <v>221</v>
@@ -42462,7 +42452,7 @@
     </row>
     <row r="581" customFormat="false" ht="57" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A581" s="60" t="s">
-        <v>1365</v>
+        <v>1368</v>
       </c>
       <c r="B581" s="59" t="n">
         <v>23</v>
@@ -42474,7 +42464,7 @@
         <v>269</v>
       </c>
       <c r="E581" s="60" t="s">
-        <v>1173</v>
+        <v>1174</v>
       </c>
       <c r="F581" s="60" t="s">
         <v>254</v>
@@ -42489,7 +42479,7 @@
     </row>
     <row r="582" customFormat="false" ht="57" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A582" s="60" t="s">
-        <v>1365</v>
+        <v>1368</v>
       </c>
       <c r="B582" s="59" t="n">
         <v>24</v>
@@ -42501,7 +42491,7 @@
         <v>269</v>
       </c>
       <c r="E582" s="60" t="s">
-        <v>1173</v>
+        <v>1174</v>
       </c>
       <c r="F582" s="60" t="s">
         <v>254</v>
@@ -42516,7 +42506,7 @@
     </row>
     <row r="583" customFormat="false" ht="57" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A583" s="60" t="s">
-        <v>1365</v>
+        <v>1368</v>
       </c>
       <c r="B583" s="59" t="n">
         <v>25</v>
@@ -42528,7 +42518,7 @@
         <v>271</v>
       </c>
       <c r="E583" s="60" t="s">
-        <v>1125</v>
+        <v>1174</v>
       </c>
       <c r="F583" s="60" t="s">
         <v>254</v>
@@ -42543,7 +42533,7 @@
     </row>
     <row r="584" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A584" s="60" t="s">
-        <v>1365</v>
+        <v>1368</v>
       </c>
       <c r="B584" s="59" t="n">
         <v>26</v>
@@ -42552,10 +42542,10 @@
         <v>326</v>
       </c>
       <c r="D584" s="61" t="s">
-        <v>1221</v>
+        <v>1223</v>
       </c>
       <c r="E584" s="60" t="s">
-        <v>1173</v>
+        <v>1174</v>
       </c>
       <c r="F584" s="60" t="s">
         <v>326</v>
@@ -42570,7 +42560,7 @@
     </row>
     <row r="585" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A585" s="60" t="s">
-        <v>1365</v>
+        <v>1368</v>
       </c>
       <c r="B585" s="59" t="n">
         <v>27</v>
@@ -42579,10 +42569,10 @@
         <v>326</v>
       </c>
       <c r="D585" s="61" t="s">
-        <v>1331</v>
+        <v>1334</v>
       </c>
       <c r="E585" s="60" t="s">
-        <v>1173</v>
+        <v>1174</v>
       </c>
       <c r="F585" s="60" t="s">
         <v>326</v>
@@ -42597,7 +42587,7 @@
     </row>
     <row r="586" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A586" s="60" t="s">
-        <v>1365</v>
+        <v>1368</v>
       </c>
       <c r="B586" s="59" t="n">
         <v>28</v>
@@ -42609,7 +42599,7 @@
         <v>331</v>
       </c>
       <c r="E586" s="60" t="s">
-        <v>1173</v>
+        <v>1174</v>
       </c>
       <c r="F586" s="60" t="s">
         <v>326</v>
@@ -42624,7 +42614,7 @@
     </row>
     <row r="587" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A587" s="60" t="s">
-        <v>1365</v>
+        <v>1368</v>
       </c>
       <c r="B587" s="59" t="n">
         <v>29</v>
@@ -42633,10 +42623,10 @@
         <v>326</v>
       </c>
       <c r="D587" s="61" t="s">
-        <v>1332</v>
+        <v>1335</v>
       </c>
       <c r="E587" s="60" t="s">
-        <v>1173</v>
+        <v>1174</v>
       </c>
       <c r="F587" s="60" t="s">
         <v>326</v>
@@ -42651,7 +42641,7 @@
     </row>
     <row r="588" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A588" s="60" t="s">
-        <v>1365</v>
+        <v>1368</v>
       </c>
       <c r="B588" s="59" t="n">
         <v>30</v>
@@ -42660,10 +42650,10 @@
         <v>326</v>
       </c>
       <c r="D588" s="61" t="s">
-        <v>1223</v>
+        <v>1225</v>
       </c>
       <c r="E588" s="60" t="s">
-        <v>1173</v>
+        <v>1174</v>
       </c>
       <c r="F588" s="60" t="s">
         <v>326</v>
@@ -42678,7 +42668,7 @@
     </row>
     <row r="589" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A589" s="60" t="s">
-        <v>1365</v>
+        <v>1368</v>
       </c>
       <c r="B589" s="59" t="n">
         <v>31</v>
@@ -42687,10 +42677,10 @@
         <v>326</v>
       </c>
       <c r="D589" s="61" t="s">
-        <v>1333</v>
+        <v>1336</v>
       </c>
       <c r="E589" s="60" t="s">
-        <v>1173</v>
+        <v>1174</v>
       </c>
       <c r="F589" s="60" t="s">
         <v>326</v>
@@ -42705,7 +42695,7 @@
     </row>
     <row r="590" customFormat="false" ht="43.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A590" s="60" t="s">
-        <v>1365</v>
+        <v>1368</v>
       </c>
       <c r="B590" s="59" t="n">
         <v>32</v>
@@ -42717,7 +42707,7 @@
         <v>384</v>
       </c>
       <c r="E590" s="60" t="s">
-        <v>1173</v>
+        <v>1174</v>
       </c>
       <c r="F590" s="60" t="s">
         <v>382</v>
@@ -42732,7 +42722,7 @@
     </row>
     <row r="591" customFormat="false" ht="43.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A591" s="60" t="s">
-        <v>1365</v>
+        <v>1368</v>
       </c>
       <c r="B591" s="59" t="n">
         <v>33</v>
@@ -42744,7 +42734,7 @@
         <v>384</v>
       </c>
       <c r="E591" s="60" t="s">
-        <v>1173</v>
+        <v>1174</v>
       </c>
       <c r="F591" s="60" t="s">
         <v>382</v>
@@ -42759,7 +42749,7 @@
     </row>
     <row r="592" customFormat="false" ht="43.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A592" s="60" t="s">
-        <v>1365</v>
+        <v>1368</v>
       </c>
       <c r="B592" s="59" t="n">
         <v>34</v>
@@ -42768,10 +42758,10 @@
         <v>382</v>
       </c>
       <c r="D592" s="61" t="s">
-        <v>1209</v>
+        <v>1211</v>
       </c>
       <c r="E592" s="60" t="s">
-        <v>1173</v>
+        <v>1174</v>
       </c>
       <c r="F592" s="60" t="s">
         <v>382</v>
@@ -42786,7 +42776,7 @@
     </row>
     <row r="593" customFormat="false" ht="57" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A593" s="60" t="s">
-        <v>1365</v>
+        <v>1368</v>
       </c>
       <c r="B593" s="59" t="n">
         <v>35</v>
@@ -42795,10 +42785,10 @@
         <v>382</v>
       </c>
       <c r="D593" s="61" t="s">
-        <v>1212</v>
+        <v>1214</v>
       </c>
       <c r="E593" s="60" t="s">
-        <v>1173</v>
+        <v>1174</v>
       </c>
       <c r="F593" s="60" t="s">
         <v>382</v>
@@ -42813,7 +42803,7 @@
     </row>
     <row r="594" customFormat="false" ht="43.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A594" s="60" t="s">
-        <v>1365</v>
+        <v>1368</v>
       </c>
       <c r="B594" s="59" t="n">
         <v>36</v>
@@ -42822,10 +42812,10 @@
         <v>382</v>
       </c>
       <c r="D594" s="61" t="s">
-        <v>1209</v>
+        <v>1211</v>
       </c>
       <c r="E594" s="60" t="s">
-        <v>1173</v>
+        <v>1174</v>
       </c>
       <c r="F594" s="60" t="s">
         <v>382</v>
@@ -42840,7 +42830,7 @@
     </row>
     <row r="595" customFormat="false" ht="43.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A595" s="60" t="s">
-        <v>1365</v>
+        <v>1368</v>
       </c>
       <c r="B595" s="59" t="n">
         <v>37</v>
@@ -42852,7 +42842,7 @@
         <v>384</v>
       </c>
       <c r="E595" s="60" t="s">
-        <v>1173</v>
+        <v>1174</v>
       </c>
       <c r="F595" s="60" t="s">
         <v>382</v>
@@ -42867,7 +42857,7 @@
     </row>
     <row r="596" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A596" s="60" t="s">
-        <v>1365</v>
+        <v>1368</v>
       </c>
       <c r="B596" s="59" t="n">
         <v>38</v>
@@ -42876,10 +42866,10 @@
         <v>430</v>
       </c>
       <c r="D596" s="61" t="s">
-        <v>1334</v>
+        <v>1337</v>
       </c>
       <c r="E596" s="60" t="s">
-        <v>1173</v>
+        <v>1174</v>
       </c>
       <c r="F596" s="60" t="s">
         <v>430</v>
@@ -42894,7 +42884,7 @@
     </row>
     <row r="597" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A597" s="60" t="s">
-        <v>1365</v>
+        <v>1368</v>
       </c>
       <c r="B597" s="59" t="n">
         <v>39</v>
@@ -42903,10 +42893,10 @@
         <v>430</v>
       </c>
       <c r="D597" s="61" t="s">
-        <v>1335</v>
+        <v>1338</v>
       </c>
       <c r="E597" s="60" t="s">
-        <v>1173</v>
+        <v>1174</v>
       </c>
       <c r="F597" s="60" t="s">
         <v>430</v>
@@ -42921,7 +42911,7 @@
     </row>
     <row r="598" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A598" s="60" t="s">
-        <v>1365</v>
+        <v>1368</v>
       </c>
       <c r="B598" s="59" t="n">
         <v>40</v>
@@ -42930,10 +42920,10 @@
         <v>430</v>
       </c>
       <c r="D598" s="61" t="s">
-        <v>1336</v>
+        <v>1339</v>
       </c>
       <c r="E598" s="60" t="s">
-        <v>1173</v>
+        <v>1174</v>
       </c>
       <c r="F598" s="60" t="s">
         <v>430</v>
@@ -42948,7 +42938,7 @@
     </row>
     <row r="599" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A599" s="60" t="s">
-        <v>1365</v>
+        <v>1368</v>
       </c>
       <c r="B599" s="59" t="n">
         <v>41</v>
@@ -42957,10 +42947,10 @@
         <v>430</v>
       </c>
       <c r="D599" s="61" t="s">
-        <v>1337</v>
+        <v>1340</v>
       </c>
       <c r="E599" s="60" t="s">
-        <v>1173</v>
+        <v>1174</v>
       </c>
       <c r="F599" s="60" t="s">
         <v>430</v>
@@ -42975,7 +42965,7 @@
     </row>
     <row r="600" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A600" s="60" t="s">
-        <v>1365</v>
+        <v>1368</v>
       </c>
       <c r="B600" s="59" t="n">
         <v>42</v>
@@ -42984,10 +42974,10 @@
         <v>430</v>
       </c>
       <c r="D600" s="61" t="s">
-        <v>1338</v>
+        <v>1341</v>
       </c>
       <c r="E600" s="60" t="s">
-        <v>1173</v>
+        <v>1174</v>
       </c>
       <c r="F600" s="60" t="s">
         <v>430</v>
@@ -43002,7 +42992,7 @@
     </row>
     <row r="601" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A601" s="60" t="s">
-        <v>1365</v>
+        <v>1368</v>
       </c>
       <c r="B601" s="59" t="n">
         <v>43</v>
@@ -43011,10 +43001,10 @@
         <v>430</v>
       </c>
       <c r="D601" s="61" t="s">
-        <v>1339</v>
+        <v>1342</v>
       </c>
       <c r="E601" s="60" t="s">
-        <v>1173</v>
+        <v>1174</v>
       </c>
       <c r="F601" s="60" t="s">
         <v>430</v>
@@ -43029,7 +43019,7 @@
     </row>
     <row r="602" customFormat="false" ht="43.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A602" s="60" t="s">
-        <v>1365</v>
+        <v>1368</v>
       </c>
       <c r="B602" s="59" t="n">
         <v>44</v>
@@ -43038,10 +43028,10 @@
         <v>430</v>
       </c>
       <c r="D602" s="61" t="s">
-        <v>1340</v>
+        <v>1343</v>
       </c>
       <c r="E602" s="60" t="s">
-        <v>1173</v>
+        <v>1174</v>
       </c>
       <c r="F602" s="60" t="s">
         <v>430</v>
@@ -43056,7 +43046,7 @@
     </row>
     <row r="603" customFormat="false" ht="43.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A603" s="60" t="s">
-        <v>1365</v>
+        <v>1368</v>
       </c>
       <c r="B603" s="59" t="n">
         <v>45</v>
@@ -43065,10 +43055,10 @@
         <v>430</v>
       </c>
       <c r="D603" s="61" t="s">
-        <v>1341</v>
+        <v>1344</v>
       </c>
       <c r="E603" s="60" t="s">
-        <v>1173</v>
+        <v>1174</v>
       </c>
       <c r="F603" s="60" t="s">
         <v>430</v>
@@ -43083,7 +43073,7 @@
     </row>
     <row r="604" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A604" s="60" t="s">
-        <v>1365</v>
+        <v>1368</v>
       </c>
       <c r="B604" s="59" t="n">
         <v>46</v>
@@ -43092,10 +43082,10 @@
         <v>430</v>
       </c>
       <c r="D604" s="61" t="s">
-        <v>1342</v>
+        <v>1345</v>
       </c>
       <c r="E604" s="60" t="s">
-        <v>1173</v>
+        <v>1174</v>
       </c>
       <c r="F604" s="60" t="s">
         <v>430</v>
@@ -43110,7 +43100,7 @@
     </row>
     <row r="605" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A605" s="60" t="s">
-        <v>1365</v>
+        <v>1368</v>
       </c>
       <c r="B605" s="59" t="n">
         <v>47</v>
@@ -43119,10 +43109,10 @@
         <v>430</v>
       </c>
       <c r="D605" s="61" t="s">
-        <v>1343</v>
+        <v>1346</v>
       </c>
       <c r="E605" s="60" t="s">
-        <v>1173</v>
+        <v>1174</v>
       </c>
       <c r="F605" s="60" t="s">
         <v>430</v>
@@ -43137,7 +43127,7 @@
     </row>
     <row r="606" customFormat="false" ht="43.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A606" s="60" t="s">
-        <v>1365</v>
+        <v>1368</v>
       </c>
       <c r="B606" s="59" t="n">
         <v>48</v>
@@ -43146,10 +43136,10 @@
         <v>382</v>
       </c>
       <c r="D606" s="61" t="s">
-        <v>1344</v>
+        <v>1347</v>
       </c>
       <c r="E606" s="60" t="s">
-        <v>1173</v>
+        <v>1174</v>
       </c>
       <c r="F606" s="60" t="s">
         <v>382</v>
@@ -43164,7 +43154,7 @@
     </row>
     <row r="607" customFormat="false" ht="43.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A607" s="60" t="s">
-        <v>1365</v>
+        <v>1368</v>
       </c>
       <c r="B607" s="59" t="n">
         <v>49</v>
@@ -43173,7 +43163,7 @@
         <v>382</v>
       </c>
       <c r="D607" s="61" t="s">
-        <v>1345</v>
+        <v>1348</v>
       </c>
       <c r="E607" s="60" t="s">
         <v>1125</v>
@@ -43191,7 +43181,7 @@
     </row>
     <row r="608" customFormat="false" ht="57" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A608" s="60" t="s">
-        <v>1365</v>
+        <v>1368</v>
       </c>
       <c r="B608" s="59" t="n">
         <v>50</v>
@@ -43200,10 +43190,10 @@
         <v>382</v>
       </c>
       <c r="D608" s="61" t="s">
-        <v>1212</v>
+        <v>1214</v>
       </c>
       <c r="E608" s="60" t="s">
-        <v>1173</v>
+        <v>1174</v>
       </c>
       <c r="F608" s="60" t="s">
         <v>382</v>
@@ -43218,7 +43208,7 @@
     </row>
     <row r="609" customFormat="false" ht="57" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A609" s="60" t="s">
-        <v>1365</v>
+        <v>1368</v>
       </c>
       <c r="B609" s="59" t="n">
         <v>51</v>
@@ -43227,10 +43217,10 @@
         <v>238</v>
       </c>
       <c r="D609" s="61" t="s">
-        <v>1322</v>
+        <v>1325</v>
       </c>
       <c r="E609" s="60" t="s">
-        <v>1173</v>
+        <v>1174</v>
       </c>
       <c r="F609" s="60" t="s">
         <v>238</v>
@@ -43245,7 +43235,7 @@
     </row>
     <row r="610" customFormat="false" ht="57" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A610" s="60" t="s">
-        <v>1365</v>
+        <v>1368</v>
       </c>
       <c r="B610" s="59" t="n">
         <v>52</v>
@@ -43254,10 +43244,10 @@
         <v>238</v>
       </c>
       <c r="D610" s="61" t="s">
-        <v>1346</v>
+        <v>1349</v>
       </c>
       <c r="E610" s="60" t="s">
-        <v>1173</v>
+        <v>1174</v>
       </c>
       <c r="F610" s="60" t="s">
         <v>238</v>
@@ -43272,7 +43262,7 @@
     </row>
     <row r="611" customFormat="false" ht="43.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A611" s="60" t="s">
-        <v>1365</v>
+        <v>1368</v>
       </c>
       <c r="B611" s="59" t="n">
         <v>53</v>
@@ -43284,7 +43274,7 @@
         <v>250</v>
       </c>
       <c r="E611" s="60" t="s">
-        <v>1173</v>
+        <v>1174</v>
       </c>
       <c r="F611" s="60" t="s">
         <v>238</v>
@@ -43299,7 +43289,7 @@
     </row>
     <row r="612" customFormat="false" ht="43.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A612" s="60" t="s">
-        <v>1365</v>
+        <v>1368</v>
       </c>
       <c r="B612" s="59" t="n">
         <v>54</v>
@@ -43311,7 +43301,7 @@
         <v>251</v>
       </c>
       <c r="E612" s="60" t="s">
-        <v>1125</v>
+        <v>1174</v>
       </c>
       <c r="F612" s="60" t="s">
         <v>238</v>
@@ -43326,7 +43316,7 @@
     </row>
     <row r="613" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A613" s="60" t="s">
-        <v>1365</v>
+        <v>1368</v>
       </c>
       <c r="B613" s="59" t="n">
         <v>55</v>
@@ -43335,16 +43325,16 @@
         <v>339</v>
       </c>
       <c r="D613" s="61" t="s">
-        <v>1166</v>
+        <v>1167</v>
       </c>
       <c r="E613" s="60" t="s">
-        <v>1173</v>
+        <v>1174</v>
       </c>
       <c r="F613" s="60" t="s">
         <v>339</v>
       </c>
       <c r="G613" s="61" t="s">
-        <v>1166</v>
+        <v>1167</v>
       </c>
       <c r="H613" s="59" t="n">
         <v>180</v>
@@ -43353,7 +43343,7 @@
     </row>
     <row r="614" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A614" s="60" t="s">
-        <v>1365</v>
+        <v>1368</v>
       </c>
       <c r="B614" s="59" t="n">
         <v>56</v>
@@ -43362,16 +43352,16 @@
         <v>339</v>
       </c>
       <c r="D614" s="61" t="s">
-        <v>1167</v>
+        <v>1168</v>
       </c>
       <c r="E614" s="60" t="s">
-        <v>1173</v>
+        <v>1174</v>
       </c>
       <c r="F614" s="60" t="s">
         <v>339</v>
       </c>
       <c r="G614" s="61" t="s">
-        <v>1167</v>
+        <v>1168</v>
       </c>
       <c r="H614" s="59" t="n">
         <v>181</v>
@@ -43380,7 +43370,7 @@
     </row>
     <row r="615" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A615" s="60" t="s">
-        <v>1365</v>
+        <v>1368</v>
       </c>
       <c r="B615" s="59" t="n">
         <v>57</v>
@@ -43389,16 +43379,16 @@
         <v>339</v>
       </c>
       <c r="D615" s="61" t="s">
-        <v>1168</v>
+        <v>1169</v>
       </c>
       <c r="E615" s="60" t="s">
-        <v>1173</v>
+        <v>1174</v>
       </c>
       <c r="F615" s="60" t="s">
         <v>339</v>
       </c>
       <c r="G615" s="61" t="s">
-        <v>1169</v>
+        <v>1170</v>
       </c>
       <c r="H615" s="59" t="n">
         <v>182</v>
@@ -43407,7 +43397,7 @@
     </row>
     <row r="616" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A616" s="60" t="s">
-        <v>1365</v>
+        <v>1368</v>
       </c>
       <c r="B616" s="59" t="n">
         <v>58</v>
@@ -43416,16 +43406,16 @@
         <v>339</v>
       </c>
       <c r="D616" s="61" t="s">
-        <v>1170</v>
+        <v>1171</v>
       </c>
       <c r="E616" s="60" t="s">
-        <v>1173</v>
+        <v>1174</v>
       </c>
       <c r="F616" s="60" t="s">
         <v>339</v>
       </c>
       <c r="G616" s="61" t="s">
-        <v>1170</v>
+        <v>1171</v>
       </c>
       <c r="H616" s="59" t="n">
         <v>183</v>
@@ -43434,7 +43424,7 @@
     </row>
     <row r="617" customFormat="false" ht="16.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A617" s="60" t="s">
-        <v>1365</v>
+        <v>1368</v>
       </c>
       <c r="B617" s="59" t="n">
         <v>59</v>
@@ -43443,16 +43433,16 @@
         <v>339</v>
       </c>
       <c r="D617" s="61" t="s">
-        <v>1171</v>
+        <v>1172</v>
       </c>
       <c r="E617" s="60" t="s">
-        <v>1173</v>
+        <v>1174</v>
       </c>
       <c r="F617" s="60" t="s">
         <v>339</v>
       </c>
       <c r="G617" s="61" t="s">
-        <v>1171</v>
+        <v>1172</v>
       </c>
       <c r="H617" s="59" t="n">
         <v>184</v>
@@ -43461,7 +43451,7 @@
     </row>
     <row r="618" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A618" s="60" t="s">
-        <v>1365</v>
+        <v>1368</v>
       </c>
       <c r="B618" s="59" t="n">
         <v>60</v>
@@ -43473,7 +43463,7 @@
         <v>352</v>
       </c>
       <c r="E618" s="60" t="s">
-        <v>1173</v>
+        <v>1174</v>
       </c>
       <c r="F618" s="60" t="s">
         <v>349</v>
@@ -43488,7 +43478,7 @@
     </row>
     <row r="619" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A619" s="60" t="s">
-        <v>1365</v>
+        <v>1368</v>
       </c>
       <c r="B619" s="59" t="n">
         <v>61</v>
@@ -43497,10 +43487,10 @@
         <v>349</v>
       </c>
       <c r="D619" s="61" t="s">
-        <v>1172</v>
+        <v>1173</v>
       </c>
       <c r="E619" s="60" t="s">
-        <v>1173</v>
+        <v>1174</v>
       </c>
       <c r="F619" s="60" t="s">
         <v>349</v>
@@ -43515,7 +43505,7 @@
     </row>
     <row r="620" customFormat="false" ht="16.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A620" s="60" t="s">
-        <v>1365</v>
+        <v>1368</v>
       </c>
       <c r="B620" s="59" t="n">
         <v>62</v>
@@ -43527,7 +43517,7 @@
         <v>354</v>
       </c>
       <c r="E620" s="60" t="s">
-        <v>1173</v>
+        <v>1174</v>
       </c>
       <c r="F620" s="60" t="s">
         <v>349</v>
@@ -43542,7 +43532,7 @@
     </row>
     <row r="621" customFormat="false" ht="16.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A621" s="60" t="s">
-        <v>1365</v>
+        <v>1368</v>
       </c>
       <c r="B621" s="59" t="n">
         <v>63</v>
@@ -43554,7 +43544,7 @@
         <v>361</v>
       </c>
       <c r="E621" s="60" t="s">
-        <v>1173</v>
+        <v>1174</v>
       </c>
       <c r="F621" s="60" t="s">
         <v>360</v>
@@ -43569,7 +43559,7 @@
     </row>
     <row r="622" customFormat="false" ht="16.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A622" s="60" t="s">
-        <v>1365</v>
+        <v>1368</v>
       </c>
       <c r="B622" s="59" t="n">
         <v>64</v>
@@ -43581,7 +43571,7 @@
         <v>363</v>
       </c>
       <c r="E622" s="60" t="s">
-        <v>1173</v>
+        <v>1174</v>
       </c>
       <c r="F622" s="60" t="s">
         <v>360</v>
@@ -43596,7 +43586,7 @@
     </row>
     <row r="623" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A623" s="60" t="s">
-        <v>1365</v>
+        <v>1368</v>
       </c>
       <c r="B623" s="59" t="n">
         <v>65</v>
@@ -43605,10 +43595,10 @@
         <v>369</v>
       </c>
       <c r="D623" s="61" t="s">
+        <v>1175</v>
+      </c>
+      <c r="E623" s="60" t="s">
         <v>1174</v>
-      </c>
-      <c r="E623" s="60" t="s">
-        <v>1173</v>
       </c>
       <c r="F623" s="60" t="s">
         <v>369</v>
@@ -43623,7 +43613,7 @@
     </row>
     <row r="624" customFormat="false" ht="43.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A624" s="60" t="s">
-        <v>1365</v>
+        <v>1368</v>
       </c>
       <c r="B624" s="59" t="n">
         <v>66</v>
@@ -43635,7 +43625,7 @@
         <v>361</v>
       </c>
       <c r="E624" s="60" t="s">
-        <v>1125</v>
+        <v>1158</v>
       </c>
       <c r="F624" s="60" t="s">
         <v>360</v>
@@ -43647,12 +43637,12 @@
         <v>191</v>
       </c>
       <c r="I624" s="61" t="s">
-        <v>1175</v>
+        <v>1176</v>
       </c>
     </row>
     <row r="625" customFormat="false" ht="43.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A625" s="60" t="s">
-        <v>1365</v>
+        <v>1368</v>
       </c>
       <c r="B625" s="59" t="n">
         <v>67</v>
@@ -43664,7 +43654,7 @@
         <v>363</v>
       </c>
       <c r="E625" s="60" t="s">
-        <v>1125</v>
+        <v>1158</v>
       </c>
       <c r="F625" s="60" t="s">
         <v>360</v>
@@ -43676,12 +43666,12 @@
         <v>192</v>
       </c>
       <c r="I625" s="61" t="s">
-        <v>1175</v>
+        <v>1176</v>
       </c>
     </row>
     <row r="626" customFormat="false" ht="16.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A626" s="60" t="s">
-        <v>1365</v>
+        <v>1368</v>
       </c>
       <c r="B626" s="59" t="n">
         <v>68</v>
@@ -43693,7 +43683,7 @@
         <v>318</v>
       </c>
       <c r="E626" s="60" t="s">
-        <v>1173</v>
+        <v>1174</v>
       </c>
       <c r="F626" s="60" t="s">
         <v>313</v>
@@ -43708,7 +43698,7 @@
     </row>
     <row r="627" customFormat="false" ht="16.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A627" s="60" t="s">
-        <v>1365</v>
+        <v>1368</v>
       </c>
       <c r="B627" s="59" t="n">
         <v>69</v>
@@ -43717,10 +43707,10 @@
         <v>313</v>
       </c>
       <c r="D627" s="61" t="s">
-        <v>1347</v>
+        <v>1350</v>
       </c>
       <c r="E627" s="60" t="s">
-        <v>1173</v>
+        <v>1174</v>
       </c>
       <c r="F627" s="60" t="s">
         <v>313</v>
@@ -43735,7 +43725,7 @@
     </row>
     <row r="628" customFormat="false" ht="16.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A628" s="60" t="s">
-        <v>1365</v>
+        <v>1368</v>
       </c>
       <c r="B628" s="59" t="n">
         <v>70</v>
@@ -43744,10 +43734,10 @@
         <v>313</v>
       </c>
       <c r="D628" s="61" t="s">
-        <v>1348</v>
+        <v>1351</v>
       </c>
       <c r="E628" s="60" t="s">
-        <v>1173</v>
+        <v>1174</v>
       </c>
       <c r="F628" s="60" t="s">
         <v>313</v>
@@ -43762,7 +43752,7 @@
     </row>
     <row r="629" customFormat="false" ht="16.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A629" s="60" t="s">
-        <v>1365</v>
+        <v>1368</v>
       </c>
       <c r="B629" s="59" t="n">
         <v>71</v>
@@ -43807,102 +43797,102 @@
   <sheetData>
     <row r="1" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="50" t="s">
-        <v>1368</v>
+        <v>1371</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="63" t="s">
-        <v>1369</v>
+        <v>1372</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="36.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B4" s="64" t="s">
-        <v>1370</v>
+        <v>1373</v>
       </c>
       <c r="C4" s="55" t="s">
-        <v>1371</v>
+        <v>1374</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="20.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B5" s="64" t="s">
-        <v>1372</v>
+        <v>1375</v>
       </c>
       <c r="C5" s="65" t="s">
-        <v>1373</v>
+        <v>1376</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="36.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B6" s="64" t="s">
-        <v>1374</v>
+        <v>1377</v>
       </c>
       <c r="C6" s="65" t="s">
-        <v>1375</v>
+        <v>1378</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="53.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B7" s="64" t="s">
-        <v>1376</v>
+        <v>1379</v>
       </c>
       <c r="C7" s="55" t="s">
-        <v>1377</v>
+        <v>1380</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="63" t="s">
-        <v>1378</v>
+        <v>1381</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="20.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B10" s="64" t="s">
-        <v>1379</v>
+        <v>1382</v>
       </c>
       <c r="C10" s="55" t="s">
-        <v>1380</v>
+        <v>1383</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="20.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B11" s="64" t="s">
-        <v>1381</v>
+        <v>1384</v>
       </c>
       <c r="C11" s="55" t="s">
-        <v>1382</v>
+        <v>1385</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="36.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B12" s="64" t="s">
-        <v>1383</v>
+        <v>1386</v>
       </c>
       <c r="C12" s="55" t="s">
-        <v>1384</v>
+        <v>1387</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="36.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B13" s="64" t="s">
-        <v>1385</v>
+        <v>1388</v>
       </c>
       <c r="C13" s="55" t="s">
-        <v>1386</v>
+        <v>1389</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="63" t="s">
-        <v>1387</v>
+        <v>1390</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="20.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B16" s="64" t="s">
-        <v>1388</v>
+        <v>1391</v>
       </c>
       <c r="C16" s="55" t="s">
-        <v>1389</v>
+        <v>1392</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="36.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B17" s="64" t="s">
-        <v>1390</v>
+        <v>1393</v>
       </c>
       <c r="C17" s="55" t="s">
-        <v>1391</v>
+        <v>1394</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="36.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -43910,23 +43900,23 @@
         <v>299</v>
       </c>
       <c r="C18" s="55" t="s">
-        <v>1392</v>
+        <v>1395</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="53.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B19" s="64" t="s">
-        <v>1393</v>
+        <v>1396</v>
       </c>
       <c r="C19" s="55" t="s">
-        <v>1394</v>
+        <v>1397</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="20.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B20" s="64" t="s">
-        <v>1395</v>
+        <v>1398</v>
       </c>
       <c r="C20" s="55" t="s">
-        <v>1396</v>
+        <v>1399</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="36.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -43934,28 +43924,28 @@
         <v>817</v>
       </c>
       <c r="C21" s="55" t="s">
-        <v>1397</v>
+        <v>1400</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="63" t="s">
-        <v>1398</v>
+        <v>1401</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="36.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B24" s="64" t="s">
-        <v>1388</v>
+        <v>1391</v>
       </c>
       <c r="C24" s="55" t="s">
-        <v>1399</v>
+        <v>1402</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="53.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B25" s="64" t="s">
-        <v>1390</v>
+        <v>1393</v>
       </c>
       <c r="C25" s="55" t="s">
-        <v>1400</v>
+        <v>1403</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="36.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -43963,52 +43953,52 @@
         <v>299</v>
       </c>
       <c r="C26" s="55" t="s">
-        <v>1401</v>
+        <v>1404</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="20.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B27" s="64" t="s">
-        <v>1393</v>
+        <v>1396</v>
       </c>
       <c r="C27" s="55" t="s">
-        <v>1402</v>
+        <v>1405</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="20.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B28" s="64" t="s">
-        <v>1395</v>
+        <v>1398</v>
       </c>
       <c r="C28" s="55" t="s">
-        <v>1403</v>
+        <v>1406</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="20.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B29" s="64" t="s">
-        <v>1404</v>
+        <v>1407</v>
       </c>
       <c r="C29" s="55" t="s">
-        <v>1405</v>
+        <v>1408</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A31" s="63" t="s">
-        <v>1406</v>
+        <v>1409</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="53.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B32" s="64" t="s">
-        <v>1407</v>
+        <v>1410</v>
       </c>
       <c r="C32" s="65" t="s">
-        <v>1408</v>
+        <v>1411</v>
       </c>
     </row>
     <row r="33" customFormat="false" ht="36.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B33" s="64" t="s">
-        <v>1409</v>
+        <v>1412</v>
       </c>
       <c r="C33" s="55" t="s">
-        <v>1410</v>
+        <v>1413</v>
       </c>
     </row>
   </sheetData>

--- a/dictionary/ユーザー辞書_統合版_公開用.xlsx
+++ b/dictionary/ユーザー辞書_統合版_公開用.xlsx
@@ -6138,7 +6138,7 @@
     <t xml:space="preserve">つむぐ</t>
   </si>
   <si>
-    <t xml:space="preserve">ケアプランセンター紡ぐ</t>
+    <t xml:space="preserve">ケアプランサービス紡ぐ</t>
   </si>
   <si>
     <t xml:space="preserve">はくあいえん</t>

--- a/dictionary/ユーザー辞書_統合版_公開用.xlsx
+++ b/dictionary/ユーザー辞書_統合版_公開用.xlsx
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7955" uniqueCount="1588">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7955" uniqueCount="1589">
   <si>
     <r>
       <rPr>
@@ -144,7 +144,7 @@
         <rFont val="WenQuanYi Zen Hei"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">件（うち選定理由・提案理由・留意事項・担当者会議・モニタリング・相談記録 </t>
+      <t xml:space="preserve">件（うち選定理由・提案理由・留意事項・ケアマネージャーとの相談記録・モニタリング・相談内容 </t>
     </r>
     <r>
       <rPr>
@@ -2137,7 +2137,7 @@
         <rFont val="WenQuanYi Zen Hei"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">担当者会議</t>
+      <t xml:space="preserve">ケアマネージャーとの相談記録</t>
     </r>
   </si>
   <si>
@@ -4339,7 +4339,7 @@
         <rFont val="WenQuanYi Zen Hei"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">相談記録（ご本人の声）</t>
+      <t xml:space="preserve">相談内容（ご本人の声）</t>
     </r>
   </si>
   <si>
@@ -6820,7 +6820,7 @@
     <t xml:space="preserve">ドラッグ＆ドロップ</t>
   </si>
   <si>
-    <t xml:space="preserve">よみ早見表（選定理由・留意事項・担当者会議・モニタリング・相談記録）</t>
+    <t xml:space="preserve">よみ早見表（選定理由・提案理由・留意事項・ケアマネージャーとの相談記録・モニタリング・相談内容）</t>
   </si>
   <si>
     <t xml:space="preserve">よみを入力して変換すると、同じよみの文章がすべて候補に出ます。「件数」は辞書一覧から自動で数えています。</t>
@@ -6892,7 +6892,7 @@
     </r>
   </si>
   <si>
-    <t xml:space="preserve">■ 担当者会議</t>
+    <t xml:space="preserve">■ ケアマネージャーとの相談記録</t>
   </si>
   <si>
     <t xml:space="preserve">会議の種類</t>
@@ -6904,7 +6904,7 @@
     <t xml:space="preserve">記入欄</t>
   </si>
   <si>
-    <t xml:space="preserve">■ 相談記録（ご本人の言葉）</t>
+    <t xml:space="preserve">■ 相談内容（ご本人の言葉）</t>
   </si>
   <si>
     <t xml:space="preserve">種類</t>
@@ -7138,7 +7138,7 @@
     <t xml:space="preserve">したん</t>
   </si>
   <si>
-    <t xml:space="preserve">担当者会議（新規）</t>
+    <t xml:space="preserve">ケアマネージャーとの相談記録（新規）</t>
   </si>
   <si>
     <t xml:space="preserve">しんそう</t>
@@ -7150,7 +7150,7 @@
     <t xml:space="preserve">ちゅたん</t>
   </si>
   <si>
-    <t xml:space="preserve">担当者会議（中間見直し）</t>
+    <t xml:space="preserve">ケアマネージャーとの相談記録（中間見直し）</t>
   </si>
   <si>
     <t xml:space="preserve">ちゅうかんぷらん</t>
@@ -7165,7 +7165,7 @@
     <t xml:space="preserve">こうたん</t>
   </si>
   <si>
-    <t xml:space="preserve">担当者会議（更新）</t>
+    <t xml:space="preserve">ケアマネージャーとの相談記録（更新）</t>
   </si>
   <si>
     <t xml:space="preserve">こたん</t>
@@ -7183,25 +7183,25 @@
     <t xml:space="preserve">ついたん</t>
   </si>
   <si>
-    <t xml:space="preserve">担当者会議（福祉用具追加）</t>
+    <t xml:space="preserve">ケアマネージャーとの相談記録（福祉用具追加）</t>
   </si>
   <si>
     <t xml:space="preserve">ついそう</t>
   </si>
   <si>
-    <t xml:space="preserve">担当者会議（サービス内容変更）</t>
+    <t xml:space="preserve">ケアマネージャーとの相談記録（サービス内容変更）</t>
   </si>
   <si>
     <t xml:space="preserve">ちょうき</t>
   </si>
   <si>
-    <t xml:space="preserve">担当者会議（ケアプラン長期切れ）</t>
+    <t xml:space="preserve">ケアマネージャーとの相談記録（ケアプラン長期切れ）</t>
   </si>
   <si>
     <t xml:space="preserve">ぷらんみなおし</t>
   </si>
   <si>
-    <t xml:space="preserve">担当者会議（不要・理由の記載）</t>
+    <t xml:space="preserve">ケアマネージャーとの相談記録（不要・理由の記載）</t>
   </si>
   <si>
     <t xml:space="preserve">にんてい</t>
@@ -7321,7 +7321,7 @@
     <t xml:space="preserve">このふく</t>
   </si>
   <si>
-    <t xml:space="preserve">相談記録（ご本人の声）（ご本人の言葉）</t>
+    <t xml:space="preserve">相談内容（ご本人の言葉）</t>
   </si>
   <si>
     <r>
@@ -9411,7 +9411,7 @@
         <rFont val="WenQuanYi Zen Hei"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">福祉用具貸与の計画書・記録で使う文章（選定理由・留意事項・担当者会議・モニタリング・相談記録）と、事業所名・定型文などの辞書登録を</t>
+      <t xml:space="preserve">福祉用具貸与の計画書・記録で使う文章（選定理由・提案理由・留意事項・ケアマネージャーとの相談記録・モニタリング・相談内容）と、事業所名・定型文などの辞書登録を</t>
     </r>
     <r>
       <rPr>
@@ -9731,7 +9731,7 @@
         <rFont val="WenQuanYi Zen Hei"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">件ずつ、担当者会議は各種類に</t>
+      <t xml:space="preserve">件ずつ、提案理由（手すり）に</t>
     </r>
     <r>
       <rPr>
@@ -9748,7 +9748,7 @@
         <rFont val="WenQuanYi Zen Hei"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">件ずつ、モニタリングは各記入欄に</t>
+      <t xml:space="preserve">件、ケアマネージャーとの相談記録は各種類に</t>
     </r>
     <r>
       <rPr>
@@ -9765,7 +9765,24 @@
         <rFont val="WenQuanYi Zen Hei"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">件ずつ、相談記録に</t>
+      <t xml:space="preserve">件ずつ、モニタリングは各記入欄に</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="游ゴシック"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">3</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">件ずつ、相談内容に</t>
     </r>
     <r>
       <rPr>
@@ -10167,6 +10184,9 @@
     <t xml:space="preserve">用具名＋「りゅ」　例：てすりりゅ／しゃわーちぇありゅ／べっどりゅ　（福祉用具全般の共通の文は「りゅうい」）</t>
   </si>
   <si>
+    <t xml:space="preserve">ケアマネージャーとの相談記録</t>
+  </si>
+  <si>
     <t xml:space="preserve">しんきたんかい（新規）／ちゅうかんたんかい（中間見直し）／こうしんたんかい（更新）／ついかたんかい（福祉用具追加）／へんこうたんかい（サービス内容変更）／ちょうきたんかい（長期切れ）</t>
   </si>
   <si>
@@ -10200,7 +10220,7 @@
     </r>
   </si>
   <si>
-    <t xml:space="preserve">相談記録</t>
+    <t xml:space="preserve">相談内容</t>
   </si>
   <si>
     <t xml:space="preserve">そうだんきろく（ご本人の言葉）</t>
@@ -10265,7 +10285,7 @@
     </r>
   </si>
   <si>
-    <t xml:space="preserve">担当者が会議の内容を記録する文（です・ます調）。「更新担当者会議。〜」で始まる短い文は、である調のメモ用です。</t>
+    <t xml:space="preserve">担当者会議などで、ケアマネージャーや関係者と相談・確認した内容を担当者が記録する文（です・ます調）。「更新担当者会議。〜」で始まる短い文は、である調のメモ用です。</t>
   </si>
   <si>
     <t xml:space="preserve">担当者がモニタリングの結果をケアマネジャー等へ報告・記録する文。</t>
@@ -18645,7 +18665,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="237" customFormat="false" ht="20.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="237" customFormat="false" ht="36.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A237" s="32" t="n">
         <v>233</v>
       </c>
@@ -19017,7 +19037,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="249" customFormat="false" ht="20.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="249" customFormat="false" ht="36.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A249" s="32" t="n">
         <v>245</v>
       </c>
@@ -19420,7 +19440,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="262" customFormat="false" ht="20.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="262" customFormat="false" ht="36.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A262" s="32" t="n">
         <v>258</v>
       </c>
@@ -19916,7 +19936,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="278" customFormat="false" ht="20.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="278" customFormat="false" ht="36.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A278" s="32" t="n">
         <v>274</v>
       </c>
@@ -20040,7 +20060,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="282" customFormat="false" ht="20.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="282" customFormat="false" ht="36.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A282" s="32" t="n">
         <v>278</v>
       </c>
@@ -20102,7 +20122,7 @@
         <v>423</v>
       </c>
     </row>
-    <row r="284" customFormat="false" ht="20.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="284" customFormat="false" ht="36.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A284" s="32" t="n">
         <v>280</v>
       </c>
@@ -20133,7 +20153,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="285" customFormat="false" ht="20.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="285" customFormat="false" ht="36.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A285" s="32" t="n">
         <v>281</v>
       </c>
@@ -20164,7 +20184,7 @@
         <v>428</v>
       </c>
     </row>
-    <row r="286" customFormat="false" ht="20.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="286" customFormat="false" ht="36.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A286" s="32" t="n">
         <v>282</v>
       </c>
@@ -23636,7 +23656,7 @@
         <v>206</v>
       </c>
     </row>
-    <row r="398" customFormat="false" ht="20.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="398" customFormat="false" ht="36.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A398" s="46" t="n">
         <v>394</v>
       </c>
@@ -24132,7 +24152,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="414" customFormat="false" ht="20.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="414" customFormat="false" ht="36.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A414" s="49" t="n">
         <v>410</v>
       </c>
@@ -24163,7 +24183,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="415" customFormat="false" ht="20.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="415" customFormat="false" ht="36.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A415" s="52" t="n">
         <v>411</v>
       </c>
@@ -24225,7 +24245,7 @@
         <v>645</v>
       </c>
     </row>
-    <row r="417" customFormat="false" ht="20.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="417" customFormat="false" ht="36.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A417" s="52" t="n">
         <v>413</v>
       </c>
@@ -24256,7 +24276,7 @@
         <v>647</v>
       </c>
     </row>
-    <row r="418" customFormat="false" ht="20.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="418" customFormat="false" ht="36.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A418" s="52" t="n">
         <v>414</v>
       </c>
@@ -24287,7 +24307,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="419" customFormat="false" ht="20.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="419" customFormat="false" ht="36.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A419" s="52" t="n">
         <v>415</v>
       </c>
@@ -24349,7 +24369,7 @@
         <v>652</v>
       </c>
     </row>
-    <row r="421" customFormat="false" ht="20.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="421" customFormat="false" ht="36.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A421" s="52" t="n">
         <v>417</v>
       </c>
@@ -24380,7 +24400,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="422" customFormat="false" ht="20.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="422" customFormat="false" ht="36.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A422" s="52" t="n">
         <v>418</v>
       </c>
@@ -24411,7 +24431,7 @@
         <v>660</v>
       </c>
     </row>
-    <row r="423" customFormat="false" ht="20.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="423" customFormat="false" ht="36.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A423" s="52" t="n">
         <v>419</v>
       </c>
@@ -24690,7 +24710,7 @@
         <v>676</v>
       </c>
     </row>
-    <row r="432" customFormat="false" ht="20.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="432" customFormat="false" ht="36.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A432" s="52" t="n">
         <v>428</v>
       </c>
@@ -24721,7 +24741,7 @@
         <v>652</v>
       </c>
     </row>
-    <row r="433" customFormat="false" ht="20.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="433" customFormat="false" ht="36.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A433" s="52" t="n">
         <v>429</v>
       </c>
@@ -24783,7 +24803,7 @@
         <v>683</v>
       </c>
     </row>
-    <row r="435" customFormat="false" ht="20.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="435" customFormat="false" ht="36.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A435" s="52" t="n">
         <v>431</v>
       </c>
@@ -24814,7 +24834,7 @@
         <v>652</v>
       </c>
     </row>
-    <row r="436" customFormat="false" ht="20.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="436" customFormat="false" ht="36.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A436" s="52" t="n">
         <v>432</v>
       </c>
@@ -24845,7 +24865,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="437" customFormat="false" ht="20.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="437" customFormat="false" ht="36.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A437" s="52" t="n">
         <v>433</v>
       </c>
@@ -24938,7 +24958,7 @@
         <v>694</v>
       </c>
     </row>
-    <row r="440" customFormat="false" ht="20.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="440" customFormat="false" ht="36.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A440" s="52" t="n">
         <v>436</v>
       </c>
@@ -24969,7 +24989,7 @@
         <v>696</v>
       </c>
     </row>
-    <row r="441" customFormat="false" ht="20.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="441" customFormat="false" ht="36.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A441" s="52" t="n">
         <v>437</v>
       </c>
@@ -25000,7 +25020,7 @@
         <v>652</v>
       </c>
     </row>
-    <row r="442" customFormat="false" ht="20.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="442" customFormat="false" ht="36.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A442" s="52" t="n">
         <v>438</v>
       </c>
@@ -26395,7 +26415,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="487" customFormat="false" ht="20.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="487" customFormat="false" ht="36.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A487" s="49" t="n">
         <v>483</v>
       </c>
@@ -26426,7 +26446,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="488" customFormat="false" ht="20.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="488" customFormat="false" ht="36.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A488" s="52" t="n">
         <v>484</v>
       </c>
@@ -26457,7 +26477,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="489" customFormat="false" ht="20.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="489" customFormat="false" ht="36.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A489" s="52" t="n">
         <v>485</v>
       </c>
@@ -26488,7 +26508,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="490" customFormat="false" ht="20.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="490" customFormat="false" ht="36.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A490" s="52" t="n">
         <v>486</v>
       </c>
@@ -26519,7 +26539,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="491" customFormat="false" ht="20.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="491" customFormat="false" ht="36.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A491" s="52" t="n">
         <v>487</v>
       </c>
@@ -26550,7 +26570,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="492" customFormat="false" ht="20.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="492" customFormat="false" ht="36.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A492" s="52" t="n">
         <v>488</v>
       </c>
@@ -26581,7 +26601,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="493" customFormat="false" ht="20.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="493" customFormat="false" ht="36.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A493" s="52" t="n">
         <v>489</v>
       </c>
@@ -26612,7 +26632,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="494" customFormat="false" ht="20.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="494" customFormat="false" ht="36.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A494" s="52" t="n">
         <v>490</v>
       </c>
@@ -26643,7 +26663,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="495" customFormat="false" ht="20.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="495" customFormat="false" ht="36.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A495" s="52" t="n">
         <v>491</v>
       </c>
@@ -26674,7 +26694,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="496" customFormat="false" ht="20.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="496" customFormat="false" ht="36.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A496" s="52" t="n">
         <v>492</v>
       </c>
@@ -26705,7 +26725,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="497" customFormat="false" ht="20.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="497" customFormat="false" ht="36.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A497" s="52" t="n">
         <v>493</v>
       </c>
@@ -26736,7 +26756,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="498" customFormat="false" ht="20.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="498" customFormat="false" ht="36.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A498" s="52" t="n">
         <v>494</v>
       </c>
@@ -26767,7 +26787,7 @@
         <v>815</v>
       </c>
     </row>
-    <row r="499" customFormat="false" ht="20.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="499" customFormat="false" ht="36.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A499" s="52" t="n">
         <v>495</v>
       </c>
@@ -26798,7 +26818,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="500" customFormat="false" ht="20.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="500" customFormat="false" ht="36.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A500" s="52" t="n">
         <v>496</v>
       </c>
@@ -26829,7 +26849,7 @@
         <v>819</v>
       </c>
     </row>
-    <row r="501" customFormat="false" ht="20.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="501" customFormat="false" ht="36.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A501" s="52" t="n">
         <v>497</v>
       </c>
@@ -26860,7 +26880,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="502" customFormat="false" ht="20.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="502" customFormat="false" ht="36.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A502" s="52" t="n">
         <v>498</v>
       </c>
@@ -26891,7 +26911,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="503" customFormat="false" ht="20.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="503" customFormat="false" ht="36.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A503" s="52" t="n">
         <v>499</v>
       </c>
@@ -26922,7 +26942,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="504" customFormat="false" ht="20.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="504" customFormat="false" ht="36.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A504" s="52" t="n">
         <v>500</v>
       </c>
@@ -26953,7 +26973,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="505" customFormat="false" ht="20.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="505" customFormat="false" ht="36.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A505" s="52" t="n">
         <v>501</v>
       </c>
@@ -26984,7 +27004,7 @@
         <v>652</v>
       </c>
     </row>
-    <row r="506" customFormat="false" ht="20.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="506" customFormat="false" ht="36.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A506" s="52" t="n">
         <v>502</v>
       </c>
@@ -27046,7 +27066,7 @@
         <v>834</v>
       </c>
     </row>
-    <row r="508" customFormat="false" ht="20.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="508" customFormat="false" ht="36.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A508" s="52" t="n">
         <v>504</v>
       </c>
@@ -27077,7 +27097,7 @@
         <v>836</v>
       </c>
     </row>
-    <row r="509" customFormat="false" ht="20.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="509" customFormat="false" ht="36.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A509" s="52" t="n">
         <v>505</v>
       </c>
@@ -27108,7 +27128,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="510" customFormat="false" ht="20.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="510" customFormat="false" ht="36.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A510" s="49" t="n">
         <v>506</v>
       </c>
@@ -27139,7 +27159,7 @@
         <v>652</v>
       </c>
     </row>
-    <row r="511" customFormat="false" ht="20.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="511" customFormat="false" ht="36.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A511" s="52" t="n">
         <v>507</v>
       </c>
@@ -27170,7 +27190,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="512" customFormat="false" ht="20.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="512" customFormat="false" ht="36.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A512" s="52" t="n">
         <v>508</v>
       </c>
@@ -27201,7 +27221,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="513" customFormat="false" ht="20.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="513" customFormat="false" ht="36.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A513" s="52" t="n">
         <v>509</v>
       </c>
@@ -27232,7 +27252,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="514" customFormat="false" ht="20.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="514" customFormat="false" ht="36.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A514" s="52" t="n">
         <v>510</v>
       </c>
@@ -28720,7 +28740,7 @@
         <v>455</v>
       </c>
     </row>
-    <row r="562" customFormat="false" ht="20.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="562" customFormat="false" ht="36.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A562" s="52" t="n">
         <v>558</v>
       </c>
@@ -28751,7 +28771,7 @@
         <v>955</v>
       </c>
     </row>
-    <row r="563" customFormat="false" ht="20.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="563" customFormat="false" ht="36.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A563" s="52" t="n">
         <v>559</v>
       </c>
@@ -28782,7 +28802,7 @@
         <v>957</v>
       </c>
     </row>
-    <row r="564" customFormat="false" ht="20.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="564" customFormat="false" ht="36.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A564" s="52" t="n">
         <v>560</v>
       </c>
@@ -28813,7 +28833,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="565" customFormat="false" ht="20.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="565" customFormat="false" ht="36.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A565" s="52" t="n">
         <v>561</v>
       </c>
@@ -28844,7 +28864,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="566" customFormat="false" ht="20.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="566" customFormat="false" ht="36.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A566" s="52" t="n">
         <v>562</v>
       </c>
@@ -28968,7 +28988,7 @@
         <v>968</v>
       </c>
     </row>
-    <row r="570" customFormat="false" ht="20.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="570" customFormat="false" ht="36.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A570" s="52" t="n">
         <v>566</v>
       </c>
@@ -28999,7 +29019,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="571" customFormat="false" ht="20.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="571" customFormat="false" ht="36.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A571" s="52" t="n">
         <v>567</v>
       </c>
@@ -29030,7 +29050,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="572" customFormat="false" ht="20.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="572" customFormat="false" ht="36.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A572" s="52" t="n">
         <v>568</v>
       </c>
@@ -29061,7 +29081,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="573" customFormat="false" ht="20.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="573" customFormat="false" ht="36.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A573" s="52" t="n">
         <v>569</v>
       </c>
@@ -29092,7 +29112,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="574" customFormat="false" ht="20.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="574" customFormat="false" ht="36.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A574" s="52" t="n">
         <v>570</v>
       </c>
@@ -29123,7 +29143,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="575" customFormat="false" ht="20.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="575" customFormat="false" ht="36.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A575" s="52" t="n">
         <v>571</v>
       </c>
@@ -29154,7 +29174,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="576" customFormat="false" ht="20.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="576" customFormat="false" ht="36.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A576" s="52" t="n">
         <v>572</v>
       </c>
@@ -29185,7 +29205,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="577" customFormat="false" ht="20.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="577" customFormat="false" ht="36.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A577" s="52" t="n">
         <v>573</v>
       </c>
@@ -29216,7 +29236,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="578" customFormat="false" ht="20.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="578" customFormat="false" ht="36.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A578" s="49" t="n">
         <v>574</v>
       </c>
@@ -29247,7 +29267,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="579" customFormat="false" ht="20.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="579" customFormat="false" ht="36.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A579" s="52" t="n">
         <v>575</v>
       </c>
@@ -29278,7 +29298,7 @@
         <v>992</v>
       </c>
     </row>
-    <row r="580" customFormat="false" ht="20.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="580" customFormat="false" ht="36.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A580" s="52" t="n">
         <v>576</v>
       </c>
@@ -29309,7 +29329,7 @@
         <v>992</v>
       </c>
     </row>
-    <row r="581" customFormat="false" ht="20.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="581" customFormat="false" ht="36.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A581" s="52" t="n">
         <v>577</v>
       </c>
@@ -29340,7 +29360,7 @@
         <v>995</v>
       </c>
     </row>
-    <row r="582" customFormat="false" ht="20.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="582" customFormat="false" ht="36.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A582" s="52" t="n">
         <v>578</v>
       </c>
@@ -29371,7 +29391,7 @@
         <v>995</v>
       </c>
     </row>
-    <row r="583" customFormat="false" ht="20.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="583" customFormat="false" ht="36.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A583" s="52" t="n">
         <v>579</v>
       </c>
@@ -29402,7 +29422,7 @@
         <v>998</v>
       </c>
     </row>
-    <row r="584" customFormat="false" ht="20.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="584" customFormat="false" ht="36.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A584" s="52" t="n">
         <v>580</v>
       </c>
@@ -29433,7 +29453,7 @@
         <v>1000</v>
       </c>
     </row>
-    <row r="585" customFormat="false" ht="20.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="585" customFormat="false" ht="36.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A585" s="52" t="n">
         <v>581</v>
       </c>
@@ -29464,7 +29484,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="586" customFormat="false" ht="20.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="586" customFormat="false" ht="36.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A586" s="52" t="n">
         <v>582</v>
       </c>
@@ -29495,7 +29515,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="587" customFormat="false" ht="20.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="587" customFormat="false" ht="36.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A587" s="52" t="n">
         <v>583</v>
       </c>
@@ -29526,7 +29546,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="588" customFormat="false" ht="20.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="588" customFormat="false" ht="36.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A588" s="52" t="n">
         <v>584</v>
       </c>
@@ -29557,7 +29577,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="589" customFormat="false" ht="20.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="589" customFormat="false" ht="36.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A589" s="52" t="n">
         <v>585</v>
       </c>
@@ -29588,7 +29608,7 @@
         <v>1012</v>
       </c>
     </row>
-    <row r="590" customFormat="false" ht="20.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="590" customFormat="false" ht="36.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A590" s="52" t="n">
         <v>586</v>
       </c>
@@ -29619,7 +29639,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="591" customFormat="false" ht="20.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="591" customFormat="false" ht="36.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A591" s="52" t="n">
         <v>587</v>
       </c>
@@ -29650,7 +29670,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="592" customFormat="false" ht="20.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="592" customFormat="false" ht="36.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A592" s="52" t="n">
         <v>588</v>
       </c>
@@ -29681,7 +29701,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="593" customFormat="false" ht="20.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="593" customFormat="false" ht="36.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A593" s="52" t="n">
         <v>589</v>
       </c>
@@ -29712,7 +29732,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="594" customFormat="false" ht="20.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="594" customFormat="false" ht="36.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A594" s="52" t="n">
         <v>590</v>
       </c>
@@ -29774,7 +29794,7 @@
         <v>1026</v>
       </c>
     </row>
-    <row r="596" customFormat="false" ht="20.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="596" customFormat="false" ht="36.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A596" s="52" t="n">
         <v>592</v>
       </c>
@@ -29836,7 +29856,7 @@
         <v>1030</v>
       </c>
     </row>
-    <row r="598" customFormat="false" ht="20.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="598" customFormat="false" ht="36.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A598" s="52" t="n">
         <v>594</v>
       </c>
@@ -29867,7 +29887,7 @@
         <v>1034</v>
       </c>
     </row>
-    <row r="599" customFormat="false" ht="20.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="599" customFormat="false" ht="36.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A599" s="52" t="n">
         <v>595</v>
       </c>
@@ -29960,7 +29980,7 @@
         <v>1041</v>
       </c>
     </row>
-    <row r="602" customFormat="false" ht="20.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="602" customFormat="false" ht="36.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A602" s="52" t="n">
         <v>598</v>
       </c>
@@ -29991,7 +30011,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="603" customFormat="false" ht="20.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="603" customFormat="false" ht="36.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A603" s="52" t="n">
         <v>599</v>
       </c>
@@ -30022,7 +30042,7 @@
         <v>1047</v>
       </c>
     </row>
-    <row r="604" customFormat="false" ht="20.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="604" customFormat="false" ht="36.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A604" s="52" t="n">
         <v>600</v>
       </c>
@@ -30053,7 +30073,7 @@
         <v>1049</v>
       </c>
     </row>
-    <row r="605" customFormat="false" ht="20.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="605" customFormat="false" ht="36.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A605" s="52" t="n">
         <v>601</v>
       </c>
@@ -30084,7 +30104,7 @@
         <v>652</v>
       </c>
     </row>
-    <row r="606" customFormat="false" ht="20.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="606" customFormat="false" ht="36.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A606" s="52" t="n">
         <v>602</v>
       </c>
@@ -30115,7 +30135,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="607" customFormat="false" ht="20.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="607" customFormat="false" ht="36.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A607" s="52" t="n">
         <v>603</v>
       </c>
@@ -30146,7 +30166,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="608" customFormat="false" ht="20.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="608" customFormat="false" ht="36.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A608" s="52" t="n">
         <v>604</v>
       </c>
@@ -30177,7 +30197,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="609" customFormat="false" ht="20.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="609" customFormat="false" ht="36.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A609" s="52" t="n">
         <v>605</v>
       </c>
@@ -30208,7 +30228,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="610" customFormat="false" ht="20.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="610" customFormat="false" ht="36.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A610" s="52" t="n">
         <v>606</v>
       </c>
@@ -30239,7 +30259,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="611" customFormat="false" ht="20.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="611" customFormat="false" ht="36.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A611" s="52" t="n">
         <v>607</v>
       </c>
@@ -30270,7 +30290,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="612" customFormat="false" ht="20.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="612" customFormat="false" ht="36.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A612" s="49" t="n">
         <v>608</v>
       </c>
@@ -30301,7 +30321,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="613" customFormat="false" ht="20.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="613" customFormat="false" ht="36.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A613" s="52" t="n">
         <v>609</v>
       </c>
@@ -30332,7 +30352,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="614" customFormat="false" ht="20.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="614" customFormat="false" ht="36.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A614" s="52" t="n">
         <v>610</v>
       </c>
@@ -30363,7 +30383,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="615" customFormat="false" ht="20.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="615" customFormat="false" ht="36.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A615" s="52" t="n">
         <v>611</v>
       </c>
@@ -30425,7 +30445,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="617" customFormat="false" ht="20.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="617" customFormat="false" ht="36.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A617" s="52" t="n">
         <v>613</v>
       </c>
@@ -30518,7 +30538,7 @@
         <v>652</v>
       </c>
     </row>
-    <row r="620" customFormat="false" ht="20.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="620" customFormat="false" ht="36.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A620" s="52" t="n">
         <v>616</v>
       </c>
@@ -30549,7 +30569,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="621" customFormat="false" ht="20.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="621" customFormat="false" ht="36.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A621" s="52" t="n">
         <v>617</v>
       </c>
@@ -30580,7 +30600,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="622" customFormat="false" ht="20.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="622" customFormat="false" ht="36.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A622" s="52" t="n">
         <v>618</v>
       </c>
@@ -49809,7 +49829,7 @@
         <v>1547</v>
       </c>
     </row>
-    <row r="7" customFormat="false" ht="69.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="7" customFormat="false" ht="86.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B7" s="70" t="s">
         <v>1548</v>
       </c>
@@ -49893,26 +49913,26 @@
     </row>
     <row r="20" customFormat="false" ht="36.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B20" s="70" t="s">
-        <v>419</v>
+        <v>1568</v>
       </c>
       <c r="C20" s="61" t="s">
-        <v>1568</v>
+        <v>1569</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="53.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B21" s="70" t="s">
-        <v>1569</v>
+        <v>1570</v>
       </c>
       <c r="C21" s="61" t="s">
-        <v>1570</v>
+        <v>1571</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="20.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B22" s="70" t="s">
-        <v>1571</v>
+        <v>1572</v>
       </c>
       <c r="C22" s="61" t="s">
-        <v>1572</v>
+        <v>1573</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="36.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -49920,12 +49940,12 @@
         <v>983</v>
       </c>
       <c r="C23" s="61" t="s">
-        <v>1573</v>
+        <v>1574</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="69" t="s">
-        <v>1574</v>
+        <v>1575</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="36.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -49933,7 +49953,7 @@
         <v>1562</v>
       </c>
       <c r="C26" s="61" t="s">
-        <v>1575</v>
+        <v>1576</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="36.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -49941,7 +49961,7 @@
         <v>1564</v>
       </c>
       <c r="C27" s="61" t="s">
-        <v>1576</v>
+        <v>1577</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="69.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -49949,60 +49969,60 @@
         <v>1566</v>
       </c>
       <c r="C28" s="61" t="s">
-        <v>1577</v>
+        <v>1578</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="36.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B29" s="70" t="s">
-        <v>419</v>
+        <v>1568</v>
       </c>
       <c r="C29" s="61" t="s">
-        <v>1578</v>
+        <v>1579</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="20.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B30" s="70" t="s">
-        <v>1569</v>
+        <v>1570</v>
       </c>
       <c r="C30" s="61" t="s">
-        <v>1579</v>
+        <v>1580</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="20.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B31" s="70" t="s">
-        <v>1571</v>
+        <v>1572</v>
       </c>
       <c r="C31" s="61" t="s">
-        <v>1580</v>
+        <v>1581</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="20.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B32" s="70" t="s">
-        <v>1581</v>
+        <v>1582</v>
       </c>
       <c r="C32" s="61" t="s">
-        <v>1582</v>
+        <v>1583</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A34" s="69" t="s">
-        <v>1583</v>
+        <v>1584</v>
       </c>
     </row>
     <row r="35" customFormat="false" ht="53.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B35" s="70" t="s">
-        <v>1584</v>
+        <v>1585</v>
       </c>
       <c r="C35" s="71" t="s">
-        <v>1585</v>
+        <v>1586</v>
       </c>
     </row>
     <row r="36" customFormat="false" ht="36.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B36" s="70" t="s">
-        <v>1586</v>
+        <v>1587</v>
       </c>
       <c r="C36" s="61" t="s">
-        <v>1587</v>
+        <v>1588</v>
       </c>
     </row>
   </sheetData>
